--- a/ANF.xlsx
+++ b/ANF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5A3ECB-1914-470D-8042-39A78874CC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9577BD04-D925-473B-AFE5-FCB40C9E3BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{5386E427-DDBF-4556-BEE6-790EAB42F0A7}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{5386E427-DDBF-4556-BEE6-790EAB42F0A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1520,6 +1520,9 @@
     <xf numFmtId="10" fontId="7" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1531,9 +1534,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1905,7 +1905,7 @@
       <c r="I3" s="3">
         <v>47.319000000000003</v>
       </c>
-      <c r="J3" s="82" t="s">
+      <c r="J3" s="78" t="s">
         <v>306</v>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
         <f>759.54+25.036</f>
         <v>784.57600000000002</v>
       </c>
-      <c r="J5" s="82" t="s">
+      <c r="J5" s="78" t="s">
         <v>306</v>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       <c r="I6" s="5">
         <v>0</v>
       </c>
-      <c r="J6" s="82" t="s">
+      <c r="J6" s="78" t="s">
         <v>306</v>
       </c>
     </row>
@@ -2216,6 +2216,9 @@
       <c r="V3" s="4">
         <v>278</v>
       </c>
+      <c r="W3" s="2">
+        <v>306</v>
+      </c>
     </row>
     <row r="4" spans="1:72" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
@@ -2259,6 +2262,9 @@
       <c r="V4" s="4">
         <v>511</v>
       </c>
+      <c r="W4" s="2">
+        <v>523</v>
+      </c>
     </row>
     <row r="5" spans="1:72" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
@@ -2305,6 +2311,10 @@
         <f>+V13/V3</f>
         <v>3.678322302158274</v>
       </c>
+      <c r="W5" s="21">
+        <f>+W13/W3</f>
+        <v>3.2989045751633985</v>
+      </c>
     </row>
     <row r="6" spans="1:72" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
@@ -2351,6 +2361,10 @@
         <f>+V16/V4</f>
         <v>3.276921917808219</v>
       </c>
+      <c r="W6" s="21">
+        <f>+W16/W4</f>
+        <v>3.6708240917782025</v>
+      </c>
     </row>
     <row r="8" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A8" s="22"/>
@@ -2397,7 +2411,9 @@
       <c r="V8" s="3">
         <v>4027.5140000000001</v>
       </c>
-      <c r="W8" s="3"/>
+      <c r="W8" s="3">
+        <v>4290.3950000000004</v>
+      </c>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
@@ -2493,7 +2509,9 @@
       <c r="V9" s="3">
         <v>770.51900000000001</v>
       </c>
-      <c r="W9" s="3"/>
+      <c r="W9" s="3">
+        <v>818.14</v>
+      </c>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
@@ -2589,7 +2607,9 @@
       <c r="V10" s="3">
         <v>150.554</v>
       </c>
-      <c r="W10" s="3"/>
+      <c r="W10" s="3">
+        <v>157.75700000000001</v>
+      </c>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
@@ -2701,7 +2721,9 @@
       <c r="V11" s="3">
         <v>2556.4340000000002</v>
       </c>
-      <c r="W11" s="3"/>
+      <c r="W11" s="3">
+        <v>2523.6619999999998</v>
+      </c>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
@@ -2782,7 +2804,10 @@
         <f>+V11*60%</f>
         <v>1533.8604</v>
       </c>
-      <c r="W12" s="3"/>
+      <c r="W12" s="3">
+        <f>+W11*60%</f>
+        <v>1514.1971999999998</v>
+      </c>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
@@ -2863,7 +2888,10 @@
         <f>+V11*40%</f>
         <v>1022.5736000000002</v>
       </c>
-      <c r="W13" s="3"/>
+      <c r="W13" s="3">
+        <f>+W11*40%</f>
+        <v>1009.4648</v>
+      </c>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
@@ -2975,7 +3003,9 @@
       <c r="V14" s="3">
         <v>2392.1529999999998</v>
       </c>
-      <c r="W14" s="3"/>
+      <c r="W14" s="3">
+        <v>2742.63</v>
+      </c>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
@@ -3056,7 +3086,10 @@
         <f>+V14*30%</f>
         <v>717.64589999999987</v>
       </c>
-      <c r="W15" s="3"/>
+      <c r="W15" s="3">
+        <f>+W14*30%</f>
+        <v>822.78899999999999</v>
+      </c>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
@@ -3137,7 +3170,10 @@
         <f>+V14*70%</f>
         <v>1674.5070999999998</v>
       </c>
-      <c r="W16" s="3"/>
+      <c r="W16" s="3">
+        <f>+W14*70%</f>
+        <v>1919.8409999999999</v>
+      </c>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
@@ -3975,7 +4011,7 @@
         <v>484.67099999999931</v>
       </c>
       <c r="V23" s="3">
-        <f t="shared" ref="V23:W23" si="14">V19-SUM(V20:V21)+V22</f>
+        <f t="shared" ref="V23" si="14">V19-SUM(V20:V21)+V22</f>
         <v>740.8200000000005</v>
       </c>
       <c r="W23" s="3">
@@ -5288,7 +5324,7 @@
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
       <c r="Q35" s="26">
-        <f t="shared" ref="Q35:V35" si="27">Q3/P3-1</f>
+        <f t="shared" ref="Q35:W35" si="27">Q3/P3-1</f>
         <v>-3.4482758620689613E-2</v>
       </c>
       <c r="R35" s="26">
@@ -5311,7 +5347,10 @@
         <f t="shared" si="27"/>
         <v>0.12550607287449389</v>
       </c>
-      <c r="W35" s="3"/>
+      <c r="W35" s="26">
+        <f t="shared" si="27"/>
+        <v>0.10071942446043169</v>
+      </c>
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
@@ -5404,7 +5443,10 @@
         <f>+V14/U14-1</f>
         <v>0.15063172471646102</v>
       </c>
-      <c r="W36" s="3"/>
+      <c r="W36" s="26">
+        <f>+W14/V14-1</f>
+        <v>0.1465111136286017</v>
+      </c>
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
@@ -5512,7 +5554,10 @@
         <f>+V11/U11-1</f>
         <v>0.16112561010062287</v>
       </c>
-      <c r="W37" s="3"/>
+      <c r="W37" s="26">
+        <f>+W11/V11-1</f>
+        <v>-1.2819419550827549E-2</v>
+      </c>
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
@@ -5620,7 +5665,10 @@
         <f>+V14/U14-1</f>
         <v>0.15063172471646102</v>
       </c>
-      <c r="W38" s="3"/>
+      <c r="W38" s="26">
+        <f>+W14/V14-1</f>
+        <v>0.1465111136286017</v>
+      </c>
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
@@ -5728,7 +5776,10 @@
         <f>V17/U17-1</f>
         <v>0.15602905802049549</v>
       </c>
-      <c r="W39" s="3"/>
+      <c r="W39" s="27">
+        <f>W17/V17-1</f>
+        <v>6.4201154794287785E-2</v>
+      </c>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
@@ -5851,7 +5902,10 @@
         <f t="shared" si="35"/>
         <v>0.64152878387305312</v>
       </c>
-      <c r="W40" s="3"/>
+      <c r="W40" s="26">
+        <f t="shared" ref="W40" si="36">W19/W17</f>
+        <v>0.6147414537591156</v>
+      </c>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
@@ -5907,39 +5961,39 @@
         <v>46</v>
       </c>
       <c r="C41" s="26">
-        <f t="shared" ref="C41:J41" si="36">C23/C17</f>
+        <f t="shared" ref="C41:J41" si="37">C23/C17</f>
         <v>4.0679717797017623E-2</v>
       </c>
       <c r="D41" s="26">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>9.6052258792210451E-2</v>
       </c>
       <c r="E41" s="26">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.13064743461712133</v>
       </c>
       <c r="F41" s="26">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.15334842491639172</v>
       </c>
       <c r="G41" s="26">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.12721189736757027</v>
       </c>
       <c r="H41" s="26">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.15487568498043178</v>
       </c>
       <c r="I41" s="26">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.14829366582683046</v>
       </c>
       <c r="J41" s="26">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.16156303453114571</v>
       </c>
       <c r="K41" s="26">
-        <f t="shared" ref="K41" si="37">K23/K17</f>
+        <f t="shared" ref="K41" si="38">K23/K17</f>
         <v>9.2528918419663944E-2</v>
       </c>
       <c r="L41" s="26"/>
@@ -5947,34 +6001,37 @@
       <c r="N41" s="26"/>
       <c r="O41" s="3"/>
       <c r="P41" s="26">
-        <f t="shared" ref="P41:V41" si="38">P23/P17</f>
+        <f t="shared" ref="P41:V41" si="39">P23/P17</f>
         <v>3.5476917274656621E-2</v>
       </c>
       <c r="Q41" s="26">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1.9339383998059279E-2</v>
       </c>
       <c r="R41" s="26">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>-6.5492752250604106E-3</v>
       </c>
       <c r="S41" s="26">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>9.2406527959732421E-2</v>
       </c>
       <c r="T41" s="26">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2.5055229516536028E-2</v>
       </c>
       <c r="U41" s="26">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.11322297851484692</v>
       </c>
       <c r="V41" s="26">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.14970333955935308</v>
       </c>
-      <c r="W41" s="3"/>
+      <c r="W41" s="26">
+        <f t="shared" ref="W41" si="40">W23/W17</f>
+        <v>0.13275811519756217</v>
+      </c>
       <c r="X41" s="3"/>
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
@@ -6030,39 +6087,39 @@
         <v>48</v>
       </c>
       <c r="C42" s="26">
-        <f t="shared" ref="C42:J42" si="39">C30/C17</f>
+        <f t="shared" ref="C42:J42" si="41">C30/C17</f>
         <v>1.9821912597458774E-2</v>
       </c>
       <c r="D42" s="26">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>6.0826753764653761E-2</v>
       </c>
       <c r="E42" s="26">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>9.1071731140036694E-2</v>
       </c>
       <c r="F42" s="26">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.10905515631764451</v>
       </c>
       <c r="G42" s="26">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.11151822715115656</v>
       </c>
       <c r="H42" s="26">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.11743479127387414</v>
       </c>
       <c r="I42" s="26">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.10916684174741052</v>
       </c>
       <c r="J42" s="26">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.11812984528527355</v>
       </c>
       <c r="K42" s="26">
-        <f t="shared" ref="K42" si="40">K30/K17</f>
+        <f t="shared" ref="K42" si="42">K30/K17</f>
         <v>7.3281868130365843E-2</v>
       </c>
       <c r="L42" s="26"/>
@@ -6070,34 +6127,37 @@
       <c r="N42" s="26"/>
       <c r="O42" s="3"/>
       <c r="P42" s="26">
-        <f t="shared" ref="P42:V42" si="41">P30/P17</f>
+        <f t="shared" ref="P42:V42" si="43">P30/P17</f>
         <v>2.0762879344331946E-2</v>
       </c>
       <c r="Q42" s="26">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>1.0863154013181801E-2</v>
       </c>
       <c r="R42" s="26">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-3.6482237062709803E-2</v>
       </c>
       <c r="S42" s="26">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>7.0839330655726368E-2</v>
       </c>
       <c r="T42" s="26">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>7.6154397632523555E-4</v>
       </c>
       <c r="U42" s="26">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>7.6652127689148086E-2</v>
       </c>
       <c r="V42" s="26">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.11442114688495938</v>
       </c>
-      <c r="W42" s="3"/>
+      <c r="W42" s="26">
+        <f t="shared" ref="W42" si="44">W30/W17</f>
+        <v>9.6257670482381166E-2</v>
+      </c>
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
@@ -6153,39 +6213,39 @@
         <v>49</v>
       </c>
       <c r="C43" s="26">
-        <f t="shared" ref="C43:J43" si="42">C27/C26</f>
+        <f t="shared" ref="C43:J43" si="45">C27/C26</f>
         <v>0.41609684279404618</v>
       </c>
       <c r="D43" s="26">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0.33820496929404442</v>
       </c>
       <c r="E43" s="26">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0.28844039636255064</v>
       </c>
       <c r="F43" s="26">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0.29229045861887204</v>
       </c>
       <c r="G43" s="26">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0.14678314003500131</v>
       </c>
       <c r="H43" s="26">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0.25133828831818056</v>
       </c>
       <c r="I43" s="26">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0.28801425418184734</v>
       </c>
       <c r="J43" s="26">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0.28406714925159093</v>
       </c>
       <c r="K43" s="26">
-        <f t="shared" ref="K43" si="43">K27/K26</f>
+        <f t="shared" ref="K43" si="46">K27/K26</f>
         <v>0.24536541231212411</v>
       </c>
       <c r="L43" s="26"/>
@@ -6193,34 +6253,37 @@
       <c r="N43" s="26"/>
       <c r="O43" s="3"/>
       <c r="P43" s="26">
-        <f t="shared" ref="P43:V43" si="44">P27/P26</f>
+        <f t="shared" ref="P43:V43" si="47">P27/P26</f>
         <v>0.32276332637259642</v>
       </c>
       <c r="Q43" s="26">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.27868957661516452</v>
       </c>
       <c r="R43" s="26">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>-1.2352748086904732</v>
       </c>
       <c r="S43" s="26">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.12592645335853508</v>
       </c>
       <c r="T43" s="26">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.84503700608809063</v>
       </c>
       <c r="U43" s="26">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.30742578448437885</v>
       </c>
       <c r="V43" s="26">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.25324160863405548</v>
       </c>
-      <c r="W43" s="3"/>
+      <c r="W43" s="26">
+        <f t="shared" ref="W43" si="48">W27/W26</f>
+        <v>0.28549527451121842</v>
+      </c>
       <c r="X43" s="3"/>
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
@@ -6382,7 +6445,10 @@
         <f>772.727+116.221</f>
         <v>888.94799999999998</v>
       </c>
-      <c r="W45" s="3"/>
+      <c r="W45" s="3">
+        <f>510.563+97.006</f>
+        <v>607.56899999999996</v>
+      </c>
       <c r="X45" s="3"/>
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
@@ -6471,7 +6537,9 @@
       <c r="V46" s="3">
         <v>105.324</v>
       </c>
-      <c r="W46" s="3"/>
+      <c r="W46" s="3">
+        <v>113.31100000000001</v>
+      </c>
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
@@ -6560,7 +6628,9 @@
       <c r="V47" s="3">
         <v>575.005</v>
       </c>
-      <c r="W47" s="3"/>
+      <c r="W47" s="3">
+        <v>542.05899999999997</v>
+      </c>
       <c r="X47" s="3"/>
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
@@ -6649,7 +6719,9 @@
       <c r="V48" s="3">
         <v>104.154</v>
       </c>
-      <c r="W48" s="3"/>
+      <c r="W48" s="3">
+        <v>111.23099999999999</v>
+      </c>
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
@@ -6718,23 +6790,23 @@
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
       <c r="P49" s="3">
-        <f t="shared" ref="P49:T49" si="45">SUM(P45:P48)</f>
+        <f t="shared" ref="P49:T49" si="49">SUM(P45:P48)</f>
         <v>1335.95</v>
       </c>
       <c r="Q49" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>1264.749</v>
       </c>
       <c r="R49" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>1661.6289999999999</v>
       </c>
       <c r="S49" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>1507.759</v>
       </c>
       <c r="T49" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>1228.0179999999998</v>
       </c>
       <c r="U49" s="3">
@@ -6745,7 +6817,10 @@
         <f>SUM(V45:V48)</f>
         <v>1673.431</v>
       </c>
-      <c r="W49" s="3"/>
+      <c r="W49" s="3">
+        <f>SUM(W45:W48)</f>
+        <v>1374.1699999999998</v>
+      </c>
       <c r="X49" s="3"/>
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
@@ -6834,7 +6909,9 @@
       <c r="V50" s="3">
         <v>575.77300000000002</v>
       </c>
-      <c r="W50" s="3"/>
+      <c r="W50" s="3">
+        <v>606.05999999999995</v>
+      </c>
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
@@ -6923,7 +7000,9 @@
       <c r="V51" s="3">
         <v>803.12099999999998</v>
       </c>
-      <c r="W51" s="3"/>
+      <c r="W51" s="3">
+        <v>868.13</v>
+      </c>
       <c r="X51" s="3"/>
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
@@ -7012,7 +7091,9 @@
       <c r="V52" s="3">
         <v>247.56200000000001</v>
       </c>
-      <c r="W52" s="3"/>
+      <c r="W52" s="3">
+        <v>247.816</v>
+      </c>
       <c r="X52" s="3"/>
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
@@ -7081,23 +7162,23 @@
       <c r="N53" s="3"/>
       <c r="O53" s="3"/>
       <c r="P53" s="3">
-        <f t="shared" ref="P53:T53" si="46">SUM(P50:P52)</f>
+        <f t="shared" ref="P53:T53" si="50">SUM(P50:P52)</f>
         <v>1049.643</v>
       </c>
       <c r="Q53" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>2284.9160000000002</v>
       </c>
       <c r="R53" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>1653.2730000000001</v>
       </c>
       <c r="S53" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>1431.732</v>
       </c>
       <c r="T53" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>1485.0819999999999</v>
       </c>
       <c r="U53" s="3">
@@ -7108,7 +7189,10 @@
         <f>SUM(V50:V52)</f>
         <v>1626.4560000000001</v>
       </c>
-      <c r="W53" s="3"/>
+      <c r="W53" s="3">
+        <f>SUM(W50:W52)</f>
+        <v>1722.0060000000001</v>
+      </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
@@ -7177,34 +7261,37 @@
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="24">
-        <f t="shared" ref="P54:V54" si="47">P49+P53</f>
+        <f t="shared" ref="P54:W54" si="51">P49+P53</f>
         <v>2385.5929999999998</v>
       </c>
       <c r="Q54" s="24">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>3549.665</v>
       </c>
       <c r="R54" s="24">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>3314.902</v>
       </c>
       <c r="S54" s="24">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>2939.491</v>
       </c>
       <c r="T54" s="24">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>2713.0999999999995</v>
       </c>
       <c r="U54" s="24">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>2974.2330000000002</v>
       </c>
       <c r="V54" s="24">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>3299.8870000000002</v>
       </c>
-      <c r="W54" s="3"/>
+      <c r="W54" s="24">
+        <f t="shared" si="51"/>
+        <v>3096.1759999999999</v>
+      </c>
       <c r="X54" s="3"/>
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
@@ -7364,7 +7451,9 @@
       <c r="V56" s="3">
         <v>364.53199999999998</v>
       </c>
-      <c r="W56" s="3"/>
+      <c r="W56" s="3">
+        <v>296.738</v>
+      </c>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
@@ -7453,7 +7542,9 @@
       <c r="V57" s="3">
         <v>504.92200000000003</v>
       </c>
-      <c r="W57" s="3"/>
+      <c r="W57" s="3">
+        <v>433.68200000000002</v>
+      </c>
       <c r="X57" s="3"/>
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
@@ -7542,7 +7633,9 @@
       <c r="V58" s="3">
         <v>211.6</v>
       </c>
-      <c r="W58" s="3"/>
+      <c r="W58" s="3">
+        <v>215.511</v>
+      </c>
       <c r="X58" s="3"/>
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
@@ -7631,7 +7724,9 @@
       <c r="V59" s="3">
         <v>45.89</v>
       </c>
-      <c r="W59" s="3"/>
+      <c r="W59" s="3">
+        <v>52.939</v>
+      </c>
       <c r="X59" s="3"/>
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
@@ -7720,7 +7815,9 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-      <c r="W60" s="3"/>
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
       <c r="X60" s="3"/>
       <c r="Y60" s="3"/>
       <c r="Z60" s="3"/>
@@ -7789,23 +7886,23 @@
       <c r="N61" s="3"/>
       <c r="O61" s="3"/>
       <c r="P61" s="3">
-        <f t="shared" ref="P61:T61" si="48">SUM(P56:P60)</f>
+        <f t="shared" ref="P61:T61" si="52">SUM(P56:P60)</f>
         <v>558.91700000000003</v>
       </c>
       <c r="Q61" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>815.35400000000004</v>
       </c>
       <c r="R61" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>959.399</v>
       </c>
       <c r="S61" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>1015.24</v>
       </c>
       <c r="T61" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>902.2</v>
       </c>
       <c r="U61" s="3">
@@ -7816,7 +7913,10 @@
         <f>SUM(V56:V60)</f>
         <v>1126.944</v>
       </c>
-      <c r="W61" s="3"/>
+      <c r="W61" s="3">
+        <f>SUM(W56:W60)</f>
+        <v>998.87</v>
+      </c>
       <c r="X61" s="3"/>
       <c r="Y61" s="3"/>
       <c r="Z61" s="3"/>
@@ -7905,7 +8005,9 @@
       <c r="V62" s="3">
         <v>740.01300000000003</v>
       </c>
-      <c r="W62" s="3"/>
+      <c r="W62" s="3">
+        <v>810.39099999999996</v>
+      </c>
       <c r="X62" s="3"/>
       <c r="Y62" s="3"/>
       <c r="Z62" s="3"/>
@@ -7994,7 +8096,9 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-      <c r="W63" s="3"/>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
       <c r="X63" s="3"/>
       <c r="Y63" s="3"/>
       <c r="Z63" s="3"/>
@@ -8084,7 +8188,9 @@
       <c r="V64" s="3">
         <v>81.606999999999999</v>
       </c>
-      <c r="W64" s="3"/>
+      <c r="W64" s="3">
+        <v>84.320999999999998</v>
+      </c>
       <c r="X64" s="3"/>
       <c r="Y64" s="3"/>
       <c r="Z64" s="3"/>
@@ -8153,23 +8259,23 @@
       <c r="N65" s="3"/>
       <c r="O65" s="3"/>
       <c r="P65" s="3">
-        <f t="shared" ref="P65:T65" si="49">SUM(P62:P64)</f>
+        <f t="shared" ref="P65:T65" si="53">SUM(P62:P64)</f>
         <v>608.05499999999995</v>
       </c>
       <c r="Q65" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>1663.133</v>
       </c>
       <c r="R65" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>1406.191</v>
       </c>
       <c r="S65" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>1086.9269999999999</v>
       </c>
       <c r="T65" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>1104.3309999999999</v>
       </c>
       <c r="U65" s="3">
@@ -8180,7 +8286,10 @@
         <f>SUM(V62:V64)</f>
         <v>821.62</v>
       </c>
-      <c r="W65" s="3"/>
+      <c r="W65" s="3">
+        <f>SUM(W62:W64)</f>
+        <v>894.71199999999999</v>
+      </c>
       <c r="X65" s="3"/>
       <c r="Y65" s="3"/>
       <c r="Z65" s="3"/>
@@ -8249,34 +8358,37 @@
       <c r="N66" s="3"/>
       <c r="O66" s="3"/>
       <c r="P66" s="3">
-        <f t="shared" ref="P66:V66" si="50">P61+P65</f>
+        <f t="shared" ref="P66:W66" si="54">P61+P65</f>
         <v>1166.972</v>
       </c>
       <c r="Q66" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>2478.4870000000001</v>
       </c>
       <c r="R66" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>2365.59</v>
       </c>
       <c r="S66" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>2102.1669999999999</v>
       </c>
       <c r="T66" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>2006.5309999999999</v>
       </c>
       <c r="U66" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>1924.4270000000001</v>
       </c>
       <c r="V66" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>1948.5639999999999</v>
       </c>
-      <c r="W66" s="3"/>
+      <c r="W66" s="3">
+        <f t="shared" si="54"/>
+        <v>1893.5819999999999</v>
+      </c>
       <c r="X66" s="3"/>
       <c r="Y66" s="3"/>
       <c r="Z66" s="3"/>
@@ -8365,7 +8477,9 @@
       <c r="V67" s="3">
         <v>1351.3230000000001</v>
       </c>
-      <c r="W67" s="3"/>
+      <c r="W67" s="3">
+        <v>1202.5940000000001</v>
+      </c>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
@@ -8434,34 +8548,37 @@
       <c r="N68" s="3"/>
       <c r="O68" s="3"/>
       <c r="P68" s="24">
-        <f t="shared" ref="P68:V68" si="51">P67+P66</f>
+        <f t="shared" ref="P68:W68" si="55">P67+P66</f>
         <v>2385.5929999999998</v>
       </c>
       <c r="Q68" s="24">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v>3549.665</v>
       </c>
       <c r="R68" s="24">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v>3314.902</v>
       </c>
       <c r="S68" s="24">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v>2939.4909999999995</v>
       </c>
       <c r="T68" s="24">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v>2713.1</v>
       </c>
       <c r="U68" s="24">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v>2974.4139999999998</v>
       </c>
       <c r="V68" s="24">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v>3299.8869999999997</v>
       </c>
-      <c r="W68" s="3"/>
+      <c r="W68" s="24">
+        <f t="shared" si="55"/>
+        <v>3096.1759999999999</v>
+      </c>
       <c r="X68" s="3"/>
       <c r="Y68" s="3"/>
       <c r="Z68" s="3"/>
@@ -8752,27 +8869,27 @@
       <c r="N72" s="3"/>
       <c r="O72" s="3"/>
       <c r="P72" s="3">
-        <f t="shared" ref="P72:U72" si="52">P28</f>
+        <f t="shared" ref="P72:U72" si="56">P28</f>
         <v>78.80800000000022</v>
       </c>
       <c r="Q72" s="3">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>44.960000000000633</v>
       </c>
       <c r="R72" s="3">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>-108.95400000000021</v>
       </c>
       <c r="S72" s="3">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>270.06599999999986</v>
       </c>
       <c r="T72" s="3">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>10.385000000000616</v>
       </c>
       <c r="U72" s="3">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>335.41299999999933</v>
       </c>
       <c r="V72" s="3"/>
@@ -10051,23 +10168,23 @@
       <c r="N87" s="3"/>
       <c r="O87" s="3"/>
       <c r="P87" s="3">
-        <f t="shared" ref="P87:T87" si="53">SUM(P81:P86)</f>
+        <f t="shared" ref="P87:T87" si="57">SUM(P81:P86)</f>
         <v>72.11399999999999</v>
       </c>
       <c r="Q87" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>30.245000000000001</v>
       </c>
       <c r="R87" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>215.63300000000004</v>
       </c>
       <c r="S87" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>-156.16800000000003</v>
       </c>
       <c r="T87" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>-199.99700000000001</v>
       </c>
       <c r="U87" s="3">
@@ -10148,23 +10265,23 @@
         <v>352.95100000000019</v>
       </c>
       <c r="Q88" s="24">
-        <f t="shared" ref="Q88:U88" si="54">Q72+SUM(Q73:Q79)+Q87</f>
+        <f t="shared" ref="Q88:U88" si="58">Q72+SUM(Q73:Q79)+Q87</f>
         <v>300.64900000000068</v>
       </c>
       <c r="R88" s="24">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>404.91799999999989</v>
       </c>
       <c r="S88" s="24">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>277.78199999999981</v>
       </c>
       <c r="T88" s="24">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>-2.3429999999993925</v>
       </c>
       <c r="U88" s="24">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>653.42199999999923</v>
       </c>
       <c r="V88" s="3"/>
@@ -10485,23 +10602,23 @@
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
       <c r="P92" s="24">
-        <f t="shared" ref="P92:T92" si="55">SUM(P89:P91)</f>
+        <f t="shared" ref="P92:T92" si="59">SUM(P89:P91)</f>
         <v>-152.393</v>
       </c>
       <c r="Q92" s="24">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>-202.78399999999999</v>
       </c>
       <c r="R92" s="24">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>-51.91</v>
       </c>
       <c r="S92" s="24">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>-96.975999999999999</v>
       </c>
       <c r="T92" s="24">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>-140.67500000000001</v>
       </c>
       <c r="U92" s="24">
@@ -11102,11 +11219,11 @@
       <c r="N99" s="3"/>
       <c r="O99" s="3"/>
       <c r="P99" s="24">
-        <f t="shared" ref="P99:Q99" si="56">SUM(P93:P98)</f>
+        <f t="shared" ref="P99:Q99" si="60">SUM(P93:P98)</f>
         <v>-131.691</v>
       </c>
       <c r="Q99" s="24">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>-147.87299999999999</v>
       </c>
       <c r="R99" s="24">
@@ -11114,15 +11231,15 @@
         <v>69.717000000000013</v>
       </c>
       <c r="S99" s="24">
-        <f t="shared" ref="S99:U99" si="57">SUM(S93:S98)</f>
+        <f t="shared" ref="S99:U99" si="61">SUM(S93:S98)</f>
         <v>-446.89800000000002</v>
       </c>
       <c r="T99" s="24">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>-155.32900000000001</v>
       </c>
       <c r="U99" s="24">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>-111.20099999999999</v>
       </c>
       <c r="V99" s="3"/>
@@ -11354,23 +11471,23 @@
       <c r="N102" s="3"/>
       <c r="O102" s="3"/>
       <c r="P102" s="24">
-        <f t="shared" ref="P102:T102" si="58">P88+P92+P99+P101</f>
+        <f t="shared" ref="P102:T102" si="62">P88+P92+P99+P101</f>
         <v>47.892000000000188</v>
       </c>
       <c r="Q102" s="24">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>-53.600999999999303</v>
       </c>
       <c r="R102" s="24">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>431.89299999999992</v>
       </c>
       <c r="S102" s="24">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>-289.78600000000023</v>
       </c>
       <c r="T102" s="24">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>-306.79899999999941</v>
       </c>
       <c r="U102" s="24">
@@ -11447,27 +11564,27 @@
       <c r="N103" s="3"/>
       <c r="O103" s="3"/>
       <c r="P103" s="3">
-        <f t="shared" ref="P103:U103" si="59">P104-P102</f>
+        <f t="shared" ref="P103:U103" si="63">P104-P102</f>
         <v>697.96999999999969</v>
       </c>
       <c r="Q103" s="3">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>745.86199999999985</v>
       </c>
       <c r="R103" s="3">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>692.26100000000054</v>
       </c>
       <c r="S103" s="3">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>1124.1540000000005</v>
       </c>
       <c r="T103" s="3">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>834.36800000000017</v>
       </c>
       <c r="U103" s="3">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>527.56900000000076</v>
       </c>
       <c r="V103" s="3"/>
@@ -23747,19 +23864,19 @@
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B69" s="73"/>
-      <c r="C69" s="78" t="s">
+      <c r="C69" s="79" t="s">
         <v>154</v>
       </c>
-      <c r="D69" s="78"/>
-      <c r="E69" s="78"/>
-      <c r="F69" s="78"/>
-      <c r="G69" s="78"/>
-      <c r="H69" s="78"/>
-      <c r="I69" s="78"/>
-      <c r="J69" s="79"/>
+      <c r="D69" s="79"/>
+      <c r="E69" s="79"/>
+      <c r="F69" s="79"/>
+      <c r="G69" s="79"/>
+      <c r="H69" s="79"/>
+      <c r="I69" s="79"/>
+      <c r="J69" s="80"/>
     </row>
     <row r="70" spans="1:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="80" t="s">
+      <c r="B70" s="81" t="s">
         <v>153</v>
       </c>
       <c r="C70" s="74"/>
@@ -23772,7 +23889,7 @@
       <c r="J70" s="75"/>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B71" s="80"/>
+      <c r="B71" s="81"/>
       <c r="C71" s="76"/>
       <c r="D71" s="77"/>
       <c r="E71" s="77"/>
@@ -23783,7 +23900,7 @@
       <c r="J71" s="77"/>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B72" s="80"/>
+      <c r="B72" s="81"/>
       <c r="C72" s="76"/>
       <c r="D72" s="77"/>
       <c r="E72" s="77"/>
@@ -23794,7 +23911,7 @@
       <c r="J72" s="77"/>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B73" s="80"/>
+      <c r="B73" s="81"/>
       <c r="C73" s="76"/>
       <c r="D73" s="77"/>
       <c r="E73" s="77"/>
@@ -23805,7 +23922,7 @@
       <c r="J73" s="77"/>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B74" s="80"/>
+      <c r="B74" s="81"/>
       <c r="C74" s="76"/>
       <c r="D74" s="77"/>
       <c r="E74" s="77"/>
@@ -23816,7 +23933,7 @@
       <c r="J74" s="77"/>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B75" s="80"/>
+      <c r="B75" s="81"/>
       <c r="C75" s="76"/>
       <c r="D75" s="77"/>
       <c r="E75" s="77"/>
@@ -23827,7 +23944,7 @@
       <c r="J75" s="77"/>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B76" s="80"/>
+      <c r="B76" s="81"/>
       <c r="C76" s="76"/>
       <c r="D76" s="77"/>
       <c r="E76" s="77"/>
@@ -23838,7 +23955,7 @@
       <c r="J76" s="77"/>
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B77" s="81"/>
+      <c r="B77" s="82"/>
       <c r="C77" s="76"/>
       <c r="D77" s="77"/>
       <c r="E77" s="77"/>

--- a/ANF.xlsx
+++ b/ANF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9577BD04-D925-473B-AFE5-FCB40C9E3BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90ECCE3D-B58A-4B61-8EF2-217260ADACFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{5386E427-DDBF-4556-BEE6-790EAB42F0A7}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{5386E427-DDBF-4556-BEE6-790EAB42F0A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>

--- a/ANF.xlsx
+++ b/ANF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90ECCE3D-B58A-4B61-8EF2-217260ADACFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8DC616-2B13-43D5-B93D-C51990484B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{5386E427-DDBF-4556-BEE6-790EAB42F0A7}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{5386E427-DDBF-4556-BEE6-790EAB42F0A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
     <author>Oscar Settje</author>
   </authors>
   <commentList>
-    <comment ref="T2" authorId="0" shapeId="0" xr:uid="{AF008465-DB72-4CDE-AD76-9D03284A8A1F}">
+    <comment ref="X2" authorId="0" shapeId="0" xr:uid="{AF008465-DB72-4CDE-AD76-9D03284A8A1F}">
       <text>
         <r>
           <rPr>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="320">
   <si>
     <t>Abercrombie &amp; Fitch</t>
   </si>
@@ -1044,6 +1044,21 @@
   </si>
   <si>
     <t>FY18</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>n.a.</t>
   </si>
 </sst>
 </file>
@@ -1520,9 +1535,6 @@
     <xf numFmtId="10" fontId="7" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1534,6 +1546,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1895,7 +1910,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="2">
-        <v>95.69</v>
+        <v>83.06</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1903,10 +1918,10 @@
         <v>3</v>
       </c>
       <c r="I3" s="3">
-        <v>47.319000000000003</v>
-      </c>
-      <c r="J3" s="78" t="s">
-        <v>306</v>
+        <v>44.969000000000001</v>
+      </c>
+      <c r="J3" s="82" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -1921,7 +1936,7 @@
       </c>
       <c r="I4" s="5">
         <f>I2*I3</f>
-        <v>4527.9551099999999</v>
+        <v>3735.1251400000001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1935,11 +1950,11 @@
         <v>5</v>
       </c>
       <c r="I5" s="5">
-        <f>759.54+25.036</f>
-        <v>784.57600000000002</v>
-      </c>
-      <c r="J5" s="78" t="s">
-        <v>306</v>
+        <f>594.08+25.144</f>
+        <v>619.22400000000005</v>
+      </c>
+      <c r="J5" s="82" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -1949,8 +1964,8 @@
       <c r="I6" s="5">
         <v>0</v>
       </c>
-      <c r="J6" s="78" t="s">
-        <v>306</v>
+      <c r="J6" s="82" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1959,7 +1974,7 @@
       </c>
       <c r="I7" s="5">
         <f>I4+I6-I5</f>
-        <v>3743.3791099999999</v>
+        <v>3115.9011399999999</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -2098,7 +2113,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC2C5BFC-961F-4D88-9AA3-E79ECCFC9F4B}">
-  <dimension ref="A1:BT248"/>
+  <dimension ref="A1:BX248"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -2106,12 +2121,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:76" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:76" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>310</v>
       </c>
@@ -2148,33 +2163,45 @@
       <c r="N2" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4" t="s">
+      <c r="O2" s="82" t="s">
+        <v>315</v>
+      </c>
+      <c r="P2" s="82" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q2" s="82" t="s">
+        <v>317</v>
+      </c>
+      <c r="R2" s="82" t="s">
+        <v>318</v>
+      </c>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="Z2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="AA2" s="4" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="3" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>40</v>
       </c>
@@ -2191,36 +2218,40 @@
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
-      <c r="P3" s="4">
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4">
         <f>270+49</f>
         <v>319</v>
       </c>
-      <c r="Q3" s="4">
+      <c r="U3" s="4">
         <f>256+52</f>
         <v>308</v>
       </c>
-      <c r="R3" s="4">
+      <c r="V3" s="4">
         <f>190+48</f>
         <v>238</v>
       </c>
-      <c r="S3" s="4">
+      <c r="W3" s="4">
         <v>224</v>
       </c>
-      <c r="T3" s="4">
+      <c r="X3" s="4">
         <f>180+53</f>
         <v>233</v>
       </c>
-      <c r="U3" s="4">
+      <c r="Y3" s="4">
         <v>247</v>
       </c>
-      <c r="V3" s="4">
+      <c r="Z3" s="4">
         <v>278</v>
       </c>
-      <c r="W3" s="2">
+      <c r="AA3" s="2">
         <v>306</v>
       </c>
     </row>
-    <row r="4" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>41</v>
       </c>
@@ -2237,36 +2268,40 @@
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
-      <c r="P4" s="4">
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4">
         <f>393+149</f>
         <v>542</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="U4" s="4">
         <f>391+155</f>
         <v>546</v>
       </c>
-      <c r="R4" s="4">
+      <c r="V4" s="4">
         <f>347+150</f>
         <v>497</v>
       </c>
-      <c r="S4" s="4">
+      <c r="W4" s="4">
         <v>505</v>
       </c>
-      <c r="T4" s="4">
+      <c r="X4" s="4">
         <f>380+149</f>
         <v>529</v>
       </c>
-      <c r="U4" s="4">
+      <c r="Y4" s="4">
         <v>518</v>
       </c>
-      <c r="V4" s="4">
+      <c r="Z4" s="4">
         <v>511</v>
       </c>
-      <c r="W4" s="2">
+      <c r="AA4" s="2">
         <v>523</v>
       </c>
     </row>
-    <row r="5" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>114</v>
       </c>
@@ -2283,40 +2318,44 @@
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
-      <c r="P5" s="21">
-        <f>P11/P3</f>
-        <v>4.5064921630094039</v>
-      </c>
-      <c r="Q5" s="21">
-        <f>Q11/Q3</f>
-        <v>4.7550616883116881</v>
-      </c>
-      <c r="R5" s="21">
-        <f>R11/R3</f>
-        <v>5.4245168067226892</v>
-      </c>
-      <c r="S5" s="21">
-        <f>S11/S3</f>
-        <v>6.9856651785714288</v>
-      </c>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
       <c r="T5" s="21">
         <f>T11/T3</f>
+        <v>4.5064921630094039</v>
+      </c>
+      <c r="U5" s="21">
+        <f>U11/U3</f>
+        <v>4.7550616883116881</v>
+      </c>
+      <c r="V5" s="21">
+        <f>V11/V3</f>
+        <v>5.4245168067226892</v>
+      </c>
+      <c r="W5" s="21">
+        <f>W11/W3</f>
+        <v>6.9856651785714288</v>
+      </c>
+      <c r="X5" s="21">
+        <f>X11/X3</f>
         <v>7.4457768240343345</v>
       </c>
-      <c r="U5" s="21">
-        <f>+U13/U3</f>
+      <c r="Y5" s="21">
+        <f>+Y13/Y3</f>
         <v>3.5654834008097169</v>
       </c>
-      <c r="V5" s="21">
-        <f>+V13/V3</f>
+      <c r="Z5" s="21">
+        <f>+Z13/Z3</f>
         <v>3.678322302158274</v>
       </c>
-      <c r="W5" s="21">
-        <f>+W13/W3</f>
+      <c r="AA5" s="21">
+        <f>+AA13/AA3</f>
         <v>3.2989045751633985</v>
       </c>
     </row>
-    <row r="6" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>115</v>
       </c>
@@ -2333,40 +2372,44 @@
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
-      <c r="P6" s="21">
-        <f>P14/P4</f>
-        <v>3.9714723247232473</v>
-      </c>
-      <c r="Q6" s="21">
-        <f>Q14/Q4</f>
-        <v>3.9533223443223444</v>
-      </c>
-      <c r="R6" s="21">
-        <f>R14/R4</f>
-        <v>3.6908430583501004</v>
-      </c>
-      <c r="S6" s="21">
-        <f>S14/S4</f>
-        <v>4.2534237623762374</v>
-      </c>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
       <c r="T6" s="21">
         <f>T14/T4</f>
+        <v>3.9714723247232473</v>
+      </c>
+      <c r="U6" s="21">
+        <f>U14/U4</f>
+        <v>3.9533223443223444</v>
+      </c>
+      <c r="V6" s="21">
+        <f>V14/V4</f>
+        <v>3.6908430583501004</v>
+      </c>
+      <c r="W6" s="21">
+        <f>W14/W4</f>
+        <v>4.2534237623762374</v>
+      </c>
+      <c r="X6" s="21">
+        <f>X14/X4</f>
         <v>3.7105576559546312</v>
       </c>
-      <c r="U6" s="21">
-        <f>+U16/U4</f>
+      <c r="Y6" s="21">
+        <f>+Y16/Y4</f>
         <v>2.809447297297297</v>
       </c>
-      <c r="V6" s="21">
-        <f>+V16/V4</f>
+      <c r="Z6" s="21">
+        <f>+Z16/Z4</f>
         <v>3.276921917808219</v>
       </c>
-      <c r="W6" s="21">
-        <f>+W16/W4</f>
+      <c r="AA6" s="21">
+        <f>+AA16/AA4</f>
         <v>3.6708240917782025</v>
       </c>
     </row>
-    <row r="8" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:76" x14ac:dyDescent="0.2">
       <c r="A8" s="22"/>
       <c r="B8" s="2" t="s">
         <v>294</v>
@@ -2401,23 +2444,25 @@
         <v>1057.4480000000001</v>
       </c>
       <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
+      <c r="O8" s="3">
+        <v>899.94399999999996</v>
+      </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
-      <c r="V8" s="3">
-        <v>4027.5140000000001</v>
-      </c>
-      <c r="W8" s="3">
-        <v>4290.3950000000004</v>
-      </c>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
+      <c r="Z8" s="3">
+        <v>4027.5140000000001</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>4290.3950000000004</v>
+      </c>
       <c r="AB8" s="3"/>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
@@ -2463,8 +2508,12 @@
       <c r="BR8" s="3"/>
       <c r="BS8" s="3"/>
       <c r="BT8" s="3"/>
-    </row>
-    <row r="9" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU8" s="3"/>
+      <c r="BV8" s="3"/>
+      <c r="BW8" s="3"/>
+      <c r="BX8" s="3"/>
+    </row>
+    <row r="9" spans="1:76" x14ac:dyDescent="0.2">
       <c r="A9" s="22"/>
       <c r="B9" s="2" t="s">
         <v>295</v>
@@ -2499,23 +2548,25 @@
         <v>194.51</v>
       </c>
       <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
+      <c r="O9" s="3">
+        <v>167.37299999999999</v>
+      </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
-      <c r="V9" s="3">
-        <v>770.51900000000001</v>
-      </c>
-      <c r="W9" s="3">
-        <v>818.14</v>
-      </c>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
+      <c r="Z9" s="3">
+        <v>770.51900000000001</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>818.14</v>
+      </c>
       <c r="AB9" s="3"/>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
@@ -2561,8 +2612,12 @@
       <c r="BR9" s="3"/>
       <c r="BS9" s="3"/>
       <c r="BT9" s="3"/>
-    </row>
-    <row r="10" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU9" s="3"/>
+      <c r="BV9" s="3"/>
+      <c r="BW9" s="3"/>
+      <c r="BX9" s="3"/>
+    </row>
+    <row r="10" spans="1:76" x14ac:dyDescent="0.2">
       <c r="A10" s="22"/>
       <c r="B10" s="2" t="s">
         <v>296</v>
@@ -2597,23 +2652,25 @@
         <v>38.661000000000001</v>
       </c>
       <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
+      <c r="O10" s="3">
+        <v>46.503999999999998</v>
+      </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
-      <c r="V10" s="3">
-        <v>150.554</v>
-      </c>
-      <c r="W10" s="3">
-        <v>157.75700000000001</v>
-      </c>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-      <c r="AA10" s="3"/>
+      <c r="Z10" s="3">
+        <v>150.554</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>157.75700000000001</v>
+      </c>
       <c r="AB10" s="3"/>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
@@ -2659,8 +2716,12 @@
       <c r="BR10" s="3"/>
       <c r="BS10" s="3"/>
       <c r="BT10" s="3"/>
-    </row>
-    <row r="11" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU10" s="3"/>
+      <c r="BV10" s="3"/>
+      <c r="BW10" s="3"/>
+      <c r="BX10" s="3"/>
+    </row>
+    <row r="11" spans="1:76" x14ac:dyDescent="0.2">
       <c r="A11" s="23"/>
       <c r="B11" s="2" t="s">
         <v>42</v>
@@ -2699,35 +2760,37 @@
         <v>617.34500000000003</v>
       </c>
       <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3">
+      <c r="O11" s="3">
+        <v>564.71900000000005</v>
+      </c>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3">
         <v>1437.5709999999999</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="U11" s="3">
         <v>1464.559</v>
       </c>
-      <c r="R11" s="3">
+      <c r="V11" s="3">
         <v>1291.0350000000001</v>
       </c>
-      <c r="S11" s="3">
+      <c r="W11" s="3">
         <v>1564.789</v>
       </c>
-      <c r="T11" s="3">
+      <c r="X11" s="3">
         <v>1734.866</v>
       </c>
-      <c r="U11" s="3">
+      <c r="Y11" s="3">
         <v>2201.6860000000001</v>
       </c>
-      <c r="V11" s="3">
+      <c r="Z11" s="3">
         <v>2556.4340000000002</v>
       </c>
-      <c r="W11" s="3">
+      <c r="AA11" s="3">
         <v>2523.6619999999998</v>
       </c>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
@@ -2773,45 +2836,82 @@
       <c r="BR11" s="3"/>
       <c r="BS11" s="3"/>
       <c r="BT11" s="3"/>
-    </row>
-    <row r="12" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU11" s="3"/>
+      <c r="BV11" s="3"/>
+      <c r="BW11" s="3"/>
+      <c r="BX11" s="3"/>
+    </row>
+    <row r="12" spans="1:76" x14ac:dyDescent="0.2">
       <c r="A12" s="23"/>
       <c r="B12" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
+      <c r="C12" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="D12" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="E12" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="F12" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="G12" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="H12" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="I12" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="J12" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="K12" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="L12" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="M12" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="N12" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="O12" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="P12" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q12" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="R12" s="82" t="s">
+        <v>319</v>
+      </c>
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
-      <c r="U12" s="3">
-        <f>60%*U11</f>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3"/>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3">
+        <f>60%*Y11</f>
         <v>1321.0116</v>
       </c>
-      <c r="V12" s="3">
-        <f>+V11*60%</f>
+      <c r="Z12" s="3">
+        <f>+Z11*60%</f>
         <v>1533.8604</v>
       </c>
-      <c r="W12" s="3">
-        <f>+W11*60%</f>
+      <c r="AA12" s="3">
+        <f>+AA11*60%</f>
         <v>1514.1971999999998</v>
       </c>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-      <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
@@ -2857,45 +2957,82 @@
       <c r="BR12" s="3"/>
       <c r="BS12" s="3"/>
       <c r="BT12" s="3"/>
-    </row>
-    <row r="13" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU12" s="3"/>
+      <c r="BV12" s="3"/>
+      <c r="BW12" s="3"/>
+      <c r="BX12" s="3"/>
+    </row>
+    <row r="13" spans="1:76" x14ac:dyDescent="0.2">
       <c r="A13" s="23"/>
       <c r="B13" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
+      <c r="C13" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="D13" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="E13" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="F13" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="G13" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="H13" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="I13" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="J13" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="K13" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="L13" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="M13" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="N13" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="O13" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="P13" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q13" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="R13" s="82" t="s">
+        <v>319</v>
+      </c>
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
-      <c r="U13" s="3">
-        <f>40%*U11</f>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="3"/>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3">
+        <f>40%*Y11</f>
         <v>880.67440000000011</v>
       </c>
-      <c r="V13" s="3">
-        <f>+V11*40%</f>
+      <c r="Z13" s="3">
+        <f>+Z11*40%</f>
         <v>1022.5736000000002</v>
       </c>
-      <c r="W13" s="3">
-        <f>+W11*40%</f>
+      <c r="AA13" s="3">
+        <f>+AA11*40%</f>
         <v>1009.4648</v>
       </c>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
@@ -2941,8 +3078,12 @@
       <c r="BR13" s="3"/>
       <c r="BS13" s="3"/>
       <c r="BT13" s="3"/>
-    </row>
-    <row r="14" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU13" s="3"/>
+      <c r="BV13" s="3"/>
+      <c r="BW13" s="3"/>
+      <c r="BX13" s="3"/>
+    </row>
+    <row r="14" spans="1:76" x14ac:dyDescent="0.2">
       <c r="A14" s="23"/>
       <c r="B14" s="2" t="s">
         <v>43</v>
@@ -2981,35 +3122,37 @@
         <v>673.274</v>
       </c>
       <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3">
+      <c r="O14" s="3">
+        <v>549.10199999999998</v>
+      </c>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3">
         <v>2152.538</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="U14" s="3">
         <v>2158.5140000000001</v>
       </c>
-      <c r="R14" s="3">
+      <c r="V14" s="3">
         <v>1834.3489999999999</v>
       </c>
-      <c r="S14" s="3">
+      <c r="W14" s="3">
         <v>2147.9789999999998</v>
       </c>
-      <c r="T14" s="3">
+      <c r="X14" s="3">
         <v>1962.885</v>
       </c>
-      <c r="U14" s="3">
+      <c r="Y14" s="3">
         <v>2078.991</v>
       </c>
-      <c r="V14" s="3">
+      <c r="Z14" s="3">
         <v>2392.1529999999998</v>
       </c>
-      <c r="W14" s="3">
+      <c r="AA14" s="3">
         <v>2742.63</v>
       </c>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
@@ -3055,45 +3198,82 @@
       <c r="BR14" s="3"/>
       <c r="BS14" s="3"/>
       <c r="BT14" s="3"/>
-    </row>
-    <row r="15" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU14" s="3"/>
+      <c r="BV14" s="3"/>
+      <c r="BW14" s="3"/>
+      <c r="BX14" s="3"/>
+    </row>
+    <row r="15" spans="1:76" x14ac:dyDescent="0.2">
       <c r="A15" s="23"/>
       <c r="B15" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
+      <c r="C15" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="D15" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="E15" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="F15" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="G15" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="H15" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="I15" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="J15" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="K15" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="L15" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="M15" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="N15" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="O15" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="P15" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q15" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="R15" s="82" t="s">
+        <v>319</v>
+      </c>
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
-      <c r="U15" s="3">
-        <f>+U14*30%</f>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="3"/>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3">
+        <f>+Y14*30%</f>
         <v>623.69729999999993</v>
       </c>
-      <c r="V15" s="3">
-        <f>+V14*30%</f>
+      <c r="Z15" s="3">
+        <f>+Z14*30%</f>
         <v>717.64589999999987</v>
       </c>
-      <c r="W15" s="3">
-        <f>+W14*30%</f>
+      <c r="AA15" s="3">
+        <f>+AA14*30%</f>
         <v>822.78899999999999</v>
       </c>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
@@ -3139,45 +3319,82 @@
       <c r="BR15" s="3"/>
       <c r="BS15" s="3"/>
       <c r="BT15" s="3"/>
-    </row>
-    <row r="16" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU15" s="3"/>
+      <c r="BV15" s="3"/>
+      <c r="BW15" s="3"/>
+      <c r="BX15" s="3"/>
+    </row>
+    <row r="16" spans="1:76" x14ac:dyDescent="0.2">
       <c r="A16" s="23"/>
       <c r="B16" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
+      <c r="C16" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="D16" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="E16" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="F16" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="G16" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="H16" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="I16" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="J16" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="K16" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="L16" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="M16" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="N16" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="O16" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="P16" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q16" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="R16" s="82" t="s">
+        <v>319</v>
+      </c>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-      <c r="U16" s="3">
-        <f>+U14*70%</f>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3">
+        <f>+Y14*70%</f>
         <v>1455.2936999999999</v>
       </c>
-      <c r="V16" s="3">
-        <f>+V14*70%</f>
+      <c r="Z16" s="3">
+        <f>+Z14*70%</f>
         <v>1674.5070999999998</v>
       </c>
-      <c r="W16" s="3">
-        <f>+W14*70%</f>
+      <c r="AA16" s="3">
+        <f>+AA14*70%</f>
         <v>1919.8409999999999</v>
       </c>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
@@ -3223,8 +3440,12 @@
       <c r="BR16" s="3"/>
       <c r="BS16" s="3"/>
       <c r="BT16" s="3"/>
-    </row>
-    <row r="17" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU16" s="3"/>
+      <c r="BV16" s="3"/>
+      <c r="BW16" s="3"/>
+      <c r="BX16" s="3"/>
+    </row>
+    <row r="17" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
         <v>20</v>
       </c>
@@ -3268,41 +3489,43 @@
         <v>1290.6189999999999</v>
       </c>
       <c r="N17" s="24"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="24">
-        <f t="shared" ref="P17:T17" si="1">P11+P14</f>
+      <c r="O17" s="24">
+        <v>1113.8209999999999</v>
+      </c>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="24"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="24">
+        <f t="shared" ref="T17:X17" si="1">T11+T14</f>
         <v>3590.1089999999999</v>
       </c>
-      <c r="Q17" s="24">
+      <c r="U17" s="24">
         <f t="shared" si="1"/>
         <v>3623.0730000000003</v>
       </c>
-      <c r="R17" s="24">
+      <c r="V17" s="24">
         <f t="shared" si="1"/>
         <v>3125.384</v>
       </c>
-      <c r="S17" s="24">
+      <c r="W17" s="24">
         <f t="shared" si="1"/>
         <v>3712.768</v>
       </c>
-      <c r="T17" s="24">
+      <c r="X17" s="24">
         <f t="shared" si="1"/>
         <v>3697.7510000000002</v>
       </c>
-      <c r="U17" s="24">
-        <f>U11+U14</f>
+      <c r="Y17" s="24">
+        <f>Y11+Y14</f>
         <v>4280.6769999999997</v>
       </c>
-      <c r="V17" s="24">
+      <c r="Z17" s="24">
         <v>4948.5870000000004</v>
       </c>
-      <c r="W17" s="24">
+      <c r="AA17" s="24">
         <v>5266.2920000000004</v>
       </c>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
-      <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
@@ -3348,8 +3571,12 @@
       <c r="BR17" s="3"/>
       <c r="BS17" s="3"/>
       <c r="BT17" s="3"/>
-    </row>
-    <row r="18" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU17" s="3"/>
+      <c r="BV17" s="3"/>
+      <c r="BW17" s="3"/>
+      <c r="BX17" s="3"/>
+    </row>
+    <row r="18" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>21</v>
       </c>
@@ -3387,35 +3614,37 @@
         <v>483.67</v>
       </c>
       <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3">
+      <c r="O18" s="3">
+        <v>413.83800000000002</v>
+      </c>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3">
         <v>1430.193</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="U18" s="3">
         <v>1472.155</v>
       </c>
-      <c r="R18" s="3">
+      <c r="V18" s="3">
         <v>1234.1790000000001</v>
       </c>
-      <c r="S18" s="3">
+      <c r="W18" s="3">
         <v>1400.7729999999999</v>
       </c>
-      <c r="T18" s="3">
+      <c r="X18" s="3">
         <v>1593.213</v>
       </c>
-      <c r="U18" s="3">
+      <c r="Y18" s="3">
         <v>1587.2650000000001</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Z18" s="3">
         <v>1773.9259999999999</v>
       </c>
-      <c r="W18" s="3">
+      <c r="AA18" s="3">
         <v>2028.884</v>
       </c>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
-      <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
@@ -3461,8 +3690,12 @@
       <c r="BR18" s="3"/>
       <c r="BS18" s="3"/>
       <c r="BT18" s="3"/>
-    </row>
-    <row r="19" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU18" s="3"/>
+      <c r="BV18" s="3"/>
+      <c r="BW18" s="3"/>
+      <c r="BX18" s="3"/>
+    </row>
+    <row r="19" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>22</v>
       </c>
@@ -3487,7 +3720,7 @@
         <v>677.45699999999999</v>
       </c>
       <c r="H19" s="3">
-        <f t="shared" ref="H19:M19" si="3">H17-H18</f>
+        <f t="shared" ref="H19:O19" si="3">H17-H18</f>
         <v>736.26200000000017</v>
       </c>
       <c r="I19" s="3">
@@ -3511,43 +3744,46 @@
         <v>806.94899999999984</v>
       </c>
       <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3">
-        <f t="shared" ref="P19" si="4">P17-P18</f>
+      <c r="O19" s="3">
+        <f t="shared" si="3"/>
+        <v>699.98299999999995</v>
+      </c>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3">
+        <f t="shared" ref="T19" si="4">T17-T18</f>
         <v>2159.9160000000002</v>
       </c>
-      <c r="Q19" s="3">
-        <f t="shared" ref="Q19" si="5">Q17-Q18</f>
+      <c r="U19" s="3">
+        <f t="shared" ref="U19" si="5">U17-U18</f>
         <v>2150.9180000000006</v>
       </c>
-      <c r="R19" s="3">
-        <f t="shared" ref="R19" si="6">R17-R18</f>
+      <c r="V19" s="3">
+        <f t="shared" ref="V19" si="6">V17-V18</f>
         <v>1891.2049999999999</v>
       </c>
-      <c r="S19" s="3">
-        <f t="shared" ref="S19" si="7">S17-S18</f>
+      <c r="W19" s="3">
+        <f t="shared" ref="W19" si="7">W17-W18</f>
         <v>2311.9949999999999</v>
       </c>
-      <c r="T19" s="3">
-        <f t="shared" ref="T19" si="8">T17-T18</f>
+      <c r="X19" s="3">
+        <f t="shared" ref="X19" si="8">X17-X18</f>
         <v>2104.5380000000005</v>
       </c>
-      <c r="U19" s="3">
-        <f t="shared" ref="U19" si="9">U17-U18</f>
+      <c r="Y19" s="3">
+        <f t="shared" ref="Y19" si="9">Y17-Y18</f>
         <v>2693.4119999999994</v>
       </c>
-      <c r="V19" s="3">
-        <f t="shared" ref="V19:W19" si="10">V17-V18</f>
+      <c r="Z19" s="3">
+        <f t="shared" ref="Z19:AA19" si="10">Z17-Z18</f>
         <v>3174.6610000000005</v>
       </c>
-      <c r="W19" s="3">
+      <c r="AA19" s="3">
         <f t="shared" si="10"/>
         <v>3237.4080000000004</v>
       </c>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
@@ -3593,8 +3829,12 @@
       <c r="BR19" s="3"/>
       <c r="BS19" s="3"/>
       <c r="BT19" s="3"/>
-    </row>
-    <row r="20" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU19" s="3"/>
+      <c r="BV19" s="3"/>
+      <c r="BW19" s="3"/>
+      <c r="BX19" s="3"/>
+    </row>
+    <row r="20" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>23</v>
       </c>
@@ -3632,35 +3872,37 @@
         <v>459.548</v>
       </c>
       <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3">
+      <c r="O20" s="3">
+        <v>431.19499999999999</v>
+      </c>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3">
         <v>1536.2159999999999</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="U20" s="3">
         <v>1551.2429999999999</v>
       </c>
-      <c r="R20" s="3">
+      <c r="V20" s="3">
         <v>1391.5840000000001</v>
       </c>
-      <c r="S20" s="3">
+      <c r="W20" s="3">
         <v>1440.423</v>
       </c>
-      <c r="T20" s="3">
+      <c r="X20" s="3">
         <v>1496.962</v>
       </c>
-      <c r="U20" s="3">
+      <c r="Y20" s="3">
         <v>1571.7370000000001</v>
       </c>
-      <c r="V20" s="3">
+      <c r="Z20" s="3">
         <v>1689.9880000000001</v>
       </c>
-      <c r="W20" s="3">
+      <c r="AA20" s="3">
         <v>1809.633</v>
       </c>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
-      <c r="AA20" s="3"/>
       <c r="AB20" s="3"/>
       <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
@@ -3706,8 +3948,12 @@
       <c r="BR20" s="3"/>
       <c r="BS20" s="3"/>
       <c r="BT20" s="3"/>
-    </row>
-    <row r="21" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU20" s="3"/>
+      <c r="BV20" s="3"/>
+      <c r="BW20" s="3"/>
+      <c r="BX20" s="3"/>
+    </row>
+    <row r="21" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>24</v>
       </c>
@@ -3745,35 +3991,37 @@
         <v>193.40199999999999</v>
       </c>
       <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3">
+      <c r="O21" s="3">
+        <v>182.75399999999999</v>
+      </c>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3">
         <v>484.863</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="U21" s="3">
         <v>464.61500000000001</v>
       </c>
-      <c r="R21" s="3">
+      <c r="V21" s="3">
         <v>463.84300000000002</v>
       </c>
-      <c r="S21" s="3">
+      <c r="W21" s="3">
         <v>536.81500000000005</v>
       </c>
-      <c r="T21" s="3">
+      <c r="X21" s="3">
         <v>517.60199999999998</v>
       </c>
-      <c r="U21" s="3">
+      <c r="Y21" s="3">
         <v>642.87699999999995</v>
       </c>
-      <c r="V21" s="3">
+      <c r="Z21" s="3">
         <v>750.48500000000001</v>
       </c>
-      <c r="W21" s="3">
+      <c r="AA21" s="3">
         <v>725.471</v>
       </c>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="3"/>
-      <c r="AA21" s="3"/>
       <c r="AB21" s="3"/>
       <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
@@ -3819,8 +4067,12 @@
       <c r="BR21" s="3"/>
       <c r="BS21" s="3"/>
       <c r="BT21" s="3"/>
-    </row>
-    <row r="22" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU21" s="3"/>
+      <c r="BV21" s="3"/>
+      <c r="BW21" s="3"/>
+      <c r="BX21" s="3"/>
+    </row>
+    <row r="22" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>25</v>
       </c>
@@ -3858,38 +4110,40 @@
         <v>1.022</v>
       </c>
       <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3">
+      <c r="O22" s="3">
+        <v>2.7629999999999999</v>
+      </c>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3">
         <f>-5.806-11.58+5.915</f>
         <v>-11.471</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="U22" s="3">
         <f>-47.257-19.135+1.4</f>
         <v>-64.99199999999999</v>
       </c>
-      <c r="R22" s="3">
+      <c r="V22" s="3">
         <f>11.636-72.937+5.054</f>
         <v>-56.247</v>
       </c>
-      <c r="S22" s="3">
+      <c r="W22" s="3">
         <v>8.327</v>
       </c>
-      <c r="T22" s="3">
+      <c r="X22" s="3">
         <v>2.6739999999999999</v>
       </c>
-      <c r="U22" s="3">
+      <c r="Y22" s="3">
         <v>5.8730000000000002</v>
       </c>
-      <c r="V22" s="3">
+      <c r="Z22" s="3">
         <v>6.6319999999999997</v>
       </c>
-      <c r="W22" s="3">
+      <c r="AA22" s="3">
         <v>-3.161</v>
       </c>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="3"/>
-      <c r="AA22" s="3"/>
       <c r="AB22" s="3"/>
       <c r="AC22" s="3"/>
       <c r="AD22" s="3"/>
@@ -3935,8 +4189,12 @@
       <c r="BR22" s="3"/>
       <c r="BS22" s="3"/>
       <c r="BT22" s="3"/>
-    </row>
-    <row r="23" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU22" s="3"/>
+      <c r="BV22" s="3"/>
+      <c r="BW22" s="3"/>
+      <c r="BX22" s="3"/>
+    </row>
+    <row r="23" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>26</v>
       </c>
@@ -3961,7 +4219,7 @@
         <v>129.84900000000002</v>
       </c>
       <c r="H23" s="3">
-        <f t="shared" ref="H23:M23" si="12">H19-H20-H21+H22</f>
+        <f t="shared" ref="H23:O23" si="12">H19-H20-H21+H22</f>
         <v>175.62500000000017</v>
       </c>
       <c r="I23" s="3">
@@ -3984,44 +4242,50 @@
         <f t="shared" si="12"/>
         <v>155.02099999999984</v>
       </c>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3">
-        <f t="shared" ref="P23:T23" si="13">P19-SUM(P20:P21)+P22</f>
+      <c r="N23" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
+        <f t="shared" si="12"/>
+        <v>88.796999999999969</v>
+      </c>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3">
+        <f t="shared" ref="T23:X23" si="13">T19-SUM(T20:T21)+T22</f>
         <v>127.36600000000021</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="U23" s="3">
         <f t="shared" si="13"/>
         <v>70.068000000000637</v>
       </c>
-      <c r="R23" s="3">
+      <c r="V23" s="3">
         <f t="shared" si="13"/>
         <v>-20.469000000000207</v>
       </c>
-      <c r="S23" s="3">
+      <c r="W23" s="3">
         <f t="shared" si="13"/>
         <v>343.08399999999983</v>
       </c>
-      <c r="T23" s="3">
+      <c r="X23" s="3">
         <f t="shared" si="13"/>
         <v>92.648000000000621</v>
       </c>
-      <c r="U23" s="3">
-        <f>U19-SUM(U20:U21)+U22</f>
+      <c r="Y23" s="3">
+        <f>Y19-SUM(Y20:Y21)+Y22</f>
         <v>484.67099999999931</v>
       </c>
-      <c r="V23" s="3">
-        <f t="shared" ref="V23" si="14">V19-SUM(V20:V21)+V22</f>
+      <c r="Z23" s="3">
+        <f t="shared" ref="Z23" si="14">Z19-SUM(Z20:Z21)+Z22</f>
         <v>740.8200000000005</v>
       </c>
-      <c r="W23" s="3">
-        <f>W19-SUM(W20:W21)+W22</f>
+      <c r="AA23" s="3">
+        <f>AA19-SUM(AA20:AA21)+AA22</f>
         <v>699.14300000000014</v>
       </c>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="3"/>
-      <c r="AA23" s="3"/>
       <c r="AB23" s="3"/>
       <c r="AC23" s="3"/>
       <c r="AD23" s="3"/>
@@ -4067,8 +4331,12 @@
       <c r="BR23" s="3"/>
       <c r="BS23" s="3"/>
       <c r="BT23" s="3"/>
-    </row>
-    <row r="24" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU23" s="3"/>
+      <c r="BV23" s="3"/>
+      <c r="BW23" s="3"/>
+      <c r="BX23" s="3"/>
+    </row>
+    <row r="24" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>28</v>
       </c>
@@ -4106,35 +4374,37 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3">
+      <c r="O24" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3">
         <v>10.999000000000001</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="U24" s="3">
         <v>7.7370000000000001</v>
       </c>
-      <c r="R24" s="3">
+      <c r="V24" s="3">
         <v>28.274000000000001</v>
       </c>
-      <c r="S24" s="3">
+      <c r="W24" s="3">
         <v>37.957999999999998</v>
       </c>
-      <c r="T24" s="3">
+      <c r="X24" s="3">
         <v>30.236000000000001</v>
       </c>
-      <c r="U24" s="3">
+      <c r="Y24" s="3">
         <v>30.352</v>
       </c>
-      <c r="V24" s="3">
+      <c r="Z24" s="3">
         <v>12.077</v>
       </c>
-      <c r="W24" s="3">
+      <c r="AA24" s="3">
         <v>2.375</v>
       </c>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="3"/>
-      <c r="AA24" s="3"/>
       <c r="AB24" s="3"/>
       <c r="AC24" s="3"/>
       <c r="AD24" s="3"/>
@@ -4180,8 +4450,12 @@
       <c r="BR24" s="3"/>
       <c r="BS24" s="3"/>
       <c r="BT24" s="3"/>
-    </row>
-    <row r="25" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU24" s="3"/>
+      <c r="BV24" s="3"/>
+      <c r="BW24" s="3"/>
+      <c r="BX24" s="3"/>
+    </row>
+    <row r="25" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>27</v>
       </c>
@@ -4219,35 +4493,37 @@
         <v>6.4909999999999997</v>
       </c>
       <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3">
+      <c r="O25" s="3">
+        <v>5.7370000000000001</v>
+      </c>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3">
+      <c r="U25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3">
+      <c r="V25" s="3">
         <v>0</v>
       </c>
-      <c r="S25" s="3">
+      <c r="W25" s="3">
         <v>3.8479999999999999</v>
       </c>
-      <c r="T25" s="3">
+      <c r="X25" s="3">
         <v>4.6040000000000001</v>
       </c>
-      <c r="U25" s="3">
+      <c r="Y25" s="3">
         <v>29.98</v>
       </c>
-      <c r="V25" s="3">
+      <c r="Z25" s="3">
         <v>39.933999999999997</v>
       </c>
-      <c r="W25" s="3">
+      <c r="AA25" s="3">
         <v>24.004000000000001</v>
       </c>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="3"/>
-      <c r="AA25" s="3"/>
       <c r="AB25" s="3"/>
       <c r="AC25" s="3"/>
       <c r="AD25" s="3"/>
@@ -4293,8 +4569,12 @@
       <c r="BR25" s="3"/>
       <c r="BS25" s="3"/>
       <c r="BT25" s="3"/>
-    </row>
-    <row r="26" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU25" s="3"/>
+      <c r="BV25" s="3"/>
+      <c r="BW25" s="3"/>
+      <c r="BX25" s="3"/>
+    </row>
+    <row r="26" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>29</v>
       </c>
@@ -4319,7 +4599,7 @@
         <v>134.85200000000003</v>
       </c>
       <c r="H26" s="3">
-        <f t="shared" ref="H26:M26" si="16">H23-H24+H25</f>
+        <f t="shared" ref="H26:O26" si="16">H23-H24+H25</f>
         <v>180.82800000000017</v>
       </c>
       <c r="I26" s="3">
@@ -4342,44 +4622,50 @@
         <f t="shared" si="16"/>
         <v>160.96199999999982</v>
       </c>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3">
-        <f t="shared" ref="P26:S26" si="17">P23-P24+P25</f>
+      <c r="N26" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
+        <f t="shared" si="16"/>
+        <v>94.083999999999961</v>
+      </c>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3">
+        <f t="shared" ref="T26:W26" si="17">T23-T24+T25</f>
         <v>116.36700000000022</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="U26" s="3">
         <f t="shared" si="17"/>
         <v>62.331000000000635</v>
       </c>
-      <c r="R26" s="3">
+      <c r="V26" s="3">
         <f t="shared" si="17"/>
         <v>-48.743000000000208</v>
       </c>
-      <c r="S26" s="3">
+      <c r="W26" s="3">
         <f t="shared" si="17"/>
         <v>308.97399999999988</v>
       </c>
-      <c r="T26" s="3">
-        <f>T23-T24+T25</f>
+      <c r="X26" s="3">
+        <f>X23-X24+X25</f>
         <v>67.016000000000616</v>
       </c>
-      <c r="U26" s="3">
-        <f>U23-U24+U25</f>
+      <c r="Y26" s="3">
+        <f>Y23-Y24+Y25</f>
         <v>484.29899999999935</v>
       </c>
-      <c r="V26" s="3">
-        <f t="shared" ref="V26:W26" si="18">V23-V24+V25</f>
+      <c r="Z26" s="3">
+        <f t="shared" ref="Z26:AA26" si="18">Z23-Z24+Z25</f>
         <v>768.67700000000048</v>
       </c>
-      <c r="W26" s="3">
+      <c r="AA26" s="3">
         <f t="shared" si="18"/>
         <v>720.77200000000016</v>
       </c>
-      <c r="X26" s="3"/>
-      <c r="Y26" s="3"/>
-      <c r="Z26" s="3"/>
-      <c r="AA26" s="3"/>
       <c r="AB26" s="3"/>
       <c r="AC26" s="3"/>
       <c r="AD26" s="3"/>
@@ -4425,8 +4711,12 @@
       <c r="BR26" s="3"/>
       <c r="BS26" s="3"/>
       <c r="BT26" s="3"/>
-    </row>
-    <row r="27" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU26" s="3"/>
+      <c r="BV26" s="3"/>
+      <c r="BW26" s="3"/>
+      <c r="BX26" s="3"/>
+    </row>
+    <row r="27" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
@@ -4464,35 +4754,37 @@
         <v>45.862000000000002</v>
       </c>
       <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3">
+      <c r="O27" s="3">
+        <v>25.965</v>
+      </c>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3">
         <v>37.558999999999997</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="U27" s="3">
         <v>17.370999999999999</v>
       </c>
-      <c r="R27" s="3">
+      <c r="V27" s="3">
         <v>60.210999999999999</v>
       </c>
-      <c r="S27" s="3">
+      <c r="W27" s="3">
         <v>38.908000000000001</v>
       </c>
-      <c r="T27" s="3">
+      <c r="X27" s="3">
         <v>56.631</v>
       </c>
-      <c r="U27" s="3">
+      <c r="Y27" s="3">
         <v>148.886</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Z27" s="3">
         <v>194.661</v>
       </c>
-      <c r="W27" s="3">
+      <c r="AA27" s="3">
         <v>205.77699999999999</v>
       </c>
-      <c r="X27" s="3"/>
-      <c r="Y27" s="3"/>
-      <c r="Z27" s="3"/>
-      <c r="AA27" s="3"/>
       <c r="AB27" s="3"/>
       <c r="AC27" s="3"/>
       <c r="AD27" s="3"/>
@@ -4538,8 +4830,12 @@
       <c r="BR27" s="3"/>
       <c r="BS27" s="3"/>
       <c r="BT27" s="3"/>
-    </row>
-    <row r="28" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU27" s="3"/>
+      <c r="BV27" s="3"/>
+      <c r="BW27" s="3"/>
+      <c r="BX27" s="3"/>
+    </row>
+    <row r="28" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>31</v>
       </c>
@@ -4564,7 +4860,7 @@
         <v>115.05800000000004</v>
       </c>
       <c r="H28" s="3">
-        <f t="shared" ref="H28:M28" si="20">H26-H27</f>
+        <f t="shared" ref="H28:O28" si="20">H26-H27</f>
         <v>135.37900000000019</v>
       </c>
       <c r="I28" s="3">
@@ -4587,44 +4883,50 @@
         <f t="shared" si="20"/>
         <v>115.09999999999982</v>
       </c>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3">
-        <f t="shared" ref="P28:W28" si="21">P26-P27</f>
+      <c r="N28" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <f t="shared" si="20"/>
+        <v>68.118999999999957</v>
+      </c>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3">
+        <f t="shared" ref="T28:AA28" si="21">T26-T27</f>
         <v>78.80800000000022</v>
       </c>
-      <c r="Q28" s="3">
+      <c r="U28" s="3">
         <f t="shared" si="21"/>
         <v>44.960000000000633</v>
       </c>
-      <c r="R28" s="3">
+      <c r="V28" s="3">
         <f t="shared" si="21"/>
         <v>-108.95400000000021</v>
       </c>
-      <c r="S28" s="3">
+      <c r="W28" s="3">
         <f t="shared" si="21"/>
         <v>270.06599999999986</v>
       </c>
-      <c r="T28" s="3">
+      <c r="X28" s="3">
         <f t="shared" si="21"/>
         <v>10.385000000000616</v>
       </c>
-      <c r="U28" s="3">
+      <c r="Y28" s="3">
         <f t="shared" si="21"/>
         <v>335.41299999999933</v>
       </c>
-      <c r="V28" s="3">
+      <c r="Z28" s="3">
         <f t="shared" si="21"/>
         <v>574.01600000000053</v>
       </c>
-      <c r="W28" s="3">
+      <c r="AA28" s="3">
         <f t="shared" si="21"/>
         <v>514.99500000000012</v>
       </c>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="3"/>
-      <c r="AA28" s="3"/>
       <c r="AB28" s="3"/>
       <c r="AC28" s="3"/>
       <c r="AD28" s="3"/>
@@ -4670,8 +4972,12 @@
       <c r="BR28" s="3"/>
       <c r="BS28" s="3"/>
       <c r="BT28" s="3"/>
-    </row>
-    <row r="29" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU28" s="3"/>
+      <c r="BV28" s="3"/>
+      <c r="BW28" s="3"/>
+      <c r="BX28" s="3"/>
+    </row>
+    <row r="29" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>32</v>
       </c>
@@ -4709,35 +5015,37 @@
         <v>2.105</v>
       </c>
       <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="3">
+      <c r="O29" s="3">
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3">
         <v>4.2670000000000003</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="U29" s="3">
         <v>5.6020000000000003</v>
       </c>
-      <c r="R29" s="3">
+      <c r="V29" s="3">
         <v>5.0670000000000002</v>
       </c>
-      <c r="S29" s="3">
+      <c r="W29" s="3">
         <v>7.056</v>
       </c>
-      <c r="T29" s="3">
+      <c r="X29" s="3">
         <v>7.569</v>
       </c>
-      <c r="U29" s="3">
+      <c r="Y29" s="3">
         <v>7.29</v>
       </c>
-      <c r="V29" s="3">
+      <c r="Z29" s="3">
         <v>7.7930000000000001</v>
       </c>
-      <c r="W29" s="3">
+      <c r="AA29" s="3">
         <v>8.0739999999999998</v>
       </c>
-      <c r="X29" s="3"/>
-      <c r="Y29" s="3"/>
-      <c r="Z29" s="3"/>
-      <c r="AA29" s="3"/>
       <c r="AB29" s="3"/>
       <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
@@ -4783,8 +5091,12 @@
       <c r="BR29" s="3"/>
       <c r="BS29" s="3"/>
       <c r="BT29" s="3"/>
-    </row>
-    <row r="30" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU29" s="3"/>
+      <c r="BV29" s="3"/>
+      <c r="BW29" s="3"/>
+      <c r="BX29" s="3"/>
+    </row>
+    <row r="30" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>33</v>
       </c>
@@ -4809,7 +5121,7 @@
         <v>113.83000000000004</v>
       </c>
       <c r="H30" s="3">
-        <f t="shared" ref="H30:M30" si="23">H28-H29</f>
+        <f t="shared" ref="H30:O30" si="23">H28-H29</f>
         <v>133.16800000000018</v>
       </c>
       <c r="I30" s="3">
@@ -4832,44 +5144,50 @@
         <f t="shared" si="23"/>
         <v>112.99499999999982</v>
       </c>
-      <c r="N30" s="3"/>
-      <c r="O30" s="3"/>
-      <c r="P30" s="3">
-        <f t="shared" ref="P30:S30" si="24">P28-P29</f>
+      <c r="N30" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <f t="shared" si="23"/>
+        <v>67.133999999999958</v>
+      </c>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3">
+        <f t="shared" ref="T30:W30" si="24">T28-T29</f>
         <v>74.541000000000224</v>
       </c>
-      <c r="Q30" s="3">
+      <c r="U30" s="3">
         <f t="shared" si="24"/>
         <v>39.358000000000629</v>
       </c>
-      <c r="R30" s="3">
+      <c r="V30" s="3">
         <f t="shared" si="24"/>
         <v>-114.02100000000021</v>
       </c>
-      <c r="S30" s="3">
+      <c r="W30" s="3">
         <f t="shared" si="24"/>
         <v>263.00999999999988</v>
       </c>
-      <c r="T30" s="3">
-        <f>T28-T29</f>
+      <c r="X30" s="3">
+        <f>X28-X29</f>
         <v>2.8160000000006162</v>
       </c>
-      <c r="U30" s="3">
-        <f>U28-U29</f>
+      <c r="Y30" s="3">
+        <f>Y28-Y29</f>
         <v>328.12299999999931</v>
       </c>
-      <c r="V30" s="3">
-        <f>V28-V29</f>
+      <c r="Z30" s="3">
+        <f>Z28-Z29</f>
         <v>566.22300000000052</v>
       </c>
-      <c r="W30" s="3">
-        <f>W28-W29</f>
+      <c r="AA30" s="3">
+        <f>AA28-AA29</f>
         <v>506.92100000000011</v>
       </c>
-      <c r="X30" s="3"/>
-      <c r="Y30" s="3"/>
-      <c r="Z30" s="3"/>
-      <c r="AA30" s="3"/>
       <c r="AB30" s="3"/>
       <c r="AC30" s="3"/>
       <c r="AD30" s="3"/>
@@ -4915,8 +5233,12 @@
       <c r="BR30" s="3"/>
       <c r="BS30" s="3"/>
       <c r="BT30" s="3"/>
-    </row>
-    <row r="31" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU30" s="3"/>
+      <c r="BV30" s="3"/>
+      <c r="BW30" s="3"/>
+      <c r="BX30" s="3"/>
+    </row>
+    <row r="31" spans="2:76" x14ac:dyDescent="0.2">
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -4987,13 +5309,17 @@
       <c r="BR31" s="3"/>
       <c r="BS31" s="3"/>
       <c r="BT31" s="3"/>
-    </row>
-    <row r="32" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU31" s="3"/>
+      <c r="BV31" s="3"/>
+      <c r="BW31" s="3"/>
+      <c r="BX31" s="3"/>
+    </row>
+    <row r="32" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C32" s="25">
-        <f t="shared" ref="C32:M32" si="25">C30/C33</f>
+        <f t="shared" ref="C32:P32" si="25">C30/C33</f>
         <v>0.33426796304514361</v>
       </c>
       <c r="D32" s="25">
@@ -5036,44 +5362,53 @@
         <f t="shared" si="25"/>
         <v>2.4122582297937711</v>
       </c>
-      <c r="N32" s="25"/>
-      <c r="O32" s="3"/>
-      <c r="P32" s="25">
-        <f t="shared" ref="P32:W32" si="26">P30/P33</f>
+      <c r="N32" s="25" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O32" s="25">
+        <f t="shared" si="25"/>
+        <v>1.4928951055171331</v>
+      </c>
+      <c r="P32" s="25" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q32" s="25"/>
+      <c r="R32" s="25"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="25">
+        <f t="shared" ref="T32:AA32" si="26">T30/T33</f>
         <v>1.1067706013363063</v>
       </c>
-      <c r="Q32" s="25">
+      <c r="U32" s="25">
         <f t="shared" si="26"/>
         <v>0.61088346681567995</v>
       </c>
-      <c r="R32" s="25">
+      <c r="V32" s="25">
         <f t="shared" si="26"/>
         <v>-1.8228485555786511</v>
       </c>
-      <c r="S32" s="25">
+      <c r="W32" s="25">
         <f t="shared" si="26"/>
         <v>4.4131416010873012</v>
       </c>
-      <c r="T32" s="25">
+      <c r="X32" s="25">
         <f t="shared" si="26"/>
         <v>5.5976305484338483E-2</v>
       </c>
-      <c r="U32" s="25">
+      <c r="Y32" s="25">
         <f t="shared" si="26"/>
         <v>6.5298109452736179</v>
       </c>
-      <c r="V32" s="25">
+      <c r="Z32" s="25">
         <f t="shared" si="26"/>
         <v>11.137571549401061</v>
       </c>
-      <c r="W32" s="25">
+      <c r="AA32" s="25">
         <f t="shared" si="26"/>
         <v>10.712842621357174</v>
       </c>
-      <c r="X32" s="3"/>
-      <c r="Y32" s="3"/>
-      <c r="Z32" s="3"/>
-      <c r="AA32" s="3"/>
       <c r="AB32" s="3"/>
       <c r="AC32" s="3"/>
       <c r="AD32" s="3"/>
@@ -5119,8 +5454,12 @@
       <c r="BR32" s="3"/>
       <c r="BS32" s="3"/>
       <c r="BT32" s="3"/>
-    </row>
-    <row r="33" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU32" s="3"/>
+      <c r="BV32" s="3"/>
+      <c r="BW32" s="3"/>
+      <c r="BX32" s="3"/>
+    </row>
+    <row r="33" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
         <v>34</v>
       </c>
@@ -5158,35 +5497,37 @@
         <v>46.841999999999999</v>
       </c>
       <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
-      <c r="P33" s="3">
+      <c r="O33" s="3">
+        <v>44.969000000000001</v>
+      </c>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3"/>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3">
         <v>67.349999999999994</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="U33" s="3">
         <v>64.427999999999997</v>
       </c>
-      <c r="R33" s="3">
+      <c r="V33" s="3">
         <v>62.551000000000002</v>
       </c>
-      <c r="S33" s="3">
+      <c r="W33" s="3">
         <v>59.597000000000001</v>
       </c>
-      <c r="T33" s="3">
+      <c r="X33" s="3">
         <v>50.307000000000002</v>
       </c>
-      <c r="U33" s="3">
+      <c r="Y33" s="3">
         <v>50.25</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Z33" s="3">
         <v>50.838999999999999</v>
       </c>
-      <c r="W33" s="3">
+      <c r="AA33" s="3">
         <v>47.319000000000003</v>
       </c>
-      <c r="X33" s="3"/>
-      <c r="Y33" s="3"/>
-      <c r="Z33" s="3"/>
-      <c r="AA33" s="3"/>
       <c r="AB33" s="3"/>
       <c r="AC33" s="3"/>
       <c r="AD33" s="3"/>
@@ -5232,8 +5573,12 @@
       <c r="BR33" s="3"/>
       <c r="BS33" s="3"/>
       <c r="BT33" s="3"/>
-    </row>
-    <row r="34" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU33" s="3"/>
+      <c r="BV33" s="3"/>
+      <c r="BW33" s="3"/>
+      <c r="BX33" s="3"/>
+    </row>
+    <row r="34" spans="2:76" x14ac:dyDescent="0.2">
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -5304,8 +5649,12 @@
       <c r="BR34" s="3"/>
       <c r="BS34" s="3"/>
       <c r="BT34" s="3"/>
-    </row>
-    <row r="35" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU34" s="3"/>
+      <c r="BV34" s="3"/>
+      <c r="BW34" s="3"/>
+      <c r="BX34" s="3"/>
+    </row>
+    <row r="35" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>44</v>
       </c>
@@ -5323,38 +5672,38 @@
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
-      <c r="Q35" s="26">
-        <f t="shared" ref="Q35:W35" si="27">Q3/P3-1</f>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="3"/>
+      <c r="S35" s="3"/>
+      <c r="T35" s="3"/>
+      <c r="U35" s="26">
+        <f t="shared" ref="U35:AA35" si="27">U3/T3-1</f>
         <v>-3.4482758620689613E-2</v>
       </c>
-      <c r="R35" s="26">
+      <c r="V35" s="26">
         <f t="shared" si="27"/>
         <v>-0.22727272727272729</v>
       </c>
-      <c r="S35" s="26">
+      <c r="W35" s="26">
         <f t="shared" si="27"/>
         <v>-5.8823529411764719E-2</v>
       </c>
-      <c r="T35" s="26">
+      <c r="X35" s="26">
         <f t="shared" si="27"/>
         <v>4.0178571428571397E-2</v>
       </c>
-      <c r="U35" s="26">
+      <c r="Y35" s="26">
         <f t="shared" si="27"/>
         <v>6.0085836909871349E-2</v>
       </c>
-      <c r="V35" s="26">
+      <c r="Z35" s="26">
         <f t="shared" si="27"/>
         <v>0.12550607287449389</v>
       </c>
-      <c r="W35" s="26">
+      <c r="AA35" s="26">
         <f t="shared" si="27"/>
         <v>0.10071942446043169</v>
       </c>
-      <c r="X35" s="3"/>
-      <c r="Y35" s="3"/>
-      <c r="Z35" s="3"/>
-      <c r="AA35" s="3"/>
       <c r="AB35" s="3"/>
       <c r="AC35" s="3"/>
       <c r="AD35" s="3"/>
@@ -5400,8 +5749,12 @@
       <c r="BR35" s="3"/>
       <c r="BS35" s="3"/>
       <c r="BT35" s="3"/>
-    </row>
-    <row r="36" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU35" s="3"/>
+      <c r="BV35" s="3"/>
+      <c r="BW35" s="3"/>
+      <c r="BX35" s="3"/>
+    </row>
+    <row r="36" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
         <v>45</v>
       </c>
@@ -5419,38 +5772,38 @@
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
-      <c r="Q36" s="26">
-        <f>Q4/P4-1</f>
-        <v>7.3800738007379074E-3</v>
-      </c>
-      <c r="R36" s="26">
-        <f>R4/Q4-1</f>
-        <v>-8.9743589743589758E-2</v>
-      </c>
-      <c r="S36" s="26">
-        <f>S4/R4-1</f>
-        <v>1.6096579476861272E-2</v>
-      </c>
-      <c r="T36" s="26">
-        <f>T4/S4-1</f>
-        <v>4.7524752475247567E-2</v>
-      </c>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3"/>
+      <c r="S36" s="3"/>
+      <c r="T36" s="3"/>
       <c r="U36" s="26">
         <f>U4/T4-1</f>
+        <v>7.3800738007379074E-3</v>
+      </c>
+      <c r="V36" s="26">
+        <f>V4/U4-1</f>
+        <v>-8.9743589743589758E-2</v>
+      </c>
+      <c r="W36" s="26">
+        <f>W4/V4-1</f>
+        <v>1.6096579476861272E-2</v>
+      </c>
+      <c r="X36" s="26">
+        <f>X4/W4-1</f>
+        <v>4.7524752475247567E-2</v>
+      </c>
+      <c r="Y36" s="26">
+        <f>Y4/X4-1</f>
         <v>-2.0793950850661602E-2</v>
       </c>
-      <c r="V36" s="26">
-        <f>+V14/U14-1</f>
+      <c r="Z36" s="26">
+        <f>+Z14/Y14-1</f>
         <v>0.15063172471646102</v>
       </c>
-      <c r="W36" s="26">
-        <f>+W14/V14-1</f>
+      <c r="AA36" s="26">
+        <f>+AA14/Z14-1</f>
         <v>0.1465111136286017</v>
       </c>
-      <c r="X36" s="3"/>
-      <c r="Y36" s="3"/>
-      <c r="Z36" s="3"/>
-      <c r="AA36" s="3"/>
       <c r="AB36" s="3"/>
       <c r="AC36" s="3"/>
       <c r="AD36" s="3"/>
@@ -5496,8 +5849,12 @@
       <c r="BR36" s="3"/>
       <c r="BS36" s="3"/>
       <c r="BT36" s="3"/>
-    </row>
-    <row r="37" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU36" s="3"/>
+      <c r="BV36" s="3"/>
+      <c r="BW36" s="3"/>
+      <c r="BX36" s="3"/>
+    </row>
+    <row r="37" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
         <v>299</v>
       </c>
@@ -5525,43 +5882,61 @@
         <f>+K11/G11-1</f>
         <v>-4.1234407616274726E-2</v>
       </c>
-      <c r="L37" s="26"/>
-      <c r="M37" s="26"/>
-      <c r="N37" s="26"/>
-      <c r="O37" s="3"/>
-      <c r="P37" s="26"/>
+      <c r="L37" s="26">
+        <f t="shared" ref="L37:Q37" si="29">+L11/H11-1</f>
+        <v>-5.2450482129612008E-2</v>
+      </c>
+      <c r="M37" s="26">
+        <f t="shared" si="29"/>
+        <v>-1.983059055149361E-2</v>
+      </c>
+      <c r="N37" s="26">
+        <f t="shared" si="29"/>
+        <v>-1</v>
+      </c>
+      <c r="O37" s="26">
+        <f t="shared" si="29"/>
+        <v>3.0608799756180805E-2</v>
+      </c>
+      <c r="P37" s="26">
+        <f t="shared" si="29"/>
+        <v>-1</v>
+      </c>
       <c r="Q37" s="26">
-        <f t="shared" ref="Q37:U37" si="29">+Q11/P11-1</f>
+        <f t="shared" si="29"/>
+        <v>-1</v>
+      </c>
+      <c r="R37" s="26"/>
+      <c r="S37" s="3"/>
+      <c r="T37" s="26"/>
+      <c r="U37" s="26">
+        <f t="shared" ref="U37:Y37" si="30">+U11/T11-1</f>
         <v>1.877333363013034E-2</v>
       </c>
-      <c r="R37" s="26">
-        <f t="shared" si="29"/>
+      <c r="V37" s="26">
+        <f t="shared" si="30"/>
         <v>-0.11848208231966062</v>
       </c>
-      <c r="S37" s="26">
-        <f t="shared" si="29"/>
+      <c r="W37" s="26">
+        <f t="shared" si="30"/>
         <v>0.21204227615827609</v>
       </c>
-      <c r="T37" s="26">
-        <f t="shared" si="29"/>
+      <c r="X37" s="26">
+        <f t="shared" si="30"/>
         <v>0.1086900534193429</v>
       </c>
-      <c r="U37" s="26">
-        <f t="shared" si="29"/>
+      <c r="Y37" s="26">
+        <f t="shared" si="30"/>
         <v>0.26908130080363568</v>
       </c>
-      <c r="V37" s="26">
-        <f>+V11/U11-1</f>
+      <c r="Z37" s="26">
+        <f>+Z11/Y11-1</f>
         <v>0.16112561010062287</v>
       </c>
-      <c r="W37" s="26">
-        <f>+W11/V11-1</f>
+      <c r="AA37" s="26">
+        <f>+AA11/Z11-1</f>
         <v>-1.2819419550827549E-2</v>
       </c>
-      <c r="X37" s="3"/>
-      <c r="Y37" s="3"/>
-      <c r="Z37" s="3"/>
-      <c r="AA37" s="3"/>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
       <c r="AD37" s="3"/>
@@ -5607,8 +5982,12 @@
       <c r="BR37" s="3"/>
       <c r="BS37" s="3"/>
       <c r="BT37" s="3"/>
-    </row>
-    <row r="38" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU37" s="3"/>
+      <c r="BV37" s="3"/>
+      <c r="BW37" s="3"/>
+      <c r="BX37" s="3"/>
+    </row>
+    <row r="38" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
         <v>300</v>
       </c>
@@ -5617,15 +5996,15 @@
       <c r="E38" s="26"/>
       <c r="F38" s="26"/>
       <c r="G38" s="26">
-        <f t="shared" ref="G38:I38" si="30">+G14/C14-1</f>
+        <f t="shared" ref="G38:I38" si="31">+G14/C14-1</f>
         <v>0.12318289786223269</v>
       </c>
       <c r="H38" s="26">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.16698756331537723</v>
       </c>
       <c r="I38" s="26">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.13844620534968333</v>
       </c>
       <c r="J38" s="26">
@@ -5636,43 +6015,61 @@
         <f>+K14/G14-1</f>
         <v>0.22293679891900808</v>
       </c>
-      <c r="L38" s="26"/>
-      <c r="M38" s="26"/>
-      <c r="N38" s="26"/>
-      <c r="O38" s="3"/>
-      <c r="P38" s="26"/>
+      <c r="L38" s="26">
+        <f t="shared" ref="L38:Q38" si="32">+L14/H14-1</f>
+        <v>0.1906127732713514</v>
+      </c>
+      <c r="M38" s="26">
+        <f t="shared" si="32"/>
+        <v>0.16255907558048177</v>
+      </c>
+      <c r="N38" s="26">
+        <f t="shared" si="32"/>
+        <v>-1</v>
+      </c>
+      <c r="O38" s="26">
+        <f t="shared" si="32"/>
+        <v>-4.7691512367042943E-4</v>
+      </c>
+      <c r="P38" s="26">
+        <f t="shared" si="32"/>
+        <v>-1</v>
+      </c>
       <c r="Q38" s="26">
-        <f t="shared" ref="Q38:U38" si="31">+Q14/P14-1</f>
+        <f t="shared" si="32"/>
+        <v>-1</v>
+      </c>
+      <c r="R38" s="26"/>
+      <c r="S38" s="3"/>
+      <c r="T38" s="26"/>
+      <c r="U38" s="26">
+        <f t="shared" ref="U38:Y38" si="33">+U14/T14-1</f>
         <v>2.7762576084604529E-3</v>
       </c>
-      <c r="R38" s="26">
-        <f t="shared" si="31"/>
+      <c r="V38" s="26">
+        <f t="shared" si="33"/>
         <v>-0.15017970696506955</v>
       </c>
-      <c r="S38" s="26">
-        <f t="shared" si="31"/>
+      <c r="W38" s="26">
+        <f t="shared" si="33"/>
         <v>0.17097618828260042</v>
       </c>
-      <c r="T38" s="26">
-        <f t="shared" si="31"/>
+      <c r="X38" s="26">
+        <f t="shared" si="33"/>
         <v>-8.6171233517645995E-2</v>
       </c>
-      <c r="U38" s="26">
-        <f t="shared" si="31"/>
+      <c r="Y38" s="26">
+        <f t="shared" si="33"/>
         <v>5.9150688909436866E-2</v>
       </c>
-      <c r="V38" s="26">
-        <f>+V14/U14-1</f>
+      <c r="Z38" s="26">
+        <f>+Z14/Y14-1</f>
         <v>0.15063172471646102</v>
       </c>
-      <c r="W38" s="26">
-        <f>+W14/V14-1</f>
+      <c r="AA38" s="26">
+        <f>+AA14/Z14-1</f>
         <v>0.1465111136286017</v>
       </c>
-      <c r="X38" s="3"/>
-      <c r="Y38" s="3"/>
-      <c r="Z38" s="3"/>
-      <c r="AA38" s="3"/>
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
       <c r="AD38" s="3"/>
@@ -5718,8 +6115,12 @@
       <c r="BR38" s="3"/>
       <c r="BS38" s="3"/>
       <c r="BT38" s="3"/>
-    </row>
-    <row r="39" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU38" s="3"/>
+      <c r="BV38" s="3"/>
+      <c r="BW38" s="3"/>
+      <c r="BX38" s="3"/>
+    </row>
+    <row r="39" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
         <v>301</v>
       </c>
@@ -5747,43 +6148,61 @@
         <f>K17/G17-1</f>
         <v>7.5025716888893257E-2</v>
       </c>
-      <c r="L39" s="27"/>
-      <c r="M39" s="27"/>
-      <c r="N39" s="27"/>
-      <c r="O39" s="24"/>
-      <c r="P39" s="27"/>
+      <c r="L39" s="27">
+        <f t="shared" ref="L39:Q39" si="34">L17/H17-1</f>
+        <v>6.5773994818223214E-2</v>
+      </c>
+      <c r="M39" s="27">
+        <f t="shared" si="34"/>
+        <v>6.753953378341504E-2</v>
+      </c>
+      <c r="N39" s="27">
+        <f t="shared" si="34"/>
+        <v>-1</v>
+      </c>
+      <c r="O39" s="27">
+        <f t="shared" si="34"/>
+        <v>1.5045871225204177E-2</v>
+      </c>
+      <c r="P39" s="27">
+        <f t="shared" si="34"/>
+        <v>-1</v>
+      </c>
       <c r="Q39" s="27">
-        <f t="shared" ref="Q39:T39" si="32">Q17/P17-1</f>
+        <f t="shared" si="34"/>
+        <v>-1</v>
+      </c>
+      <c r="R39" s="27"/>
+      <c r="S39" s="24"/>
+      <c r="T39" s="27"/>
+      <c r="U39" s="27">
+        <f t="shared" ref="U39:X39" si="35">U17/T17-1</f>
         <v>9.1818939202126248E-3</v>
       </c>
-      <c r="R39" s="27">
-        <f t="shared" si="32"/>
+      <c r="V39" s="27">
+        <f t="shared" si="35"/>
         <v>-0.137366539399013</v>
       </c>
-      <c r="S39" s="27">
-        <f t="shared" si="32"/>
+      <c r="W39" s="27">
+        <f t="shared" si="35"/>
         <v>0.18793978595910144</v>
       </c>
-      <c r="T39" s="27">
-        <f t="shared" si="32"/>
+      <c r="X39" s="27">
+        <f t="shared" si="35"/>
         <v>-4.0446911845825051E-3</v>
       </c>
-      <c r="U39" s="27">
-        <f>U17/T17-1</f>
+      <c r="Y39" s="27">
+        <f>Y17/X17-1</f>
         <v>0.15764338918439869</v>
       </c>
-      <c r="V39" s="27">
-        <f>V17/U17-1</f>
+      <c r="Z39" s="27">
+        <f>Z17/Y17-1</f>
         <v>0.15602905802049549</v>
       </c>
-      <c r="W39" s="27">
-        <f>W17/V17-1</f>
+      <c r="AA39" s="27">
+        <f>AA17/Z17-1</f>
         <v>6.4201154794287785E-2</v>
       </c>
-      <c r="X39" s="3"/>
-      <c r="Y39" s="3"/>
-      <c r="Z39" s="3"/>
-      <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
@@ -5829,87 +6248,109 @@
       <c r="BR39" s="3"/>
       <c r="BS39" s="3"/>
       <c r="BT39" s="3"/>
-    </row>
-    <row r="40" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU39" s="3"/>
+      <c r="BV39" s="3"/>
+      <c r="BW39" s="3"/>
+      <c r="BX39" s="3"/>
+    </row>
+    <row r="40" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C40" s="26">
-        <f t="shared" ref="C40:J40" si="33">C19/C17</f>
+        <f t="shared" ref="C40:J40" si="36">C19/C17</f>
         <v>0.60980581200343542</v>
       </c>
       <c r="D40" s="26">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.6247748157097115</v>
       </c>
       <c r="E40" s="26">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.6490428622408847</v>
       </c>
       <c r="F40" s="26">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.62878697673010042</v>
       </c>
       <c r="G40" s="26">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.66369852948380081</v>
       </c>
       <c r="H40" s="26">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.64927590932419976</v>
       </c>
       <c r="I40" s="26">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.65091325976082037</v>
       </c>
       <c r="J40" s="26">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.61454953161585113</v>
       </c>
       <c r="K40" s="26">
-        <f t="shared" ref="K40" si="34">K19/K17</f>
+        <f t="shared" ref="K40:Q40" si="37">K19/K17</f>
         <v>0.61985890964366519</v>
       </c>
-      <c r="L40" s="26"/>
-      <c r="M40" s="26"/>
-      <c r="N40" s="26"/>
-      <c r="O40" s="3"/>
-      <c r="P40" s="26">
-        <f t="shared" ref="P40:V40" si="35">P19/P17</f>
+      <c r="L40" s="26">
+        <f t="shared" si="37"/>
+        <v>0.62634043820745355</v>
+      </c>
+      <c r="M40" s="26">
+        <f t="shared" si="37"/>
+        <v>0.62524184131800309</v>
+      </c>
+      <c r="N40" s="26" t="e">
+        <f t="shared" si="37"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O40" s="26">
+        <f t="shared" si="37"/>
+        <v>0.62845196849403984</v>
+      </c>
+      <c r="P40" s="26" t="e">
+        <f t="shared" si="37"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q40" s="26" t="e">
+        <f t="shared" si="37"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R40" s="26"/>
+      <c r="S40" s="3"/>
+      <c r="T40" s="26">
+        <f t="shared" ref="T40:Z40" si="38">T19/T17</f>
         <v>0.60162964411386954</v>
       </c>
-      <c r="Q40" s="26">
-        <f t="shared" si="35"/>
+      <c r="U40" s="26">
+        <f t="shared" si="38"/>
         <v>0.59367227764938779</v>
       </c>
-      <c r="R40" s="26">
-        <f t="shared" si="35"/>
+      <c r="V40" s="26">
+        <f t="shared" si="38"/>
         <v>0.60511124393034577</v>
       </c>
-      <c r="S40" s="26">
-        <f t="shared" si="35"/>
+      <c r="W40" s="26">
+        <f t="shared" si="38"/>
         <v>0.6227146430910846</v>
       </c>
-      <c r="T40" s="26">
-        <f t="shared" si="35"/>
+      <c r="X40" s="26">
+        <f t="shared" si="38"/>
         <v>0.56913999888040068</v>
       </c>
-      <c r="U40" s="26">
-        <f t="shared" si="35"/>
+      <c r="Y40" s="26">
+        <f t="shared" si="38"/>
         <v>0.62920234346109261</v>
       </c>
-      <c r="V40" s="26">
-        <f t="shared" si="35"/>
+      <c r="Z40" s="26">
+        <f t="shared" si="38"/>
         <v>0.64152878387305312</v>
       </c>
-      <c r="W40" s="26">
-        <f t="shared" ref="W40" si="36">W19/W17</f>
+      <c r="AA40" s="26">
+        <f t="shared" ref="AA40" si="39">AA19/AA17</f>
         <v>0.6147414537591156</v>
       </c>
-      <c r="X40" s="3"/>
-      <c r="Y40" s="3"/>
-      <c r="Z40" s="3"/>
-      <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
@@ -5955,87 +6396,109 @@
       <c r="BR40" s="3"/>
       <c r="BS40" s="3"/>
       <c r="BT40" s="3"/>
-    </row>
-    <row r="41" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU40" s="3"/>
+      <c r="BV40" s="3"/>
+      <c r="BW40" s="3"/>
+      <c r="BX40" s="3"/>
+    </row>
+    <row r="41" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C41" s="26">
-        <f t="shared" ref="C41:J41" si="37">C23/C17</f>
+        <f t="shared" ref="C41:J41" si="40">C23/C17</f>
         <v>4.0679717797017623E-2</v>
       </c>
       <c r="D41" s="26">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>9.6052258792210451E-2</v>
       </c>
       <c r="E41" s="26">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.13064743461712133</v>
       </c>
       <c r="F41" s="26">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.15334842491639172</v>
       </c>
       <c r="G41" s="26">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.12721189736757027</v>
       </c>
       <c r="H41" s="26">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.15487568498043178</v>
       </c>
       <c r="I41" s="26">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.14829366582683046</v>
       </c>
       <c r="J41" s="26">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.16156303453114571</v>
       </c>
       <c r="K41" s="26">
-        <f t="shared" ref="K41" si="38">K23/K17</f>
+        <f t="shared" ref="K41:Q41" si="41">K23/K17</f>
         <v>9.2528918419663944E-2</v>
       </c>
-      <c r="L41" s="26"/>
-      <c r="M41" s="26"/>
-      <c r="N41" s="26"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="26">
-        <f t="shared" ref="P41:V41" si="39">P23/P17</f>
+      <c r="L41" s="26">
+        <f t="shared" si="41"/>
+        <v>0.17099523399748465</v>
+      </c>
+      <c r="M41" s="26">
+        <f t="shared" si="41"/>
+        <v>0.12011368188442899</v>
+      </c>
+      <c r="N41" s="26" t="e">
+        <f t="shared" si="41"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O41" s="26">
+        <f t="shared" si="41"/>
+        <v>7.9722863907216668E-2</v>
+      </c>
+      <c r="P41" s="26" t="e">
+        <f t="shared" si="41"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q41" s="26" t="e">
+        <f t="shared" si="41"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R41" s="26"/>
+      <c r="S41" s="3"/>
+      <c r="T41" s="26">
+        <f t="shared" ref="T41:Z41" si="42">T23/T17</f>
         <v>3.5476917274656621E-2</v>
       </c>
-      <c r="Q41" s="26">
-        <f t="shared" si="39"/>
+      <c r="U41" s="26">
+        <f t="shared" si="42"/>
         <v>1.9339383998059279E-2</v>
       </c>
-      <c r="R41" s="26">
-        <f t="shared" si="39"/>
+      <c r="V41" s="26">
+        <f t="shared" si="42"/>
         <v>-6.5492752250604106E-3</v>
       </c>
-      <c r="S41" s="26">
-        <f t="shared" si="39"/>
+      <c r="W41" s="26">
+        <f t="shared" si="42"/>
         <v>9.2406527959732421E-2</v>
       </c>
-      <c r="T41" s="26">
-        <f t="shared" si="39"/>
+      <c r="X41" s="26">
+        <f t="shared" si="42"/>
         <v>2.5055229516536028E-2</v>
       </c>
-      <c r="U41" s="26">
-        <f t="shared" si="39"/>
+      <c r="Y41" s="26">
+        <f t="shared" si="42"/>
         <v>0.11322297851484692</v>
       </c>
-      <c r="V41" s="26">
-        <f t="shared" si="39"/>
+      <c r="Z41" s="26">
+        <f t="shared" si="42"/>
         <v>0.14970333955935308</v>
       </c>
-      <c r="W41" s="26">
-        <f t="shared" ref="W41" si="40">W23/W17</f>
+      <c r="AA41" s="26">
+        <f t="shared" ref="AA41" si="43">AA23/AA17</f>
         <v>0.13275811519756217</v>
       </c>
-      <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
-      <c r="Z41" s="3"/>
-      <c r="AA41" s="3"/>
       <c r="AB41" s="3"/>
       <c r="AC41" s="3"/>
       <c r="AD41" s="3"/>
@@ -6081,87 +6544,109 @@
       <c r="BR41" s="3"/>
       <c r="BS41" s="3"/>
       <c r="BT41" s="3"/>
-    </row>
-    <row r="42" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU41" s="3"/>
+      <c r="BV41" s="3"/>
+      <c r="BW41" s="3"/>
+      <c r="BX41" s="3"/>
+    </row>
+    <row r="42" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C42" s="26">
-        <f t="shared" ref="C42:J42" si="41">C30/C17</f>
+        <f t="shared" ref="C42:J42" si="44">C30/C17</f>
         <v>1.9821912597458774E-2</v>
       </c>
       <c r="D42" s="26">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>6.0826753764653761E-2</v>
       </c>
       <c r="E42" s="26">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>9.1071731140036694E-2</v>
       </c>
       <c r="F42" s="26">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0.10905515631764451</v>
       </c>
       <c r="G42" s="26">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0.11151822715115656</v>
       </c>
       <c r="H42" s="26">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0.11743479127387414</v>
       </c>
       <c r="I42" s="26">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0.10916684174741052</v>
       </c>
       <c r="J42" s="26">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0.11812984528527355</v>
       </c>
       <c r="K42" s="26">
-        <f t="shared" ref="K42" si="42">K30/K17</f>
+        <f t="shared" ref="K42:Q42" si="45">K30/K17</f>
         <v>7.3281868130365843E-2</v>
       </c>
-      <c r="L42" s="26"/>
-      <c r="M42" s="26"/>
-      <c r="N42" s="26"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="26">
-        <f t="shared" ref="P42:V42" si="43">P30/P17</f>
+      <c r="L42" s="26">
+        <f t="shared" si="45"/>
+        <v>0.11698467597802346</v>
+      </c>
+      <c r="M42" s="26">
+        <f t="shared" si="45"/>
+        <v>8.7551012343689213E-2</v>
+      </c>
+      <c r="N42" s="26" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O42" s="26">
+        <f t="shared" si="45"/>
+        <v>6.0273598720081561E-2</v>
+      </c>
+      <c r="P42" s="26" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q42" s="26" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R42" s="26"/>
+      <c r="S42" s="3"/>
+      <c r="T42" s="26">
+        <f t="shared" ref="T42:Z42" si="46">T30/T17</f>
         <v>2.0762879344331946E-2</v>
       </c>
-      <c r="Q42" s="26">
-        <f t="shared" si="43"/>
+      <c r="U42" s="26">
+        <f t="shared" si="46"/>
         <v>1.0863154013181801E-2</v>
       </c>
-      <c r="R42" s="26">
-        <f t="shared" si="43"/>
+      <c r="V42" s="26">
+        <f t="shared" si="46"/>
         <v>-3.6482237062709803E-2</v>
       </c>
-      <c r="S42" s="26">
-        <f t="shared" si="43"/>
+      <c r="W42" s="26">
+        <f t="shared" si="46"/>
         <v>7.0839330655726368E-2</v>
       </c>
-      <c r="T42" s="26">
-        <f t="shared" si="43"/>
+      <c r="X42" s="26">
+        <f t="shared" si="46"/>
         <v>7.6154397632523555E-4</v>
       </c>
-      <c r="U42" s="26">
-        <f t="shared" si="43"/>
+      <c r="Y42" s="26">
+        <f t="shared" si="46"/>
         <v>7.6652127689148086E-2</v>
       </c>
-      <c r="V42" s="26">
-        <f t="shared" si="43"/>
+      <c r="Z42" s="26">
+        <f t="shared" si="46"/>
         <v>0.11442114688495938</v>
       </c>
-      <c r="W42" s="26">
-        <f t="shared" ref="W42" si="44">W30/W17</f>
+      <c r="AA42" s="26">
+        <f t="shared" ref="AA42" si="47">AA30/AA17</f>
         <v>9.6257670482381166E-2</v>
       </c>
-      <c r="X42" s="3"/>
-      <c r="Y42" s="3"/>
-      <c r="Z42" s="3"/>
-      <c r="AA42" s="3"/>
       <c r="AB42" s="3"/>
       <c r="AC42" s="3"/>
       <c r="AD42" s="3"/>
@@ -6207,87 +6692,109 @@
       <c r="BR42" s="3"/>
       <c r="BS42" s="3"/>
       <c r="BT42" s="3"/>
-    </row>
-    <row r="43" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU42" s="3"/>
+      <c r="BV42" s="3"/>
+      <c r="BW42" s="3"/>
+      <c r="BX42" s="3"/>
+    </row>
+    <row r="43" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C43" s="26">
-        <f t="shared" ref="C43:J43" si="45">C27/C26</f>
+        <f t="shared" ref="C43:J43" si="48">C27/C26</f>
         <v>0.41609684279404618</v>
       </c>
       <c r="D43" s="26">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0.33820496929404442</v>
       </c>
       <c r="E43" s="26">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0.28844039636255064</v>
       </c>
       <c r="F43" s="26">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0.29229045861887204</v>
       </c>
       <c r="G43" s="26">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0.14678314003500131</v>
       </c>
       <c r="H43" s="26">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0.25133828831818056</v>
       </c>
       <c r="I43" s="26">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0.28801425418184734</v>
       </c>
       <c r="J43" s="26">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0.28406714925159093</v>
       </c>
       <c r="K43" s="26">
-        <f t="shared" ref="K43" si="46">K27/K26</f>
+        <f t="shared" ref="K43:Q43" si="49">K27/K26</f>
         <v>0.24536541231212411</v>
       </c>
-      <c r="L43" s="26"/>
-      <c r="M43" s="26"/>
-      <c r="N43" s="26"/>
-      <c r="O43" s="3"/>
-      <c r="P43" s="26">
-        <f t="shared" ref="P43:V43" si="47">P27/P26</f>
+      <c r="L43" s="26">
+        <f t="shared" si="49"/>
+        <v>0.31436604632480913</v>
+      </c>
+      <c r="M43" s="26">
+        <f t="shared" si="49"/>
+        <v>0.28492439209254389</v>
+      </c>
+      <c r="N43" s="26" t="e">
+        <f t="shared" si="49"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O43" s="26">
+        <f t="shared" si="49"/>
+        <v>0.27597678670124581</v>
+      </c>
+      <c r="P43" s="26" t="e">
+        <f t="shared" si="49"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q43" s="26" t="e">
+        <f t="shared" si="49"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R43" s="26"/>
+      <c r="S43" s="3"/>
+      <c r="T43" s="26">
+        <f t="shared" ref="T43:Z43" si="50">T27/T26</f>
         <v>0.32276332637259642</v>
       </c>
-      <c r="Q43" s="26">
-        <f t="shared" si="47"/>
+      <c r="U43" s="26">
+        <f t="shared" si="50"/>
         <v>0.27868957661516452</v>
       </c>
-      <c r="R43" s="26">
-        <f t="shared" si="47"/>
+      <c r="V43" s="26">
+        <f t="shared" si="50"/>
         <v>-1.2352748086904732</v>
       </c>
-      <c r="S43" s="26">
-        <f t="shared" si="47"/>
+      <c r="W43" s="26">
+        <f t="shared" si="50"/>
         <v>0.12592645335853508</v>
       </c>
-      <c r="T43" s="26">
-        <f t="shared" si="47"/>
+      <c r="X43" s="26">
+        <f t="shared" si="50"/>
         <v>0.84503700608809063</v>
       </c>
-      <c r="U43" s="26">
-        <f t="shared" si="47"/>
+      <c r="Y43" s="26">
+        <f t="shared" si="50"/>
         <v>0.30742578448437885</v>
       </c>
-      <c r="V43" s="26">
-        <f t="shared" si="47"/>
+      <c r="Z43" s="26">
+        <f t="shared" si="50"/>
         <v>0.25324160863405548</v>
       </c>
-      <c r="W43" s="26">
-        <f t="shared" ref="W43" si="48">W27/W26</f>
+      <c r="AA43" s="26">
+        <f t="shared" ref="AA43" si="51">AA27/AA26</f>
         <v>0.28549527451121842</v>
       </c>
-      <c r="X43" s="3"/>
-      <c r="Y43" s="3"/>
-      <c r="Z43" s="3"/>
-      <c r="AA43" s="3"/>
       <c r="AB43" s="3"/>
       <c r="AC43" s="3"/>
       <c r="AD43" s="3"/>
@@ -6333,8 +6840,12 @@
       <c r="BR43" s="3"/>
       <c r="BS43" s="3"/>
       <c r="BT43" s="3"/>
-    </row>
-    <row r="44" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU43" s="3"/>
+      <c r="BV43" s="3"/>
+      <c r="BW43" s="3"/>
+      <c r="BX43" s="3"/>
+    </row>
+    <row r="44" spans="2:76" x14ac:dyDescent="0.2">
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -6405,8 +6916,12 @@
       <c r="BR44" s="3"/>
       <c r="BS44" s="3"/>
       <c r="BT44" s="3"/>
-    </row>
-    <row r="45" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU44" s="3"/>
+      <c r="BV44" s="3"/>
+      <c r="BW44" s="3"/>
+      <c r="BX44" s="3"/>
+    </row>
+    <row r="45" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
         <v>50</v>
       </c>
@@ -6423,36 +6938,36 @@
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
-      <c r="P45" s="3">
+      <c r="P45" s="3"/>
+      <c r="Q45" s="3"/>
+      <c r="R45" s="3"/>
+      <c r="S45" s="3"/>
+      <c r="T45" s="3">
         <v>723.13499999999999</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="U45" s="3">
         <v>671.26700000000005</v>
       </c>
-      <c r="R45" s="3">
+      <c r="V45" s="3">
         <v>1104.8620000000001</v>
       </c>
-      <c r="S45" s="3">
+      <c r="W45" s="3">
         <v>823.13900000000001</v>
       </c>
-      <c r="T45" s="3">
+      <c r="X45" s="3">
         <v>517.60199999999998</v>
       </c>
-      <c r="U45" s="3">
+      <c r="Y45" s="3">
         <v>900.88400000000001</v>
       </c>
-      <c r="V45" s="3">
+      <c r="Z45" s="3">
         <f>772.727+116.221</f>
         <v>888.94799999999998</v>
       </c>
-      <c r="W45" s="3">
+      <c r="AA45" s="3">
         <f>510.563+97.006</f>
         <v>607.56899999999996</v>
       </c>
-      <c r="X45" s="3"/>
-      <c r="Y45" s="3"/>
-      <c r="Z45" s="3"/>
-      <c r="AA45" s="3"/>
       <c r="AB45" s="3"/>
       <c r="AC45" s="3"/>
       <c r="AD45" s="3"/>
@@ -6498,8 +7013,12 @@
       <c r="BR45" s="3"/>
       <c r="BS45" s="3"/>
       <c r="BT45" s="3"/>
-    </row>
-    <row r="46" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU45" s="3"/>
+      <c r="BV45" s="3"/>
+      <c r="BW45" s="3"/>
+      <c r="BX45" s="3"/>
+    </row>
+    <row r="46" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
         <v>51</v>
       </c>
@@ -6516,34 +7035,34 @@
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
-      <c r="P46" s="3">
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3"/>
+      <c r="R46" s="3"/>
+      <c r="S46" s="3"/>
+      <c r="T46" s="3">
         <v>73.111999999999995</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="U46" s="3">
         <v>80.251000000000005</v>
       </c>
-      <c r="R46" s="3">
+      <c r="V46" s="3">
         <v>83.856999999999999</v>
       </c>
-      <c r="S46" s="3">
+      <c r="W46" s="3">
         <v>69.102000000000004</v>
       </c>
-      <c r="T46" s="3">
+      <c r="X46" s="3">
         <v>104.506</v>
       </c>
-      <c r="U46" s="3">
+      <c r="Y46" s="3">
         <v>78.346000000000004</v>
       </c>
-      <c r="V46" s="3">
+      <c r="Z46" s="3">
         <v>105.324</v>
       </c>
-      <c r="W46" s="3">
+      <c r="AA46" s="3">
         <v>113.31100000000001</v>
       </c>
-      <c r="X46" s="3"/>
-      <c r="Y46" s="3"/>
-      <c r="Z46" s="3"/>
-      <c r="AA46" s="3"/>
       <c r="AB46" s="3"/>
       <c r="AC46" s="3"/>
       <c r="AD46" s="3"/>
@@ -6589,8 +7108,12 @@
       <c r="BR46" s="3"/>
       <c r="BS46" s="3"/>
       <c r="BT46" s="3"/>
-    </row>
-    <row r="47" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU46" s="3"/>
+      <c r="BV46" s="3"/>
+      <c r="BW46" s="3"/>
+      <c r="BX46" s="3"/>
+    </row>
+    <row r="47" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
         <v>52</v>
       </c>
@@ -6607,34 +7130,34 @@
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
-      <c r="P47" s="3">
+      <c r="P47" s="3"/>
+      <c r="Q47" s="3"/>
+      <c r="R47" s="3"/>
+      <c r="S47" s="3"/>
+      <c r="T47" s="3">
         <v>437.87900000000002</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="U47" s="3">
         <v>434.32600000000002</v>
       </c>
-      <c r="R47" s="3">
+      <c r="V47" s="3">
         <v>404.053</v>
       </c>
-      <c r="S47" s="3">
+      <c r="W47" s="3">
         <v>525.86400000000003</v>
       </c>
-      <c r="T47" s="3">
+      <c r="X47" s="3">
         <v>505.62099999999998</v>
       </c>
-      <c r="U47" s="3">
+      <c r="Y47" s="3">
         <v>469.46600000000001</v>
       </c>
-      <c r="V47" s="3">
+      <c r="Z47" s="3">
         <v>575.005</v>
       </c>
-      <c r="W47" s="3">
+      <c r="AA47" s="3">
         <v>542.05899999999997</v>
       </c>
-      <c r="X47" s="3"/>
-      <c r="Y47" s="3"/>
-      <c r="Z47" s="3"/>
-      <c r="AA47" s="3"/>
       <c r="AB47" s="3"/>
       <c r="AC47" s="3"/>
       <c r="AD47" s="3"/>
@@ -6680,8 +7203,12 @@
       <c r="BR47" s="3"/>
       <c r="BS47" s="3"/>
       <c r="BT47" s="3"/>
-    </row>
-    <row r="48" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU47" s="3"/>
+      <c r="BV47" s="3"/>
+      <c r="BW47" s="3"/>
+      <c r="BX47" s="3"/>
+    </row>
+    <row r="48" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B48" s="2" t="s">
         <v>53</v>
       </c>
@@ -6698,34 +7225,34 @@
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
-      <c r="P48" s="3">
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3"/>
+      <c r="R48" s="3"/>
+      <c r="S48" s="3"/>
+      <c r="T48" s="3">
         <v>101.824</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="U48" s="3">
         <v>78.905000000000001</v>
       </c>
-      <c r="R48" s="3">
+      <c r="V48" s="3">
         <v>68.856999999999999</v>
       </c>
-      <c r="S48" s="3">
+      <c r="W48" s="3">
         <v>89.653999999999996</v>
       </c>
-      <c r="T48" s="3">
+      <c r="X48" s="3">
         <v>100.289</v>
       </c>
-      <c r="U48" s="3">
+      <c r="Y48" s="3">
         <v>88.569000000000003</v>
       </c>
-      <c r="V48" s="3">
+      <c r="Z48" s="3">
         <v>104.154</v>
       </c>
-      <c r="W48" s="3">
+      <c r="AA48" s="3">
         <v>111.23099999999999</v>
       </c>
-      <c r="X48" s="3"/>
-      <c r="Y48" s="3"/>
-      <c r="Z48" s="3"/>
-      <c r="AA48" s="3"/>
       <c r="AB48" s="3"/>
       <c r="AC48" s="3"/>
       <c r="AD48" s="3"/>
@@ -6771,8 +7298,12 @@
       <c r="BR48" s="3"/>
       <c r="BS48" s="3"/>
       <c r="BT48" s="3"/>
-    </row>
-    <row r="49" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU48" s="3"/>
+      <c r="BV48" s="3"/>
+      <c r="BW48" s="3"/>
+      <c r="BX48" s="3"/>
+    </row>
+    <row r="49" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
         <v>54</v>
       </c>
@@ -6789,42 +7320,42 @@
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
-      <c r="P49" s="3">
-        <f t="shared" ref="P49:T49" si="49">SUM(P45:P48)</f>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="3"/>
+      <c r="R49" s="3"/>
+      <c r="S49" s="3"/>
+      <c r="T49" s="3">
+        <f t="shared" ref="T49:X49" si="52">SUM(T45:T48)</f>
         <v>1335.95</v>
       </c>
-      <c r="Q49" s="3">
-        <f t="shared" si="49"/>
+      <c r="U49" s="3">
+        <f t="shared" si="52"/>
         <v>1264.749</v>
       </c>
-      <c r="R49" s="3">
-        <f t="shared" si="49"/>
+      <c r="V49" s="3">
+        <f t="shared" si="52"/>
         <v>1661.6289999999999</v>
       </c>
-      <c r="S49" s="3">
-        <f t="shared" si="49"/>
+      <c r="W49" s="3">
+        <f t="shared" si="52"/>
         <v>1507.759</v>
       </c>
-      <c r="T49" s="3">
-        <f t="shared" si="49"/>
+      <c r="X49" s="3">
+        <f t="shared" si="52"/>
         <v>1228.0179999999998</v>
       </c>
-      <c r="U49" s="3">
-        <f>SUM(U45:U48)</f>
+      <c r="Y49" s="3">
+        <f>SUM(Y45:Y48)</f>
         <v>1537.2649999999999</v>
       </c>
-      <c r="V49" s="3">
-        <f>SUM(V45:V48)</f>
+      <c r="Z49" s="3">
+        <f>SUM(Z45:Z48)</f>
         <v>1673.431</v>
       </c>
-      <c r="W49" s="3">
-        <f>SUM(W45:W48)</f>
+      <c r="AA49" s="3">
+        <f>SUM(AA45:AA48)</f>
         <v>1374.1699999999998</v>
       </c>
-      <c r="X49" s="3"/>
-      <c r="Y49" s="3"/>
-      <c r="Z49" s="3"/>
-      <c r="AA49" s="3"/>
       <c r="AB49" s="3"/>
       <c r="AC49" s="3"/>
       <c r="AD49" s="3"/>
@@ -6870,8 +7401,12 @@
       <c r="BR49" s="3"/>
       <c r="BS49" s="3"/>
       <c r="BT49" s="3"/>
-    </row>
-    <row r="50" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU49" s="3"/>
+      <c r="BV49" s="3"/>
+      <c r="BW49" s="3"/>
+      <c r="BX49" s="3"/>
+    </row>
+    <row r="50" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
         <v>55</v>
       </c>
@@ -6888,34 +7423,34 @@
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
-      <c r="P50" s="3">
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="3"/>
+      <c r="S50" s="3"/>
+      <c r="T50" s="3">
         <v>694.85500000000002</v>
       </c>
-      <c r="Q50" s="3">
+      <c r="U50" s="3">
         <v>665.29</v>
       </c>
-      <c r="R50" s="3">
+      <c r="V50" s="3">
         <v>550.58699999999999</v>
       </c>
-      <c r="S50" s="3">
+      <c r="W50" s="3">
         <v>508.33600000000001</v>
       </c>
-      <c r="T50" s="3">
+      <c r="X50" s="3">
         <v>551.58500000000004</v>
       </c>
-      <c r="U50" s="3">
+      <c r="Y50" s="3">
         <v>538.03300000000002</v>
       </c>
-      <c r="V50" s="3">
+      <c r="Z50" s="3">
         <v>575.77300000000002</v>
       </c>
-      <c r="W50" s="3">
+      <c r="AA50" s="3">
         <v>606.05999999999995</v>
       </c>
-      <c r="X50" s="3"/>
-      <c r="Y50" s="3"/>
-      <c r="Z50" s="3"/>
-      <c r="AA50" s="3"/>
       <c r="AB50" s="3"/>
       <c r="AC50" s="3"/>
       <c r="AD50" s="3"/>
@@ -6961,8 +7496,12 @@
       <c r="BR50" s="3"/>
       <c r="BS50" s="3"/>
       <c r="BT50" s="3"/>
-    </row>
-    <row r="51" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU50" s="3"/>
+      <c r="BV50" s="3"/>
+      <c r="BW50" s="3"/>
+      <c r="BX50" s="3"/>
+    </row>
+    <row r="51" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
         <v>86</v>
       </c>
@@ -6979,34 +7518,34 @@
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
       <c r="O51" s="3"/>
-      <c r="P51" s="3">
+      <c r="P51" s="3"/>
+      <c r="Q51" s="3"/>
+      <c r="R51" s="3"/>
+      <c r="S51" s="3"/>
+      <c r="T51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3">
+      <c r="U51" s="3">
         <v>1230.954</v>
       </c>
-      <c r="R51" s="3">
+      <c r="V51" s="3">
         <v>893.98900000000003</v>
       </c>
-      <c r="S51" s="3">
+      <c r="W51" s="3">
         <v>698.23099999999999</v>
       </c>
-      <c r="T51" s="3">
+      <c r="X51" s="3">
         <v>723.55</v>
       </c>
-      <c r="U51" s="3">
+      <c r="Y51" s="3">
         <v>678.25599999999997</v>
       </c>
-      <c r="V51" s="3">
+      <c r="Z51" s="3">
         <v>803.12099999999998</v>
       </c>
-      <c r="W51" s="3">
+      <c r="AA51" s="3">
         <v>868.13</v>
       </c>
-      <c r="X51" s="3"/>
-      <c r="Y51" s="3"/>
-      <c r="Z51" s="3"/>
-      <c r="AA51" s="3"/>
       <c r="AB51" s="3"/>
       <c r="AC51" s="3"/>
       <c r="AD51" s="3"/>
@@ -7052,8 +7591,12 @@
       <c r="BR51" s="3"/>
       <c r="BS51" s="3"/>
       <c r="BT51" s="3"/>
-    </row>
-    <row r="52" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU51" s="3"/>
+      <c r="BV51" s="3"/>
+      <c r="BW51" s="3"/>
+      <c r="BX51" s="3"/>
+    </row>
+    <row r="52" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
         <v>56</v>
       </c>
@@ -7070,34 +7613,34 @@
       <c r="M52" s="3"/>
       <c r="N52" s="3"/>
       <c r="O52" s="3"/>
-      <c r="P52" s="3">
+      <c r="P52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="3"/>
+      <c r="S52" s="3"/>
+      <c r="T52" s="3">
         <v>354.78800000000001</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="U52" s="3">
         <v>388.67200000000003</v>
       </c>
-      <c r="R52" s="3">
+      <c r="V52" s="3">
         <v>208.697</v>
       </c>
-      <c r="S52" s="3">
+      <c r="W52" s="3">
         <v>225.16499999999999</v>
       </c>
-      <c r="T52" s="3">
+      <c r="X52" s="3">
         <v>209.947</v>
       </c>
-      <c r="U52" s="3">
+      <c r="Y52" s="3">
         <v>220.679</v>
       </c>
-      <c r="V52" s="3">
+      <c r="Z52" s="3">
         <v>247.56200000000001</v>
       </c>
-      <c r="W52" s="3">
+      <c r="AA52" s="3">
         <v>247.816</v>
       </c>
-      <c r="X52" s="3"/>
-      <c r="Y52" s="3"/>
-      <c r="Z52" s="3"/>
-      <c r="AA52" s="3"/>
       <c r="AB52" s="3"/>
       <c r="AC52" s="3"/>
       <c r="AD52" s="3"/>
@@ -7143,8 +7686,12 @@
       <c r="BR52" s="3"/>
       <c r="BS52" s="3"/>
       <c r="BT52" s="3"/>
-    </row>
-    <row r="53" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU52" s="3"/>
+      <c r="BV52" s="3"/>
+      <c r="BW52" s="3"/>
+      <c r="BX52" s="3"/>
+    </row>
+    <row r="53" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B53" s="2" t="s">
         <v>57</v>
       </c>
@@ -7161,42 +7708,42 @@
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3"/>
-      <c r="P53" s="3">
-        <f t="shared" ref="P53:T53" si="50">SUM(P50:P52)</f>
+      <c r="P53" s="3"/>
+      <c r="Q53" s="3"/>
+      <c r="R53" s="3"/>
+      <c r="S53" s="3"/>
+      <c r="T53" s="3">
+        <f t="shared" ref="T53:X53" si="53">SUM(T50:T52)</f>
         <v>1049.643</v>
       </c>
-      <c r="Q53" s="3">
-        <f t="shared" si="50"/>
+      <c r="U53" s="3">
+        <f t="shared" si="53"/>
         <v>2284.9160000000002</v>
       </c>
-      <c r="R53" s="3">
-        <f t="shared" si="50"/>
+      <c r="V53" s="3">
+        <f t="shared" si="53"/>
         <v>1653.2730000000001</v>
       </c>
-      <c r="S53" s="3">
-        <f t="shared" si="50"/>
+      <c r="W53" s="3">
+        <f t="shared" si="53"/>
         <v>1431.732</v>
       </c>
-      <c r="T53" s="3">
-        <f t="shared" si="50"/>
+      <c r="X53" s="3">
+        <f t="shared" si="53"/>
         <v>1485.0819999999999</v>
       </c>
-      <c r="U53" s="3">
-        <f>SUM(U50:U52)</f>
+      <c r="Y53" s="3">
+        <f>SUM(Y50:Y52)</f>
         <v>1436.9680000000001</v>
       </c>
-      <c r="V53" s="3">
-        <f>SUM(V50:V52)</f>
+      <c r="Z53" s="3">
+        <f>SUM(Z50:Z52)</f>
         <v>1626.4560000000001</v>
       </c>
-      <c r="W53" s="3">
-        <f>SUM(W50:W52)</f>
+      <c r="AA53" s="3">
+        <f>SUM(AA50:AA52)</f>
         <v>1722.0060000000001</v>
       </c>
-      <c r="X53" s="3"/>
-      <c r="Y53" s="3"/>
-      <c r="Z53" s="3"/>
-      <c r="AA53" s="3"/>
       <c r="AB53" s="3"/>
       <c r="AC53" s="3"/>
       <c r="AD53" s="3"/>
@@ -7242,8 +7789,12 @@
       <c r="BR53" s="3"/>
       <c r="BS53" s="3"/>
       <c r="BT53" s="3"/>
-    </row>
-    <row r="54" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU53" s="3"/>
+      <c r="BV53" s="3"/>
+      <c r="BW53" s="3"/>
+      <c r="BX53" s="3"/>
+    </row>
+    <row r="54" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
         <v>58</v>
       </c>
@@ -7260,42 +7811,42 @@
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
-      <c r="P54" s="24">
-        <f t="shared" ref="P54:W54" si="51">P49+P53</f>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="3"/>
+      <c r="R54" s="3"/>
+      <c r="S54" s="3"/>
+      <c r="T54" s="24">
+        <f t="shared" ref="T54:AA54" si="54">T49+T53</f>
         <v>2385.5929999999998</v>
       </c>
-      <c r="Q54" s="24">
-        <f t="shared" si="51"/>
+      <c r="U54" s="24">
+        <f t="shared" si="54"/>
         <v>3549.665</v>
       </c>
-      <c r="R54" s="24">
-        <f t="shared" si="51"/>
+      <c r="V54" s="24">
+        <f t="shared" si="54"/>
         <v>3314.902</v>
       </c>
-      <c r="S54" s="24">
-        <f t="shared" si="51"/>
+      <c r="W54" s="24">
+        <f t="shared" si="54"/>
         <v>2939.491</v>
       </c>
-      <c r="T54" s="24">
-        <f t="shared" si="51"/>
+      <c r="X54" s="24">
+        <f t="shared" si="54"/>
         <v>2713.0999999999995</v>
       </c>
-      <c r="U54" s="24">
-        <f t="shared" si="51"/>
+      <c r="Y54" s="24">
+        <f t="shared" si="54"/>
         <v>2974.2330000000002</v>
       </c>
-      <c r="V54" s="24">
-        <f t="shared" si="51"/>
+      <c r="Z54" s="24">
+        <f t="shared" si="54"/>
         <v>3299.8870000000002</v>
       </c>
-      <c r="W54" s="24">
-        <f t="shared" si="51"/>
+      <c r="AA54" s="24">
+        <f t="shared" si="54"/>
         <v>3096.1759999999999</v>
       </c>
-      <c r="X54" s="3"/>
-      <c r="Y54" s="3"/>
-      <c r="Z54" s="3"/>
-      <c r="AA54" s="3"/>
       <c r="AB54" s="3"/>
       <c r="AC54" s="3"/>
       <c r="AD54" s="3"/>
@@ -7341,8 +7892,12 @@
       <c r="BR54" s="3"/>
       <c r="BS54" s="3"/>
       <c r="BT54" s="3"/>
-    </row>
-    <row r="55" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU54" s="3"/>
+      <c r="BV54" s="3"/>
+      <c r="BW54" s="3"/>
+      <c r="BX54" s="3"/>
+    </row>
+    <row r="55" spans="2:76" x14ac:dyDescent="0.2">
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -7361,10 +7916,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-      <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
@@ -7412,8 +7967,12 @@
       <c r="BR55" s="3"/>
       <c r="BS55" s="3"/>
       <c r="BT55" s="3"/>
-    </row>
-    <row r="56" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU55" s="3"/>
+      <c r="BV55" s="3"/>
+      <c r="BW55" s="3"/>
+      <c r="BX55" s="3"/>
+    </row>
+    <row r="56" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B56" s="2" t="s">
         <v>59</v>
       </c>
@@ -7430,34 +7989,34 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-      <c r="P56" s="3">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+      <c r="T56" s="3">
         <v>226.87799999999999</v>
       </c>
-      <c r="Q56" s="3">
+      <c r="U56" s="3">
         <v>219.91900000000001</v>
       </c>
-      <c r="R56" s="3">
+      <c r="V56" s="3">
         <v>289.39600000000002</v>
       </c>
-      <c r="S56" s="3">
+      <c r="W56" s="3">
         <v>374.82900000000001</v>
       </c>
-      <c r="T56" s="3">
+      <c r="X56" s="3">
         <v>258.89499999999998</v>
       </c>
-      <c r="U56" s="3">
+      <c r="Y56" s="3">
         <v>296.976</v>
       </c>
-      <c r="V56" s="3">
+      <c r="Z56" s="3">
         <v>364.53199999999998</v>
       </c>
-      <c r="W56" s="3">
+      <c r="AA56" s="3">
         <v>296.738</v>
       </c>
-      <c r="X56" s="3"/>
-      <c r="Y56" s="3"/>
-      <c r="Z56" s="3"/>
-      <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
@@ -7503,8 +8062,12 @@
       <c r="BR56" s="3"/>
       <c r="BS56" s="3"/>
       <c r="BT56" s="3"/>
-    </row>
-    <row r="57" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU56" s="3"/>
+      <c r="BV56" s="3"/>
+      <c r="BW56" s="3"/>
+      <c r="BX56" s="3"/>
+    </row>
+    <row r="57" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B57" s="2" t="s">
         <v>60</v>
       </c>
@@ -7521,34 +8084,34 @@
       <c r="M57" s="3"/>
       <c r="N57" s="3"/>
       <c r="O57" s="3"/>
-      <c r="P57" s="3">
+      <c r="P57" s="3"/>
+      <c r="Q57" s="3"/>
+      <c r="R57" s="3"/>
+      <c r="S57" s="3"/>
+      <c r="T57" s="3">
         <v>293.57900000000001</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="U57" s="3">
         <v>302.214</v>
       </c>
-      <c r="R57" s="3">
+      <c r="V57" s="3">
         <v>396.36500000000001</v>
       </c>
-      <c r="S57" s="3">
+      <c r="W57" s="3">
         <v>395.815</v>
       </c>
-      <c r="T57" s="3">
+      <c r="X57" s="3">
         <v>413.303</v>
       </c>
-      <c r="U57" s="3">
+      <c r="Y57" s="3">
         <v>436.65499999999997</v>
       </c>
-      <c r="V57" s="3">
+      <c r="Z57" s="3">
         <v>504.92200000000003</v>
       </c>
-      <c r="W57" s="3">
+      <c r="AA57" s="3">
         <v>433.68200000000002</v>
       </c>
-      <c r="X57" s="3"/>
-      <c r="Y57" s="3"/>
-      <c r="Z57" s="3"/>
-      <c r="AA57" s="3"/>
       <c r="AB57" s="3"/>
       <c r="AC57" s="3"/>
       <c r="AD57" s="3"/>
@@ -7594,8 +8157,12 @@
       <c r="BR57" s="3"/>
       <c r="BS57" s="3"/>
       <c r="BT57" s="3"/>
-    </row>
-    <row r="58" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU57" s="3"/>
+      <c r="BV57" s="3"/>
+      <c r="BW57" s="3"/>
+      <c r="BX57" s="3"/>
+    </row>
+    <row r="58" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B58" s="2" t="s">
         <v>61</v>
       </c>
@@ -7612,34 +8179,34 @@
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
       <c r="O58" s="3"/>
-      <c r="P58" s="3">
+      <c r="P58" s="3"/>
+      <c r="Q58" s="3"/>
+      <c r="R58" s="3"/>
+      <c r="S58" s="3"/>
+      <c r="T58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="U58" s="3">
         <v>282.82900000000001</v>
       </c>
-      <c r="R58" s="3">
+      <c r="V58" s="3">
         <v>248.846</v>
       </c>
-      <c r="S58" s="3">
+      <c r="W58" s="3">
         <v>222.82300000000001</v>
       </c>
-      <c r="T58" s="3">
+      <c r="X58" s="3">
         <v>213.97900000000001</v>
       </c>
-      <c r="U58" s="3">
+      <c r="Y58" s="3">
         <v>179.625</v>
       </c>
-      <c r="V58" s="3">
+      <c r="Z58" s="3">
         <v>211.6</v>
       </c>
-      <c r="W58" s="3">
+      <c r="AA58" s="3">
         <v>215.511</v>
       </c>
-      <c r="X58" s="3"/>
-      <c r="Y58" s="3"/>
-      <c r="Z58" s="3"/>
-      <c r="AA58" s="3"/>
       <c r="AB58" s="3"/>
       <c r="AC58" s="3"/>
       <c r="AD58" s="3"/>
@@ -7685,8 +8252,12 @@
       <c r="BR58" s="3"/>
       <c r="BS58" s="3"/>
       <c r="BT58" s="3"/>
-    </row>
-    <row r="59" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU58" s="3"/>
+      <c r="BV58" s="3"/>
+      <c r="BW58" s="3"/>
+      <c r="BX58" s="3"/>
+    </row>
+    <row r="59" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B59" s="2" t="s">
         <v>62</v>
       </c>
@@ -7703,34 +8274,34 @@
       <c r="M59" s="3"/>
       <c r="N59" s="3"/>
       <c r="O59" s="3"/>
-      <c r="P59" s="3">
+      <c r="P59" s="3"/>
+      <c r="Q59" s="3"/>
+      <c r="R59" s="3"/>
+      <c r="S59" s="3"/>
+      <c r="T59" s="3">
         <v>18.902000000000001</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="U59" s="3">
         <v>10.391999999999999</v>
       </c>
-      <c r="R59" s="3">
+      <c r="V59" s="3">
         <v>24.792000000000002</v>
       </c>
-      <c r="S59" s="3">
+      <c r="W59" s="3">
         <v>21.773</v>
       </c>
-      <c r="T59" s="3">
+      <c r="X59" s="3">
         <v>16.023</v>
       </c>
-      <c r="U59" s="3">
+      <c r="Y59" s="3">
         <v>53.564</v>
       </c>
-      <c r="V59" s="3">
+      <c r="Z59" s="3">
         <v>45.89</v>
       </c>
-      <c r="W59" s="3">
+      <c r="AA59" s="3">
         <v>52.939</v>
       </c>
-      <c r="X59" s="3"/>
-      <c r="Y59" s="3"/>
-      <c r="Z59" s="3"/>
-      <c r="AA59" s="3"/>
       <c r="AB59" s="3"/>
       <c r="AC59" s="3"/>
       <c r="AD59" s="3"/>
@@ -7776,8 +8347,12 @@
       <c r="BR59" s="3"/>
       <c r="BS59" s="3"/>
       <c r="BT59" s="3"/>
-    </row>
-    <row r="60" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU59" s="3"/>
+      <c r="BV59" s="3"/>
+      <c r="BW59" s="3"/>
+      <c r="BX59" s="3"/>
+    </row>
+    <row r="60" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B60" s="2" t="s">
         <v>302</v>
       </c>
@@ -7794,20 +8369,12 @@
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
       <c r="O60" s="3"/>
-      <c r="P60" s="3">
+      <c r="P60" s="3"/>
+      <c r="Q60" s="3"/>
+      <c r="R60" s="3"/>
+      <c r="S60" s="3"/>
+      <c r="T60" s="3">
         <v>19.558</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
-      <c r="R60" s="3">
-        <v>0</v>
-      </c>
-      <c r="S60" s="3">
-        <v>0</v>
-      </c>
-      <c r="T60" s="3">
-        <v>0</v>
       </c>
       <c r="U60" s="3">
         <v>0</v>
@@ -7818,10 +8385,18 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-      <c r="X60" s="3"/>
-      <c r="Y60" s="3"/>
-      <c r="Z60" s="3"/>
-      <c r="AA60" s="3"/>
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
       <c r="AB60" s="3"/>
       <c r="AC60" s="3"/>
       <c r="AD60" s="3"/>
@@ -7867,8 +8442,12 @@
       <c r="BR60" s="3"/>
       <c r="BS60" s="3"/>
       <c r="BT60" s="3"/>
-    </row>
-    <row r="61" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU60" s="3"/>
+      <c r="BV60" s="3"/>
+      <c r="BW60" s="3"/>
+      <c r="BX60" s="3"/>
+    </row>
+    <row r="61" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B61" s="2" t="s">
         <v>63</v>
       </c>
@@ -7885,42 +8464,42 @@
       <c r="M61" s="3"/>
       <c r="N61" s="3"/>
       <c r="O61" s="3"/>
-      <c r="P61" s="3">
-        <f t="shared" ref="P61:T61" si="52">SUM(P56:P60)</f>
+      <c r="P61" s="3"/>
+      <c r="Q61" s="3"/>
+      <c r="R61" s="3"/>
+      <c r="S61" s="3"/>
+      <c r="T61" s="3">
+        <f t="shared" ref="T61:X61" si="55">SUM(T56:T60)</f>
         <v>558.91700000000003</v>
       </c>
-      <c r="Q61" s="3">
-        <f t="shared" si="52"/>
+      <c r="U61" s="3">
+        <f t="shared" si="55"/>
         <v>815.35400000000004</v>
       </c>
-      <c r="R61" s="3">
-        <f t="shared" si="52"/>
+      <c r="V61" s="3">
+        <f t="shared" si="55"/>
         <v>959.399</v>
       </c>
-      <c r="S61" s="3">
-        <f t="shared" si="52"/>
+      <c r="W61" s="3">
+        <f t="shared" si="55"/>
         <v>1015.24</v>
       </c>
-      <c r="T61" s="3">
-        <f t="shared" si="52"/>
+      <c r="X61" s="3">
+        <f t="shared" si="55"/>
         <v>902.2</v>
       </c>
-      <c r="U61" s="3">
-        <f>SUM(U56:U60)</f>
+      <c r="Y61" s="3">
+        <f>SUM(Y56:Y60)</f>
         <v>966.81999999999994</v>
       </c>
-      <c r="V61" s="3">
-        <f>SUM(V56:V60)</f>
+      <c r="Z61" s="3">
+        <f>SUM(Z56:Z60)</f>
         <v>1126.944</v>
       </c>
-      <c r="W61" s="3">
-        <f>SUM(W56:W60)</f>
+      <c r="AA61" s="3">
+        <f>SUM(AA56:AA60)</f>
         <v>998.87</v>
       </c>
-      <c r="X61" s="3"/>
-      <c r="Y61" s="3"/>
-      <c r="Z61" s="3"/>
-      <c r="AA61" s="3"/>
       <c r="AB61" s="3"/>
       <c r="AC61" s="3"/>
       <c r="AD61" s="3"/>
@@ -7966,8 +8545,12 @@
       <c r="BR61" s="3"/>
       <c r="BS61" s="3"/>
       <c r="BT61" s="3"/>
-    </row>
-    <row r="62" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU61" s="3"/>
+      <c r="BV61" s="3"/>
+      <c r="BW61" s="3"/>
+      <c r="BX61" s="3"/>
+    </row>
+    <row r="62" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B62" s="2" t="s">
         <v>64</v>
       </c>
@@ -7984,34 +8567,34 @@
       <c r="M62" s="3"/>
       <c r="N62" s="3"/>
       <c r="O62" s="3"/>
-      <c r="P62" s="3">
+      <c r="P62" s="3"/>
+      <c r="Q62" s="3"/>
+      <c r="R62" s="3"/>
+      <c r="S62" s="3"/>
+      <c r="T62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="U62" s="3">
         <v>1252.634</v>
       </c>
-      <c r="R62" s="3">
+      <c r="V62" s="3">
         <v>957.58799999999997</v>
       </c>
-      <c r="S62" s="3">
+      <c r="W62" s="3">
         <v>697.26400000000001</v>
       </c>
-      <c r="T62" s="3">
+      <c r="X62" s="3">
         <v>713.36099999999999</v>
       </c>
-      <c r="U62" s="3">
+      <c r="Y62" s="3">
         <v>646.62400000000002</v>
       </c>
-      <c r="V62" s="3">
+      <c r="Z62" s="3">
         <v>740.01300000000003</v>
       </c>
-      <c r="W62" s="3">
+      <c r="AA62" s="3">
         <v>810.39099999999996</v>
       </c>
-      <c r="X62" s="3"/>
-      <c r="Y62" s="3"/>
-      <c r="Z62" s="3"/>
-      <c r="AA62" s="3"/>
       <c r="AB62" s="3"/>
       <c r="AC62" s="3"/>
       <c r="AD62" s="3"/>
@@ -8057,8 +8640,12 @@
       <c r="BR62" s="3"/>
       <c r="BS62" s="3"/>
       <c r="BT62" s="3"/>
-    </row>
-    <row r="63" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU62" s="3"/>
+      <c r="BV62" s="3"/>
+      <c r="BW62" s="3"/>
+      <c r="BX62" s="3"/>
+    </row>
+    <row r="63" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B63" s="2" t="s">
         <v>65</v>
       </c>
@@ -8075,34 +8662,34 @@
       <c r="M63" s="3"/>
       <c r="N63" s="3"/>
       <c r="O63" s="3"/>
-      <c r="P63" s="3">
+      <c r="P63" s="3"/>
+      <c r="Q63" s="3"/>
+      <c r="R63" s="3"/>
+      <c r="S63" s="3"/>
+      <c r="T63" s="3">
         <v>250.43899999999999</v>
       </c>
-      <c r="Q63" s="3">
+      <c r="U63" s="3">
         <v>231.96299999999999</v>
       </c>
-      <c r="R63" s="3">
+      <c r="V63" s="3">
         <v>343.91</v>
       </c>
-      <c r="S63" s="3">
+      <c r="W63" s="3">
         <v>303.57400000000001</v>
       </c>
-      <c r="T63" s="3">
+      <c r="X63" s="3">
         <v>296.85199999999998</v>
       </c>
-      <c r="U63" s="3">
+      <c r="Y63" s="3">
         <v>222.119</v>
       </c>
-      <c r="V63" s="3">
+      <c r="Z63" s="3">
         <v>0</v>
       </c>
-      <c r="W63" s="3">
+      <c r="AA63" s="3">
         <v>0</v>
       </c>
-      <c r="X63" s="3"/>
-      <c r="Y63" s="3"/>
-      <c r="Z63" s="3"/>
-      <c r="AA63" s="3"/>
       <c r="AB63" s="3"/>
       <c r="AC63" s="3"/>
       <c r="AD63" s="3"/>
@@ -8148,8 +8735,12 @@
       <c r="BR63" s="3"/>
       <c r="BS63" s="3"/>
       <c r="BT63" s="3"/>
-    </row>
-    <row r="64" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU63" s="3"/>
+      <c r="BV63" s="3"/>
+      <c r="BW63" s="3"/>
+      <c r="BX63" s="3"/>
+    </row>
+    <row r="64" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B64" s="2" t="s">
         <v>66</v>
       </c>
@@ -8166,35 +8757,35 @@
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>
       <c r="O64" s="3"/>
-      <c r="P64" s="3">
+      <c r="P64" s="3"/>
+      <c r="Q64" s="3"/>
+      <c r="R64" s="3"/>
+      <c r="S64" s="3"/>
+      <c r="T64" s="3">
         <f>76.134+46.337+235.145</f>
         <v>357.61599999999999</v>
       </c>
-      <c r="Q64" s="3">
+      <c r="U64" s="3">
         <v>178.536</v>
       </c>
-      <c r="R64" s="3">
+      <c r="V64" s="3">
         <v>104.693</v>
       </c>
-      <c r="S64" s="3">
+      <c r="W64" s="3">
         <v>86.088999999999999</v>
       </c>
-      <c r="T64" s="3">
+      <c r="X64" s="3">
         <v>94.117999999999995</v>
       </c>
-      <c r="U64" s="3">
+      <c r="Y64" s="3">
         <v>88.864000000000004</v>
       </c>
-      <c r="V64" s="3">
+      <c r="Z64" s="3">
         <v>81.606999999999999</v>
       </c>
-      <c r="W64" s="3">
+      <c r="AA64" s="3">
         <v>84.320999999999998</v>
       </c>
-      <c r="X64" s="3"/>
-      <c r="Y64" s="3"/>
-      <c r="Z64" s="3"/>
-      <c r="AA64" s="3"/>
       <c r="AB64" s="3"/>
       <c r="AC64" s="3"/>
       <c r="AD64" s="3"/>
@@ -8240,8 +8831,12 @@
       <c r="BR64" s="3"/>
       <c r="BS64" s="3"/>
       <c r="BT64" s="3"/>
-    </row>
-    <row r="65" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU64" s="3"/>
+      <c r="BV64" s="3"/>
+      <c r="BW64" s="3"/>
+      <c r="BX64" s="3"/>
+    </row>
+    <row r="65" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B65" s="2" t="s">
         <v>67</v>
       </c>
@@ -8258,42 +8853,42 @@
       <c r="M65" s="3"/>
       <c r="N65" s="3"/>
       <c r="O65" s="3"/>
-      <c r="P65" s="3">
-        <f t="shared" ref="P65:T65" si="53">SUM(P62:P64)</f>
+      <c r="P65" s="3"/>
+      <c r="Q65" s="3"/>
+      <c r="R65" s="3"/>
+      <c r="S65" s="3"/>
+      <c r="T65" s="3">
+        <f t="shared" ref="T65:X65" si="56">SUM(T62:T64)</f>
         <v>608.05499999999995</v>
       </c>
-      <c r="Q65" s="3">
-        <f t="shared" si="53"/>
+      <c r="U65" s="3">
+        <f t="shared" si="56"/>
         <v>1663.133</v>
       </c>
-      <c r="R65" s="3">
-        <f t="shared" si="53"/>
+      <c r="V65" s="3">
+        <f t="shared" si="56"/>
         <v>1406.191</v>
       </c>
-      <c r="S65" s="3">
-        <f t="shared" si="53"/>
+      <c r="W65" s="3">
+        <f t="shared" si="56"/>
         <v>1086.9269999999999</v>
       </c>
-      <c r="T65" s="3">
-        <f t="shared" si="53"/>
+      <c r="X65" s="3">
+        <f t="shared" si="56"/>
         <v>1104.3309999999999</v>
       </c>
-      <c r="U65" s="3">
-        <f>SUM(U62:U64)</f>
+      <c r="Y65" s="3">
+        <f>SUM(Y62:Y64)</f>
         <v>957.60700000000008</v>
       </c>
-      <c r="V65" s="3">
-        <f>SUM(V62:V64)</f>
+      <c r="Z65" s="3">
+        <f>SUM(Z62:Z64)</f>
         <v>821.62</v>
       </c>
-      <c r="W65" s="3">
-        <f>SUM(W62:W64)</f>
+      <c r="AA65" s="3">
+        <f>SUM(AA62:AA64)</f>
         <v>894.71199999999999</v>
       </c>
-      <c r="X65" s="3"/>
-      <c r="Y65" s="3"/>
-      <c r="Z65" s="3"/>
-      <c r="AA65" s="3"/>
       <c r="AB65" s="3"/>
       <c r="AC65" s="3"/>
       <c r="AD65" s="3"/>
@@ -8339,8 +8934,12 @@
       <c r="BR65" s="3"/>
       <c r="BS65" s="3"/>
       <c r="BT65" s="3"/>
-    </row>
-    <row r="66" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU65" s="3"/>
+      <c r="BV65" s="3"/>
+      <c r="BW65" s="3"/>
+      <c r="BX65" s="3"/>
+    </row>
+    <row r="66" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B66" s="2" t="s">
         <v>68</v>
       </c>
@@ -8357,42 +8956,42 @@
       <c r="M66" s="3"/>
       <c r="N66" s="3"/>
       <c r="O66" s="3"/>
-      <c r="P66" s="3">
-        <f t="shared" ref="P66:W66" si="54">P61+P65</f>
+      <c r="P66" s="3"/>
+      <c r="Q66" s="3"/>
+      <c r="R66" s="3"/>
+      <c r="S66" s="3"/>
+      <c r="T66" s="3">
+        <f t="shared" ref="T66:AA66" si="57">T61+T65</f>
         <v>1166.972</v>
       </c>
-      <c r="Q66" s="3">
-        <f t="shared" si="54"/>
+      <c r="U66" s="3">
+        <f t="shared" si="57"/>
         <v>2478.4870000000001</v>
       </c>
-      <c r="R66" s="3">
-        <f t="shared" si="54"/>
+      <c r="V66" s="3">
+        <f t="shared" si="57"/>
         <v>2365.59</v>
       </c>
-      <c r="S66" s="3">
-        <f t="shared" si="54"/>
+      <c r="W66" s="3">
+        <f t="shared" si="57"/>
         <v>2102.1669999999999</v>
       </c>
-      <c r="T66" s="3">
-        <f t="shared" si="54"/>
+      <c r="X66" s="3">
+        <f t="shared" si="57"/>
         <v>2006.5309999999999</v>
       </c>
-      <c r="U66" s="3">
-        <f t="shared" si="54"/>
+      <c r="Y66" s="3">
+        <f t="shared" si="57"/>
         <v>1924.4270000000001</v>
       </c>
-      <c r="V66" s="3">
-        <f t="shared" si="54"/>
+      <c r="Z66" s="3">
+        <f t="shared" si="57"/>
         <v>1948.5639999999999</v>
       </c>
-      <c r="W66" s="3">
-        <f t="shared" si="54"/>
+      <c r="AA66" s="3">
+        <f t="shared" si="57"/>
         <v>1893.5819999999999</v>
       </c>
-      <c r="X66" s="3"/>
-      <c r="Y66" s="3"/>
-      <c r="Z66" s="3"/>
-      <c r="AA66" s="3"/>
       <c r="AB66" s="3"/>
       <c r="AC66" s="3"/>
       <c r="AD66" s="3"/>
@@ -8438,8 +9037,12 @@
       <c r="BR66" s="3"/>
       <c r="BS66" s="3"/>
       <c r="BT66" s="3"/>
-    </row>
-    <row r="67" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU66" s="3"/>
+      <c r="BV66" s="3"/>
+      <c r="BW66" s="3"/>
+      <c r="BX66" s="3"/>
+    </row>
+    <row r="67" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B67" s="2" t="s">
         <v>69</v>
       </c>
@@ -8456,34 +9059,34 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-      <c r="P67" s="3">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+      <c r="T67" s="3">
         <v>1218.6209999999999</v>
       </c>
-      <c r="Q67" s="3">
+      <c r="U67" s="3">
         <v>1071.1779999999999</v>
       </c>
-      <c r="R67" s="3">
+      <c r="V67" s="3">
         <v>949.31200000000013</v>
       </c>
-      <c r="S67" s="3">
+      <c r="W67" s="3">
         <v>837.32399999999973</v>
       </c>
-      <c r="T67" s="3">
+      <c r="X67" s="3">
         <v>706.56900000000007</v>
       </c>
-      <c r="U67" s="3">
+      <c r="Y67" s="3">
         <v>1049.9869999999999</v>
       </c>
-      <c r="V67" s="3">
+      <c r="Z67" s="3">
         <v>1351.3230000000001</v>
       </c>
-      <c r="W67" s="3">
+      <c r="AA67" s="3">
         <v>1202.5940000000001</v>
       </c>
-      <c r="X67" s="3"/>
-      <c r="Y67" s="3"/>
-      <c r="Z67" s="3"/>
-      <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
@@ -8529,8 +9132,12 @@
       <c r="BR67" s="3"/>
       <c r="BS67" s="3"/>
       <c r="BT67" s="3"/>
-    </row>
-    <row r="68" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU67" s="3"/>
+      <c r="BV67" s="3"/>
+      <c r="BW67" s="3"/>
+      <c r="BX67" s="3"/>
+    </row>
+    <row r="68" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B68" s="1" t="s">
         <v>70</v>
       </c>
@@ -8547,42 +9154,42 @@
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
       <c r="O68" s="3"/>
-      <c r="P68" s="24">
-        <f t="shared" ref="P68:W68" si="55">P67+P66</f>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="3"/>
+      <c r="R68" s="3"/>
+      <c r="S68" s="3"/>
+      <c r="T68" s="24">
+        <f t="shared" ref="T68:AA68" si="58">T67+T66</f>
         <v>2385.5929999999998</v>
       </c>
-      <c r="Q68" s="24">
-        <f t="shared" si="55"/>
+      <c r="U68" s="24">
+        <f t="shared" si="58"/>
         <v>3549.665</v>
       </c>
-      <c r="R68" s="24">
-        <f t="shared" si="55"/>
+      <c r="V68" s="24">
+        <f t="shared" si="58"/>
         <v>3314.902</v>
       </c>
-      <c r="S68" s="24">
-        <f t="shared" si="55"/>
+      <c r="W68" s="24">
+        <f t="shared" si="58"/>
         <v>2939.4909999999995</v>
       </c>
-      <c r="T68" s="24">
-        <f t="shared" si="55"/>
+      <c r="X68" s="24">
+        <f t="shared" si="58"/>
         <v>2713.1</v>
       </c>
-      <c r="U68" s="24">
-        <f t="shared" si="55"/>
+      <c r="Y68" s="24">
+        <f t="shared" si="58"/>
         <v>2974.4139999999998</v>
       </c>
-      <c r="V68" s="24">
-        <f t="shared" si="55"/>
+      <c r="Z68" s="24">
+        <f t="shared" si="58"/>
         <v>3299.8869999999997</v>
       </c>
-      <c r="W68" s="24">
-        <f t="shared" si="55"/>
+      <c r="AA68" s="24">
+        <f t="shared" si="58"/>
         <v>3096.1759999999999</v>
       </c>
-      <c r="X68" s="3"/>
-      <c r="Y68" s="3"/>
-      <c r="Z68" s="3"/>
-      <c r="AA68" s="3"/>
       <c r="AB68" s="3"/>
       <c r="AC68" s="3"/>
       <c r="AD68" s="3"/>
@@ -8628,8 +9235,12 @@
       <c r="BR68" s="3"/>
       <c r="BS68" s="3"/>
       <c r="BT68" s="3"/>
-    </row>
-    <row r="69" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU68" s="3"/>
+      <c r="BV68" s="3"/>
+      <c r="BW68" s="3"/>
+      <c r="BX68" s="3"/>
+    </row>
+    <row r="69" spans="1:76" x14ac:dyDescent="0.2">
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -8700,8 +9311,12 @@
       <c r="BR69" s="3"/>
       <c r="BS69" s="3"/>
       <c r="BT69" s="3"/>
-    </row>
-    <row r="70" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU69" s="3"/>
+      <c r="BV69" s="3"/>
+      <c r="BW69" s="3"/>
+      <c r="BX69" s="3"/>
+    </row>
+    <row r="70" spans="1:76" x14ac:dyDescent="0.2">
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -8772,8 +9387,12 @@
       <c r="BR70" s="3"/>
       <c r="BS70" s="3"/>
       <c r="BT70" s="3"/>
-    </row>
-    <row r="71" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU70" s="3"/>
+      <c r="BV70" s="3"/>
+      <c r="BW70" s="3"/>
+      <c r="BX70" s="3"/>
+    </row>
+    <row r="71" spans="1:76" x14ac:dyDescent="0.2">
       <c r="A71" s="23" t="s">
         <v>9</v>
       </c>
@@ -8850,8 +9469,12 @@
       <c r="BR71" s="3"/>
       <c r="BS71" s="3"/>
       <c r="BT71" s="3"/>
-    </row>
-    <row r="72" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU71" s="3"/>
+      <c r="BV71" s="3"/>
+      <c r="BW71" s="3"/>
+      <c r="BX71" s="3"/>
+    </row>
+    <row r="72" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B72" s="2" t="s">
         <v>72</v>
       </c>
@@ -8868,34 +9491,34 @@
       <c r="M72" s="3"/>
       <c r="N72" s="3"/>
       <c r="O72" s="3"/>
-      <c r="P72" s="3">
-        <f t="shared" ref="P72:U72" si="56">P28</f>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="3"/>
+      <c r="R72" s="3"/>
+      <c r="S72" s="3"/>
+      <c r="T72" s="3">
+        <f t="shared" ref="T72:Y72" si="59">T28</f>
         <v>78.80800000000022</v>
       </c>
-      <c r="Q72" s="3">
-        <f t="shared" si="56"/>
+      <c r="U72" s="3">
+        <f t="shared" si="59"/>
         <v>44.960000000000633</v>
       </c>
-      <c r="R72" s="3">
-        <f t="shared" si="56"/>
+      <c r="V72" s="3">
+        <f t="shared" si="59"/>
         <v>-108.95400000000021</v>
       </c>
-      <c r="S72" s="3">
-        <f t="shared" si="56"/>
+      <c r="W72" s="3">
+        <f t="shared" si="59"/>
         <v>270.06599999999986</v>
       </c>
-      <c r="T72" s="3">
-        <f t="shared" si="56"/>
+      <c r="X72" s="3">
+        <f t="shared" si="59"/>
         <v>10.385000000000616</v>
       </c>
-      <c r="U72" s="3">
-        <f t="shared" si="56"/>
+      <c r="Y72" s="3">
+        <f t="shared" si="59"/>
         <v>335.41299999999933</v>
       </c>
-      <c r="V72" s="3"/>
-      <c r="W72" s="3"/>
-      <c r="X72" s="3"/>
-      <c r="Y72" s="3"/>
       <c r="Z72" s="3"/>
       <c r="AA72" s="3"/>
       <c r="AB72" s="3"/>
@@ -8943,8 +9566,12 @@
       <c r="BR72" s="3"/>
       <c r="BS72" s="3"/>
       <c r="BT72" s="3"/>
-    </row>
-    <row r="73" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU72" s="3"/>
+      <c r="BV72" s="3"/>
+      <c r="BW72" s="3"/>
+      <c r="BX72" s="3"/>
+    </row>
+    <row r="73" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B73" s="2" t="s">
         <v>73</v>
       </c>
@@ -8961,28 +9588,28 @@
       <c r="M73" s="3"/>
       <c r="N73" s="3"/>
       <c r="O73" s="3"/>
-      <c r="P73" s="3">
+      <c r="P73" s="3"/>
+      <c r="Q73" s="3"/>
+      <c r="R73" s="3"/>
+      <c r="S73" s="3"/>
+      <c r="T73" s="3">
         <v>178.03</v>
       </c>
-      <c r="Q73" s="3">
+      <c r="U73" s="3">
         <v>173.625</v>
       </c>
-      <c r="R73" s="3">
+      <c r="V73" s="3">
         <v>166.28100000000001</v>
       </c>
-      <c r="S73" s="3">
+      <c r="W73" s="3">
         <v>144.035</v>
       </c>
-      <c r="T73" s="3">
+      <c r="X73" s="3">
         <v>132.24299999999999</v>
       </c>
-      <c r="U73" s="3">
+      <c r="Y73" s="3">
         <v>141.10400000000001</v>
       </c>
-      <c r="V73" s="3"/>
-      <c r="W73" s="3"/>
-      <c r="X73" s="3"/>
-      <c r="Y73" s="3"/>
       <c r="Z73" s="3"/>
       <c r="AA73" s="3"/>
       <c r="AB73" s="3"/>
@@ -9030,8 +9657,12 @@
       <c r="BR73" s="3"/>
       <c r="BS73" s="3"/>
       <c r="BT73" s="3"/>
-    </row>
-    <row r="74" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU73" s="3"/>
+      <c r="BV73" s="3"/>
+      <c r="BW73" s="3"/>
+      <c r="BX73" s="3"/>
+    </row>
+    <row r="74" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B74" s="2" t="s">
         <v>74</v>
       </c>
@@ -9048,28 +9679,28 @@
       <c r="M74" s="3"/>
       <c r="N74" s="3"/>
       <c r="O74" s="3"/>
-      <c r="P74" s="3">
+      <c r="P74" s="3"/>
+      <c r="Q74" s="3"/>
+      <c r="R74" s="3"/>
+      <c r="S74" s="3"/>
+      <c r="T74" s="3">
         <v>11.58</v>
       </c>
-      <c r="Q74" s="3">
+      <c r="U74" s="3">
         <v>22.364000000000001</v>
       </c>
-      <c r="R74" s="3">
+      <c r="V74" s="3">
         <v>72.936999999999998</v>
       </c>
-      <c r="S74" s="3">
+      <c r="W74" s="3">
         <v>12.1</v>
       </c>
-      <c r="T74" s="3">
+      <c r="X74" s="3">
         <v>14.031000000000001</v>
       </c>
-      <c r="U74" s="3">
+      <c r="Y74" s="3">
         <v>8.2889999999999997</v>
       </c>
-      <c r="V74" s="3"/>
-      <c r="W74" s="3"/>
-      <c r="X74" s="3"/>
-      <c r="Y74" s="3"/>
       <c r="Z74" s="3"/>
       <c r="AA74" s="3"/>
       <c r="AB74" s="3"/>
@@ -9117,8 +9748,12 @@
       <c r="BR74" s="3"/>
       <c r="BS74" s="3"/>
       <c r="BT74" s="3"/>
-    </row>
-    <row r="75" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU74" s="3"/>
+      <c r="BV74" s="3"/>
+      <c r="BW74" s="3"/>
+      <c r="BX74" s="3"/>
+    </row>
+    <row r="75" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B75" s="2" t="s">
         <v>75</v>
       </c>
@@ -9135,28 +9770,28 @@
       <c r="M75" s="3"/>
       <c r="N75" s="3"/>
       <c r="O75" s="3"/>
-      <c r="P75" s="3">
+      <c r="P75" s="3"/>
+      <c r="Q75" s="3"/>
+      <c r="R75" s="3"/>
+      <c r="S75" s="3"/>
+      <c r="T75" s="3">
         <v>6.02</v>
       </c>
-      <c r="Q75" s="3">
+      <c r="U75" s="3">
         <v>6.298</v>
       </c>
-      <c r="R75" s="3">
+      <c r="V75" s="3">
         <v>16.353000000000002</v>
       </c>
-      <c r="S75" s="3">
+      <c r="W75" s="3">
         <v>5.0199999999999996</v>
       </c>
-      <c r="T75" s="3">
+      <c r="X75" s="3">
         <v>0.55200000000000005</v>
       </c>
-      <c r="U75" s="3">
+      <c r="Y75" s="3">
         <v>6.4080000000000004</v>
       </c>
-      <c r="V75" s="3"/>
-      <c r="W75" s="3"/>
-      <c r="X75" s="3"/>
-      <c r="Y75" s="3"/>
       <c r="Z75" s="3"/>
       <c r="AA75" s="3"/>
       <c r="AB75" s="3"/>
@@ -9204,8 +9839,12 @@
       <c r="BR75" s="3"/>
       <c r="BS75" s="3"/>
       <c r="BT75" s="3"/>
-    </row>
-    <row r="76" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU75" s="3"/>
+      <c r="BV75" s="3"/>
+      <c r="BW75" s="3"/>
+      <c r="BX75" s="3"/>
+    </row>
+    <row r="76" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B76" s="2" t="s">
         <v>76</v>
       </c>
@@ -9222,28 +9861,28 @@
       <c r="M76" s="3"/>
       <c r="N76" s="3"/>
       <c r="O76" s="3"/>
-      <c r="P76" s="3">
+      <c r="P76" s="3"/>
+      <c r="Q76" s="3"/>
+      <c r="R76" s="3"/>
+      <c r="S76" s="3"/>
+      <c r="T76" s="3">
         <v>5.9640000000000004</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="U76" s="3">
         <v>9.15</v>
       </c>
-      <c r="R76" s="3">
+      <c r="V76" s="3">
         <v>23.986000000000001</v>
       </c>
-      <c r="S76" s="3">
+      <c r="W76" s="3">
         <v>-31.922000000000001</v>
       </c>
-      <c r="T76" s="3">
+      <c r="X76" s="3">
         <v>11.5</v>
       </c>
-      <c r="U76" s="3">
+      <c r="Y76" s="3">
         <v>-4.7430000000000003</v>
       </c>
-      <c r="V76" s="3"/>
-      <c r="W76" s="3"/>
-      <c r="X76" s="3"/>
-      <c r="Y76" s="3"/>
       <c r="Z76" s="3"/>
       <c r="AA76" s="3"/>
       <c r="AB76" s="3"/>
@@ -9291,8 +9930,12 @@
       <c r="BR76" s="3"/>
       <c r="BS76" s="3"/>
       <c r="BT76" s="3"/>
-    </row>
-    <row r="77" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU76" s="3"/>
+      <c r="BV76" s="3"/>
+      <c r="BW76" s="3"/>
+      <c r="BX76" s="3"/>
+    </row>
+    <row r="77" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B77" s="2" t="s">
         <v>78</v>
       </c>
@@ -9309,28 +9952,28 @@
       <c r="M77" s="3"/>
       <c r="N77" s="3"/>
       <c r="O77" s="3"/>
-      <c r="P77" s="3">
+      <c r="P77" s="3"/>
+      <c r="Q77" s="3"/>
+      <c r="R77" s="3"/>
+      <c r="S77" s="3"/>
+      <c r="T77" s="3">
         <v>21.754999999999999</v>
       </c>
-      <c r="Q77" s="3">
+      <c r="U77" s="3">
         <v>14.007</v>
       </c>
-      <c r="R77" s="3">
+      <c r="V77" s="3">
         <v>18.681999999999999</v>
       </c>
-      <c r="S77" s="3">
+      <c r="W77" s="3">
         <v>29.303999999999998</v>
       </c>
-      <c r="T77" s="3">
+      <c r="X77" s="3">
         <v>28.995000000000001</v>
       </c>
-      <c r="U77" s="3">
+      <c r="Y77" s="3">
         <v>40.122</v>
       </c>
-      <c r="V77" s="3"/>
-      <c r="W77" s="3"/>
-      <c r="X77" s="3"/>
-      <c r="Y77" s="3"/>
       <c r="Z77" s="3"/>
       <c r="AA77" s="3"/>
       <c r="AB77" s="3"/>
@@ -9378,8 +10021,12 @@
       <c r="BR77" s="3"/>
       <c r="BS77" s="3"/>
       <c r="BT77" s="3"/>
-    </row>
-    <row r="78" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU77" s="3"/>
+      <c r="BV77" s="3"/>
+      <c r="BW77" s="3"/>
+      <c r="BX77" s="3"/>
+    </row>
+    <row r="78" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B78" s="2" t="s">
         <v>79</v>
       </c>
@@ -9396,28 +10043,28 @@
       <c r="M78" s="3"/>
       <c r="N78" s="3"/>
       <c r="O78" s="3"/>
-      <c r="P78" s="3">
+      <c r="P78" s="3"/>
+      <c r="Q78" s="3"/>
+      <c r="R78" s="3"/>
+      <c r="S78" s="3"/>
+      <c r="T78" s="3">
         <v>0</v>
       </c>
-      <c r="Q78" s="3">
+      <c r="U78" s="3">
         <v>0</v>
       </c>
-      <c r="R78" s="3">
+      <c r="V78" s="3">
         <v>0</v>
       </c>
-      <c r="S78" s="3">
+      <c r="W78" s="3">
         <v>5.3470000000000004</v>
       </c>
-      <c r="T78" s="3">
+      <c r="X78" s="3">
         <v>-5.1999999999999998E-2</v>
       </c>
-      <c r="U78" s="3">
+      <c r="Y78" s="3">
         <v>1.9750000000000001</v>
       </c>
-      <c r="V78" s="3"/>
-      <c r="W78" s="3"/>
-      <c r="X78" s="3"/>
-      <c r="Y78" s="3"/>
       <c r="Z78" s="3"/>
       <c r="AA78" s="3"/>
       <c r="AB78" s="3"/>
@@ -9465,8 +10112,12 @@
       <c r="BR78" s="3"/>
       <c r="BS78" s="3"/>
       <c r="BT78" s="3"/>
-    </row>
-    <row r="79" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU78" s="3"/>
+      <c r="BV78" s="3"/>
+      <c r="BW78" s="3"/>
+      <c r="BX78" s="3"/>
+    </row>
+    <row r="79" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B79" s="2" t="s">
         <v>110</v>
       </c>
@@ -9483,28 +10134,28 @@
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
       <c r="O79" s="3"/>
-      <c r="P79" s="3">
+      <c r="P79" s="3"/>
+      <c r="Q79" s="3"/>
+      <c r="R79" s="3"/>
+      <c r="S79" s="3"/>
+      <c r="T79" s="3">
         <v>-21.32</v>
-      </c>
-      <c r="Q79" s="3">
-        <v>0</v>
-      </c>
-      <c r="R79" s="3">
-        <v>0</v>
-      </c>
-      <c r="S79" s="3">
-        <v>0</v>
-      </c>
-      <c r="T79" s="3">
-        <v>0</v>
       </c>
       <c r="U79" s="3">
         <v>0</v>
       </c>
-      <c r="V79" s="3"/>
-      <c r="W79" s="3"/>
-      <c r="X79" s="3"/>
-      <c r="Y79" s="3"/>
+      <c r="V79" s="3">
+        <v>0</v>
+      </c>
+      <c r="W79" s="3">
+        <v>0</v>
+      </c>
+      <c r="X79" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="3">
+        <v>0</v>
+      </c>
       <c r="Z79" s="3"/>
       <c r="AA79" s="3"/>
       <c r="AB79" s="3"/>
@@ -9552,8 +10203,12 @@
       <c r="BR79" s="3"/>
       <c r="BS79" s="3"/>
       <c r="BT79" s="3"/>
-    </row>
-    <row r="80" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BU79" s="3"/>
+      <c r="BV79" s="3"/>
+      <c r="BW79" s="3"/>
+      <c r="BX79" s="3"/>
+    </row>
+    <row r="80" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B80" s="28" t="s">
         <v>80</v>
       </c>
@@ -9627,8 +10282,12 @@
       <c r="BR80" s="3"/>
       <c r="BS80" s="3"/>
       <c r="BT80" s="3"/>
-    </row>
-    <row r="81" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU80" s="3"/>
+      <c r="BV80" s="3"/>
+      <c r="BW80" s="3"/>
+      <c r="BX80" s="3"/>
+    </row>
+    <row r="81" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B81" s="2" t="s">
         <v>82</v>
       </c>
@@ -9645,28 +10304,28 @@
       <c r="M81" s="3"/>
       <c r="N81" s="3"/>
       <c r="O81" s="3"/>
-      <c r="P81" s="3">
+      <c r="P81" s="3"/>
+      <c r="Q81" s="3"/>
+      <c r="R81" s="3"/>
+      <c r="S81" s="3"/>
+      <c r="T81" s="3">
         <v>-23.82</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="U81" s="3">
         <v>2.27</v>
       </c>
-      <c r="R81" s="3">
+      <c r="V81" s="3">
         <v>33.311999999999998</v>
       </c>
-      <c r="S81" s="3">
+      <c r="W81" s="3">
         <v>-123.221</v>
       </c>
-      <c r="T81" s="3">
+      <c r="X81" s="3">
         <v>18.504999999999999</v>
       </c>
-      <c r="U81" s="3">
+      <c r="Y81" s="3">
         <v>35.042999999999999</v>
       </c>
-      <c r="V81" s="3"/>
-      <c r="W81" s="3"/>
-      <c r="X81" s="3"/>
-      <c r="Y81" s="3"/>
       <c r="Z81" s="3"/>
       <c r="AA81" s="3"/>
       <c r="AB81" s="3"/>
@@ -9714,8 +10373,12 @@
       <c r="BR81" s="3"/>
       <c r="BS81" s="3"/>
       <c r="BT81" s="3"/>
-    </row>
-    <row r="82" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU81" s="3"/>
+      <c r="BV81" s="3"/>
+      <c r="BW81" s="3"/>
+      <c r="BX81" s="3"/>
+    </row>
+    <row r="82" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B82" s="2" t="s">
         <v>84</v>
       </c>
@@ -9732,28 +10395,28 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-      <c r="P82" s="3">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+      <c r="T82" s="3">
         <v>63.155000000000001</v>
       </c>
-      <c r="Q82" s="3">
+      <c r="U82" s="3">
         <v>10.821</v>
       </c>
-      <c r="R82" s="3">
+      <c r="V82" s="3">
         <v>186.74700000000001</v>
       </c>
-      <c r="S82" s="3">
+      <c r="W82" s="3">
         <v>77.91</v>
       </c>
-      <c r="T82" s="3">
+      <c r="X82" s="3">
         <v>-115.152</v>
       </c>
-      <c r="U82" s="3">
+      <c r="Y82" s="3">
         <v>82.924999999999997</v>
       </c>
-      <c r="V82" s="3"/>
-      <c r="W82" s="3"/>
-      <c r="X82" s="3"/>
-      <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
@@ -9801,8 +10464,12 @@
       <c r="BR82" s="3"/>
       <c r="BS82" s="3"/>
       <c r="BT82" s="3"/>
-    </row>
-    <row r="83" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU82" s="3"/>
+      <c r="BV82" s="3"/>
+      <c r="BW82" s="3"/>
+      <c r="BX82" s="3"/>
+    </row>
+    <row r="83" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B83" s="2" t="s">
         <v>83</v>
       </c>
@@ -9819,28 +10486,28 @@
       <c r="M83" s="3"/>
       <c r="N83" s="3"/>
       <c r="O83" s="3"/>
-      <c r="P83" s="3">
+      <c r="P83" s="3"/>
+      <c r="Q83" s="3"/>
+      <c r="R83" s="3"/>
+      <c r="S83" s="3"/>
+      <c r="T83" s="3">
         <v>0</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="U83" s="3">
         <v>46.442</v>
       </c>
-      <c r="R83" s="3">
+      <c r="V83" s="3">
         <v>-55.7</v>
       </c>
-      <c r="S83" s="3">
+      <c r="W83" s="3">
         <v>-93.826999999999998</v>
       </c>
-      <c r="T83" s="3">
+      <c r="X83" s="3">
         <v>-18.495000000000001</v>
       </c>
-      <c r="U83" s="3">
+      <c r="Y83" s="3">
         <v>-55.646000000000001</v>
       </c>
-      <c r="V83" s="3"/>
-      <c r="W83" s="3"/>
-      <c r="X83" s="3"/>
-      <c r="Y83" s="3"/>
       <c r="Z83" s="3"/>
       <c r="AA83" s="3"/>
       <c r="AB83" s="3"/>
@@ -9888,8 +10555,12 @@
       <c r="BR83" s="3"/>
       <c r="BS83" s="3"/>
       <c r="BT83" s="3"/>
-    </row>
-    <row r="84" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU83" s="3"/>
+      <c r="BV83" s="3"/>
+      <c r="BW83" s="3"/>
+      <c r="BX83" s="3"/>
+    </row>
+    <row r="84" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B84" s="2" t="s">
         <v>85</v>
       </c>
@@ -9906,28 +10577,28 @@
       <c r="M84" s="3"/>
       <c r="N84" s="3"/>
       <c r="O84" s="3"/>
-      <c r="P84" s="3">
+      <c r="P84" s="3"/>
+      <c r="Q84" s="3"/>
+      <c r="R84" s="3"/>
+      <c r="S84" s="3"/>
+      <c r="T84" s="3">
         <v>5.4089999999999998</v>
       </c>
-      <c r="Q84" s="3">
+      <c r="U84" s="3">
         <v>-5.4729999999999999</v>
       </c>
-      <c r="R84" s="3">
+      <c r="V84" s="3">
         <v>10.753</v>
       </c>
-      <c r="S84" s="3">
+      <c r="W84" s="3">
         <v>-3.0859999999999999</v>
       </c>
-      <c r="T84" s="3">
+      <c r="X84" s="3">
         <v>-7.39</v>
       </c>
-      <c r="U84" s="3">
+      <c r="Y84" s="3">
         <v>35.805999999999997</v>
       </c>
-      <c r="V84" s="3"/>
-      <c r="W84" s="3"/>
-      <c r="X84" s="3"/>
-      <c r="Y84" s="3"/>
       <c r="Z84" s="3"/>
       <c r="AA84" s="3"/>
       <c r="AB84" s="3"/>
@@ -9975,8 +10646,12 @@
       <c r="BR84" s="3"/>
       <c r="BS84" s="3"/>
       <c r="BT84" s="3"/>
-    </row>
-    <row r="85" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU84" s="3"/>
+      <c r="BV84" s="3"/>
+      <c r="BW84" s="3"/>
+      <c r="BX84" s="3"/>
+    </row>
+    <row r="85" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B85" s="2" t="s">
         <v>56</v>
       </c>
@@ -9993,28 +10668,28 @@
       <c r="M85" s="3"/>
       <c r="N85" s="3"/>
       <c r="O85" s="3"/>
-      <c r="P85" s="3">
+      <c r="P85" s="3"/>
+      <c r="Q85" s="3"/>
+      <c r="R85" s="3"/>
+      <c r="S85" s="3"/>
+      <c r="T85" s="3">
         <v>33.302</v>
       </c>
-      <c r="Q85" s="3">
+      <c r="U85" s="3">
         <v>-20.172999999999998</v>
       </c>
-      <c r="R85" s="3">
+      <c r="V85" s="3">
         <v>38.631999999999998</v>
       </c>
-      <c r="S85" s="3">
+      <c r="W85" s="3">
         <v>0.39600000000000002</v>
       </c>
-      <c r="T85" s="3">
+      <c r="X85" s="3">
         <v>-86.923000000000002</v>
       </c>
-      <c r="U85" s="3">
+      <c r="Y85" s="3">
         <v>33.622999999999998</v>
       </c>
-      <c r="V85" s="3"/>
-      <c r="W85" s="3"/>
-      <c r="X85" s="3"/>
-      <c r="Y85" s="3"/>
       <c r="Z85" s="3"/>
       <c r="AA85" s="3"/>
       <c r="AB85" s="3"/>
@@ -10062,8 +10737,12 @@
       <c r="BR85" s="3"/>
       <c r="BS85" s="3"/>
       <c r="BT85" s="3"/>
-    </row>
-    <row r="86" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU85" s="3"/>
+      <c r="BV85" s="3"/>
+      <c r="BW85" s="3"/>
+      <c r="BX85" s="3"/>
+    </row>
+    <row r="86" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B86" s="2" t="s">
         <v>66</v>
       </c>
@@ -10080,28 +10759,28 @@
       <c r="M86" s="3"/>
       <c r="N86" s="3"/>
       <c r="O86" s="3"/>
-      <c r="P86" s="3">
+      <c r="P86" s="3"/>
+      <c r="Q86" s="3"/>
+      <c r="R86" s="3"/>
+      <c r="S86" s="3"/>
+      <c r="T86" s="3">
         <v>-5.9320000000000004</v>
       </c>
-      <c r="Q86" s="3">
+      <c r="U86" s="3">
         <v>-3.6419999999999999</v>
       </c>
-      <c r="R86" s="3">
+      <c r="V86" s="3">
         <v>1.889</v>
       </c>
-      <c r="S86" s="3">
+      <c r="W86" s="3">
         <v>-14.34</v>
       </c>
-      <c r="T86" s="3">
+      <c r="X86" s="3">
         <v>9.4580000000000002</v>
       </c>
-      <c r="U86" s="3">
+      <c r="Y86" s="3">
         <v>-6.8970000000000002</v>
       </c>
-      <c r="V86" s="3"/>
-      <c r="W86" s="3"/>
-      <c r="X86" s="3"/>
-      <c r="Y86" s="3"/>
       <c r="Z86" s="3"/>
       <c r="AA86" s="3"/>
       <c r="AB86" s="3"/>
@@ -10149,8 +10828,12 @@
       <c r="BR86" s="3"/>
       <c r="BS86" s="3"/>
       <c r="BT86" s="3"/>
-    </row>
-    <row r="87" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU86" s="3"/>
+      <c r="BV86" s="3"/>
+      <c r="BW86" s="3"/>
+      <c r="BX86" s="3"/>
+    </row>
+    <row r="87" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B87" s="2" t="s">
         <v>81</v>
       </c>
@@ -10167,34 +10850,34 @@
       <c r="M87" s="3"/>
       <c r="N87" s="3"/>
       <c r="O87" s="3"/>
-      <c r="P87" s="3">
-        <f t="shared" ref="P87:T87" si="57">SUM(P81:P86)</f>
+      <c r="P87" s="3"/>
+      <c r="Q87" s="3"/>
+      <c r="R87" s="3"/>
+      <c r="S87" s="3"/>
+      <c r="T87" s="3">
+        <f t="shared" ref="T87:X87" si="60">SUM(T81:T86)</f>
         <v>72.11399999999999</v>
       </c>
-      <c r="Q87" s="3">
-        <f t="shared" si="57"/>
+      <c r="U87" s="3">
+        <f t="shared" si="60"/>
         <v>30.245000000000001</v>
       </c>
-      <c r="R87" s="3">
-        <f t="shared" si="57"/>
+      <c r="V87" s="3">
+        <f t="shared" si="60"/>
         <v>215.63300000000004</v>
       </c>
-      <c r="S87" s="3">
-        <f t="shared" si="57"/>
+      <c r="W87" s="3">
+        <f t="shared" si="60"/>
         <v>-156.16800000000003</v>
       </c>
-      <c r="T87" s="3">
-        <f t="shared" si="57"/>
+      <c r="X87" s="3">
+        <f t="shared" si="60"/>
         <v>-199.99700000000001</v>
       </c>
-      <c r="U87" s="3">
-        <f>SUM(U81:U86)</f>
+      <c r="Y87" s="3">
+        <f>SUM(Y81:Y86)</f>
         <v>124.85399999999997</v>
       </c>
-      <c r="V87" s="3"/>
-      <c r="W87" s="3"/>
-      <c r="X87" s="3"/>
-      <c r="Y87" s="3"/>
       <c r="Z87" s="3"/>
       <c r="AA87" s="3"/>
       <c r="AB87" s="3"/>
@@ -10242,8 +10925,12 @@
       <c r="BR87" s="3"/>
       <c r="BS87" s="3"/>
       <c r="BT87" s="3"/>
-    </row>
-    <row r="88" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU87" s="3"/>
+      <c r="BV87" s="3"/>
+      <c r="BW87" s="3"/>
+      <c r="BX87" s="3"/>
+    </row>
+    <row r="88" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B88" s="1" t="s">
         <v>77</v>
       </c>
@@ -10260,34 +10947,34 @@
       <c r="M88" s="3"/>
       <c r="N88" s="3"/>
       <c r="O88" s="3"/>
-      <c r="P88" s="24">
-        <f>P72+SUM(P73:P79)+P87</f>
+      <c r="P88" s="3"/>
+      <c r="Q88" s="3"/>
+      <c r="R88" s="3"/>
+      <c r="S88" s="3"/>
+      <c r="T88" s="24">
+        <f>T72+SUM(T73:T79)+T87</f>
         <v>352.95100000000019</v>
       </c>
-      <c r="Q88" s="24">
-        <f t="shared" ref="Q88:U88" si="58">Q72+SUM(Q73:Q79)+Q87</f>
+      <c r="U88" s="24">
+        <f t="shared" ref="U88:Y88" si="61">U72+SUM(U73:U79)+U87</f>
         <v>300.64900000000068</v>
       </c>
-      <c r="R88" s="24">
-        <f t="shared" si="58"/>
+      <c r="V88" s="24">
+        <f t="shared" si="61"/>
         <v>404.91799999999989</v>
       </c>
-      <c r="S88" s="24">
-        <f t="shared" si="58"/>
+      <c r="W88" s="24">
+        <f t="shared" si="61"/>
         <v>277.78199999999981</v>
       </c>
-      <c r="T88" s="24">
-        <f t="shared" si="58"/>
+      <c r="X88" s="24">
+        <f t="shared" si="61"/>
         <v>-2.3429999999993925</v>
       </c>
-      <c r="U88" s="24">
-        <f t="shared" si="58"/>
+      <c r="Y88" s="24">
+        <f t="shared" si="61"/>
         <v>653.42199999999923</v>
       </c>
-      <c r="V88" s="3"/>
-      <c r="W88" s="3"/>
-      <c r="X88" s="3"/>
-      <c r="Y88" s="3"/>
       <c r="Z88" s="3"/>
       <c r="AA88" s="3"/>
       <c r="AB88" s="3"/>
@@ -10335,33 +11022,33 @@
       <c r="BR88" s="3"/>
       <c r="BS88" s="3"/>
       <c r="BT88" s="3"/>
-    </row>
-    <row r="89" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU88" s="3"/>
+      <c r="BV88" s="3"/>
+      <c r="BW88" s="3"/>
+      <c r="BX88" s="3"/>
+    </row>
+    <row r="89" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B89" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="P89" s="3">
+      <c r="T89" s="3">
         <v>-152.393</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="U89" s="3">
         <v>-202.78399999999999</v>
       </c>
-      <c r="R89" s="3">
+      <c r="V89" s="3">
         <v>-101.91</v>
       </c>
-      <c r="S89" s="3">
+      <c r="W89" s="3">
         <v>-96.975999999999999</v>
       </c>
-      <c r="T89" s="3">
+      <c r="X89" s="3">
         <v>-164.566</v>
       </c>
-      <c r="U89" s="3">
+      <c r="Y89" s="3">
         <v>-157.797</v>
       </c>
-      <c r="V89" s="3"/>
-      <c r="W89" s="3"/>
-      <c r="X89" s="3"/>
-      <c r="Y89" s="3"/>
       <c r="Z89" s="3"/>
       <c r="AA89" s="3"/>
       <c r="AB89" s="3"/>
@@ -10409,8 +11096,12 @@
       <c r="BR89" s="3"/>
       <c r="BS89" s="3"/>
       <c r="BT89" s="3"/>
-    </row>
-    <row r="90" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU89" s="3"/>
+      <c r="BV89" s="3"/>
+      <c r="BW89" s="3"/>
+      <c r="BX89" s="3"/>
+    </row>
+    <row r="90" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B90" s="2" t="s">
         <v>88</v>
       </c>
@@ -10427,28 +11118,28 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-      <c r="P90" s="3">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+      <c r="T90" s="3">
         <v>0</v>
       </c>
-      <c r="Q90" s="3">
+      <c r="U90" s="3">
         <v>0</v>
       </c>
-      <c r="R90" s="3">
+      <c r="V90" s="3">
         <v>0</v>
       </c>
-      <c r="S90" s="3">
+      <c r="W90" s="3">
         <v>0</v>
       </c>
-      <c r="T90" s="3">
+      <c r="X90" s="3">
         <v>11.891</v>
       </c>
-      <c r="U90" s="3">
+      <c r="Y90" s="3">
         <v>0.61499999999999999</v>
       </c>
-      <c r="V90" s="3"/>
-      <c r="W90" s="3"/>
-      <c r="X90" s="3"/>
-      <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
@@ -10496,8 +11187,12 @@
       <c r="BR90" s="3"/>
       <c r="BS90" s="3"/>
       <c r="BT90" s="3"/>
-    </row>
-    <row r="91" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU90" s="3"/>
+      <c r="BV90" s="3"/>
+      <c r="BW90" s="3"/>
+      <c r="BX90" s="3"/>
+    </row>
+    <row r="91" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B91" s="2" t="s">
         <v>89</v>
       </c>
@@ -10514,28 +11209,28 @@
       <c r="M91" s="3"/>
       <c r="N91" s="3"/>
       <c r="O91" s="3"/>
-      <c r="P91" s="3">
+      <c r="P91" s="3"/>
+      <c r="Q91" s="3"/>
+      <c r="R91" s="3"/>
+      <c r="S91" s="3"/>
+      <c r="T91" s="3">
         <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>50</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>12</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3"/>
-      <c r="W91" s="3"/>
-      <c r="X91" s="3"/>
-      <c r="Y91" s="3"/>
+      <c r="V91" s="3">
+        <v>50</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>12</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
       <c r="Z91" s="3"/>
       <c r="AA91" s="3"/>
       <c r="AB91" s="3"/>
@@ -10583,8 +11278,12 @@
       <c r="BR91" s="3"/>
       <c r="BS91" s="3"/>
       <c r="BT91" s="3"/>
-    </row>
-    <row r="92" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU91" s="3"/>
+      <c r="BV91" s="3"/>
+      <c r="BW91" s="3"/>
+      <c r="BX91" s="3"/>
+    </row>
+    <row r="92" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B92" s="1" t="s">
         <v>90</v>
       </c>
@@ -10601,34 +11300,34 @@
       <c r="M92" s="3"/>
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
-      <c r="P92" s="24">
-        <f t="shared" ref="P92:T92" si="59">SUM(P89:P91)</f>
+      <c r="P92" s="3"/>
+      <c r="Q92" s="3"/>
+      <c r="R92" s="3"/>
+      <c r="S92" s="3"/>
+      <c r="T92" s="24">
+        <f t="shared" ref="T92:X92" si="62">SUM(T89:T91)</f>
         <v>-152.393</v>
       </c>
-      <c r="Q92" s="24">
-        <f t="shared" si="59"/>
+      <c r="U92" s="24">
+        <f t="shared" si="62"/>
         <v>-202.78399999999999</v>
       </c>
-      <c r="R92" s="24">
-        <f t="shared" si="59"/>
+      <c r="V92" s="24">
+        <f t="shared" si="62"/>
         <v>-51.91</v>
       </c>
-      <c r="S92" s="24">
-        <f t="shared" si="59"/>
+      <c r="W92" s="24">
+        <f t="shared" si="62"/>
         <v>-96.975999999999999</v>
       </c>
-      <c r="T92" s="24">
-        <f t="shared" si="59"/>
+      <c r="X92" s="24">
+        <f t="shared" si="62"/>
         <v>-140.67500000000001</v>
       </c>
-      <c r="U92" s="24">
-        <f>SUM(U89:U91)</f>
+      <c r="Y92" s="24">
+        <f>SUM(Y89:Y91)</f>
         <v>-157.18199999999999</v>
       </c>
-      <c r="V92" s="3"/>
-      <c r="W92" s="3"/>
-      <c r="X92" s="3"/>
-      <c r="Y92" s="3"/>
       <c r="Z92" s="3"/>
       <c r="AA92" s="3"/>
       <c r="AB92" s="3"/>
@@ -10676,8 +11375,12 @@
       <c r="BR92" s="3"/>
       <c r="BS92" s="3"/>
       <c r="BT92" s="3"/>
-    </row>
-    <row r="93" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU92" s="3"/>
+      <c r="BV92" s="3"/>
+      <c r="BW92" s="3"/>
+      <c r="BX92" s="3"/>
+    </row>
+    <row r="93" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B93" s="2" t="s">
         <v>111</v>
       </c>
@@ -10694,29 +11397,29 @@
       <c r="M93" s="3"/>
       <c r="N93" s="3"/>
       <c r="O93" s="3"/>
-      <c r="P93" s="3">
+      <c r="P93" s="3"/>
+      <c r="Q93" s="3"/>
+      <c r="R93" s="3"/>
+      <c r="S93" s="3"/>
+      <c r="T93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3">
+      <c r="U93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3">
+      <c r="V93" s="3">
         <f>350+210</f>
         <v>560</v>
       </c>
-      <c r="S93" s="3">
+      <c r="W93" s="3">
         <v>0</v>
       </c>
-      <c r="T93" s="3">
+      <c r="X93" s="3">
         <v>0</v>
       </c>
-      <c r="U93" s="3">
+      <c r="Y93" s="3">
         <v>0</v>
       </c>
-      <c r="V93" s="3"/>
-      <c r="W93" s="3"/>
-      <c r="X93" s="3"/>
-      <c r="Y93" s="3"/>
       <c r="Z93" s="3"/>
       <c r="AA93" s="3"/>
       <c r="AB93" s="3"/>
@@ -10764,8 +11467,12 @@
       <c r="BR93" s="3"/>
       <c r="BS93" s="3"/>
       <c r="BT93" s="3"/>
-    </row>
-    <row r="94" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU93" s="3"/>
+      <c r="BV93" s="3"/>
+      <c r="BW93" s="3"/>
+      <c r="BX93" s="3"/>
+    </row>
+    <row r="94" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B94" s="2" t="s">
         <v>91</v>
       </c>
@@ -10782,29 +11489,29 @@
       <c r="M94" s="3"/>
       <c r="N94" s="3"/>
       <c r="O94" s="3"/>
-      <c r="P94" s="3">
+      <c r="P94" s="3"/>
+      <c r="Q94" s="3"/>
+      <c r="R94" s="3"/>
+      <c r="S94" s="3"/>
+      <c r="T94" s="3">
         <v>0</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="U94" s="3">
         <v>-20</v>
       </c>
-      <c r="R94" s="3">
+      <c r="V94" s="3">
         <f>-233.25-210</f>
         <v>-443.25</v>
       </c>
-      <c r="S94" s="3">
+      <c r="W94" s="3">
         <v>-46.969000000000001</v>
       </c>
-      <c r="T94" s="3">
+      <c r="X94" s="3">
         <v>-7.8620000000000001</v>
       </c>
-      <c r="U94" s="3">
+      <c r="Y94" s="3">
         <v>-77.971999999999994</v>
       </c>
-      <c r="V94" s="3"/>
-      <c r="W94" s="3"/>
-      <c r="X94" s="3"/>
-      <c r="Y94" s="3"/>
       <c r="Z94" s="3"/>
       <c r="AA94" s="3"/>
       <c r="AB94" s="3"/>
@@ -10852,8 +11559,12 @@
       <c r="BR94" s="3"/>
       <c r="BS94" s="3"/>
       <c r="BT94" s="3"/>
-    </row>
-    <row r="95" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU94" s="3"/>
+      <c r="BV94" s="3"/>
+      <c r="BW94" s="3"/>
+      <c r="BX94" s="3"/>
+    </row>
+    <row r="95" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B95" s="2" t="s">
         <v>113</v>
       </c>
@@ -10870,28 +11581,28 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-      <c r="P95" s="3">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+      <c r="T95" s="3">
         <v>0</v>
       </c>
-      <c r="Q95" s="3">
+      <c r="U95" s="3">
         <v>0</v>
       </c>
-      <c r="R95" s="3">
+      <c r="V95" s="3">
         <v>-7.3179999999999996</v>
       </c>
-      <c r="S95" s="3">
+      <c r="W95" s="3">
         <v>-2.016</v>
       </c>
-      <c r="T95" s="3">
+      <c r="X95" s="3">
         <v>-0.18099999999999999</v>
       </c>
-      <c r="U95" s="3">
+      <c r="Y95" s="3">
         <v>-0.18</v>
       </c>
-      <c r="V95" s="3"/>
-      <c r="W95" s="3"/>
-      <c r="X95" s="3"/>
-      <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
@@ -10939,8 +11650,12 @@
       <c r="BR95" s="3"/>
       <c r="BS95" s="3"/>
       <c r="BT95" s="3"/>
-    </row>
-    <row r="96" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU95" s="3"/>
+      <c r="BV95" s="3"/>
+      <c r="BW95" s="3"/>
+      <c r="BX95" s="3"/>
+    </row>
+    <row r="96" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B96" s="2" t="s">
         <v>112</v>
       </c>
@@ -10957,28 +11672,28 @@
       <c r="M96" s="3"/>
       <c r="N96" s="3"/>
       <c r="O96" s="3"/>
-      <c r="P96" s="3">
+      <c r="P96" s="3"/>
+      <c r="Q96" s="3"/>
+      <c r="R96" s="3"/>
+      <c r="S96" s="3"/>
+      <c r="T96" s="3">
         <v>-53.713999999999999</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="U96" s="3">
         <v>-51.51</v>
       </c>
-      <c r="R96" s="3">
+      <c r="V96" s="3">
         <v>-12.555999999999999</v>
       </c>
-      <c r="S96" s="3">
+      <c r="W96" s="3">
         <v>0</v>
       </c>
-      <c r="T96" s="3">
+      <c r="X96" s="3">
         <v>0</v>
       </c>
-      <c r="U96" s="3">
+      <c r="Y96" s="3">
         <v>0</v>
       </c>
-      <c r="V96" s="3"/>
-      <c r="W96" s="3"/>
-      <c r="X96" s="3"/>
-      <c r="Y96" s="3"/>
       <c r="Z96" s="3"/>
       <c r="AA96" s="3"/>
       <c r="AB96" s="3"/>
@@ -11026,8 +11741,12 @@
       <c r="BR96" s="3"/>
       <c r="BS96" s="3"/>
       <c r="BT96" s="3"/>
-    </row>
-    <row r="97" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU96" s="3"/>
+      <c r="BV96" s="3"/>
+      <c r="BW96" s="3"/>
+      <c r="BX96" s="3"/>
+    </row>
+    <row r="97" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B97" s="2" t="s">
         <v>92</v>
       </c>
@@ -11044,28 +11763,28 @@
       <c r="M97" s="3"/>
       <c r="N97" s="3"/>
       <c r="O97" s="3"/>
-      <c r="P97" s="3">
+      <c r="P97" s="3"/>
+      <c r="Q97" s="3"/>
+      <c r="R97" s="3"/>
+      <c r="S97" s="3"/>
+      <c r="T97" s="3">
         <v>-68.67</v>
       </c>
-      <c r="Q97" s="3">
+      <c r="U97" s="3">
         <v>-63.542000000000002</v>
       </c>
-      <c r="R97" s="3">
+      <c r="V97" s="3">
         <v>-15.172000000000001</v>
       </c>
-      <c r="S97" s="3">
+      <c r="W97" s="3">
         <v>-377.29</v>
       </c>
-      <c r="T97" s="3">
+      <c r="X97" s="3">
         <v>-125.77500000000001</v>
       </c>
-      <c r="U97" s="3">
+      <c r="Y97" s="3">
         <v>0</v>
       </c>
-      <c r="V97" s="3"/>
-      <c r="W97" s="3"/>
-      <c r="X97" s="3"/>
-      <c r="Y97" s="3"/>
       <c r="Z97" s="3"/>
       <c r="AA97" s="3"/>
       <c r="AB97" s="3"/>
@@ -11113,8 +11832,12 @@
       <c r="BR97" s="3"/>
       <c r="BS97" s="3"/>
       <c r="BT97" s="3"/>
-    </row>
-    <row r="98" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU97" s="3"/>
+      <c r="BV97" s="3"/>
+      <c r="BW97" s="3"/>
+      <c r="BX97" s="3"/>
+    </row>
+    <row r="98" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B98" s="2" t="s">
         <v>93</v>
       </c>
@@ -11131,28 +11854,28 @@
       <c r="M98" s="3"/>
       <c r="N98" s="3"/>
       <c r="O98" s="3"/>
-      <c r="P98" s="3">
+      <c r="P98" s="3"/>
+      <c r="Q98" s="3"/>
+      <c r="R98" s="3"/>
+      <c r="S98" s="3"/>
+      <c r="T98" s="3">
         <v>-9.3070000000000004</v>
       </c>
-      <c r="Q98" s="3">
+      <c r="U98" s="3">
         <v>-12.821</v>
       </c>
-      <c r="R98" s="3">
+      <c r="V98" s="3">
         <v>-11.987</v>
       </c>
-      <c r="S98" s="3">
+      <c r="W98" s="3">
         <v>-20.623000000000001</v>
       </c>
-      <c r="T98" s="3">
+      <c r="X98" s="3">
         <v>-21.510999999999999</v>
       </c>
-      <c r="U98" s="3">
+      <c r="Y98" s="3">
         <v>-33.048999999999999</v>
       </c>
-      <c r="V98" s="3"/>
-      <c r="W98" s="3"/>
-      <c r="X98" s="3"/>
-      <c r="Y98" s="3"/>
       <c r="Z98" s="3"/>
       <c r="AA98" s="3"/>
       <c r="AB98" s="3"/>
@@ -11200,8 +11923,12 @@
       <c r="BR98" s="3"/>
       <c r="BS98" s="3"/>
       <c r="BT98" s="3"/>
-    </row>
-    <row r="99" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU98" s="3"/>
+      <c r="BV98" s="3"/>
+      <c r="BW98" s="3"/>
+      <c r="BX98" s="3"/>
+    </row>
+    <row r="99" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B99" s="1" t="s">
         <v>94</v>
       </c>
@@ -11218,34 +11945,34 @@
       <c r="M99" s="3"/>
       <c r="N99" s="3"/>
       <c r="O99" s="3"/>
-      <c r="P99" s="24">
-        <f t="shared" ref="P99:Q99" si="60">SUM(P93:P98)</f>
+      <c r="P99" s="3"/>
+      <c r="Q99" s="3"/>
+      <c r="R99" s="3"/>
+      <c r="S99" s="3"/>
+      <c r="T99" s="24">
+        <f t="shared" ref="T99:U99" si="63">SUM(T93:T98)</f>
         <v>-131.691</v>
       </c>
-      <c r="Q99" s="24">
-        <f t="shared" si="60"/>
+      <c r="U99" s="24">
+        <f t="shared" si="63"/>
         <v>-147.87299999999999</v>
       </c>
-      <c r="R99" s="24">
-        <f>SUM(R93:R98)</f>
+      <c r="V99" s="24">
+        <f>SUM(V93:V98)</f>
         <v>69.717000000000013</v>
       </c>
-      <c r="S99" s="24">
-        <f t="shared" ref="S99:U99" si="61">SUM(S93:S98)</f>
+      <c r="W99" s="24">
+        <f t="shared" ref="W99:Y99" si="64">SUM(W93:W98)</f>
         <v>-446.89800000000002</v>
       </c>
-      <c r="T99" s="24">
-        <f t="shared" si="61"/>
+      <c r="X99" s="24">
+        <f t="shared" si="64"/>
         <v>-155.32900000000001</v>
       </c>
-      <c r="U99" s="24">
-        <f t="shared" si="61"/>
+      <c r="Y99" s="24">
+        <f t="shared" si="64"/>
         <v>-111.20099999999999</v>
       </c>
-      <c r="V99" s="3"/>
-      <c r="W99" s="3"/>
-      <c r="X99" s="3"/>
-      <c r="Y99" s="3"/>
       <c r="Z99" s="3"/>
       <c r="AA99" s="3"/>
       <c r="AB99" s="3"/>
@@ -11293,8 +12020,12 @@
       <c r="BR99" s="3"/>
       <c r="BS99" s="3"/>
       <c r="BT99" s="3"/>
-    </row>
-    <row r="100" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU99" s="3"/>
+      <c r="BV99" s="3"/>
+      <c r="BW99" s="3"/>
+      <c r="BX99" s="3"/>
+    </row>
+    <row r="100" spans="2:76" x14ac:dyDescent="0.2">
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -11365,8 +12096,12 @@
       <c r="BR100" s="3"/>
       <c r="BS100" s="3"/>
       <c r="BT100" s="3"/>
-    </row>
-    <row r="101" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU100" s="3"/>
+      <c r="BV100" s="3"/>
+      <c r="BW100" s="3"/>
+      <c r="BX100" s="3"/>
+    </row>
+    <row r="101" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B101" s="2" t="s">
         <v>95</v>
       </c>
@@ -11383,28 +12118,28 @@
       <c r="M101" s="3"/>
       <c r="N101" s="3"/>
       <c r="O101" s="3"/>
-      <c r="P101" s="3">
+      <c r="P101" s="3"/>
+      <c r="Q101" s="3"/>
+      <c r="R101" s="3"/>
+      <c r="S101" s="3"/>
+      <c r="T101" s="3">
         <v>-20.975000000000001</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="U101" s="3">
         <v>-3.593</v>
       </c>
-      <c r="R101" s="3">
+      <c r="V101" s="3">
         <v>9.1679999999999993</v>
       </c>
-      <c r="S101" s="3">
+      <c r="W101" s="3">
         <v>-23.693999999999999</v>
       </c>
-      <c r="T101" s="3">
+      <c r="X101" s="3">
         <v>-8.452</v>
       </c>
-      <c r="U101" s="3">
+      <c r="Y101" s="3">
         <v>-2.923</v>
       </c>
-      <c r="V101" s="3"/>
-      <c r="W101" s="3"/>
-      <c r="X101" s="3"/>
-      <c r="Y101" s="3"/>
       <c r="Z101" s="3"/>
       <c r="AA101" s="3"/>
       <c r="AB101" s="3"/>
@@ -11452,8 +12187,12 @@
       <c r="BR101" s="3"/>
       <c r="BS101" s="3"/>
       <c r="BT101" s="3"/>
-    </row>
-    <row r="102" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU101" s="3"/>
+      <c r="BV101" s="3"/>
+      <c r="BW101" s="3"/>
+      <c r="BX101" s="3"/>
+    </row>
+    <row r="102" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B102" s="1" t="s">
         <v>96</v>
       </c>
@@ -11470,34 +12209,34 @@
       <c r="M102" s="3"/>
       <c r="N102" s="3"/>
       <c r="O102" s="3"/>
-      <c r="P102" s="24">
-        <f t="shared" ref="P102:T102" si="62">P88+P92+P99+P101</f>
+      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
+      <c r="T102" s="24">
+        <f t="shared" ref="T102:X102" si="65">T88+T92+T99+T101</f>
         <v>47.892000000000188</v>
       </c>
-      <c r="Q102" s="24">
-        <f t="shared" si="62"/>
+      <c r="U102" s="24">
+        <f t="shared" si="65"/>
         <v>-53.600999999999303</v>
       </c>
-      <c r="R102" s="24">
-        <f t="shared" si="62"/>
+      <c r="V102" s="24">
+        <f t="shared" si="65"/>
         <v>431.89299999999992</v>
       </c>
-      <c r="S102" s="24">
-        <f t="shared" si="62"/>
+      <c r="W102" s="24">
+        <f t="shared" si="65"/>
         <v>-289.78600000000023</v>
       </c>
-      <c r="T102" s="24">
-        <f t="shared" si="62"/>
+      <c r="X102" s="24">
+        <f t="shared" si="65"/>
         <v>-306.79899999999941</v>
       </c>
-      <c r="U102" s="24">
-        <f>U88+U92+U99+U101</f>
+      <c r="Y102" s="24">
+        <f>Y88+Y92+Y99+Y101</f>
         <v>382.11599999999919</v>
       </c>
-      <c r="V102" s="3"/>
-      <c r="W102" s="3"/>
-      <c r="X102" s="3"/>
-      <c r="Y102" s="3"/>
       <c r="Z102" s="3"/>
       <c r="AA102" s="3"/>
       <c r="AB102" s="3"/>
@@ -11545,8 +12284,12 @@
       <c r="BR102" s="3"/>
       <c r="BS102" s="3"/>
       <c r="BT102" s="3"/>
-    </row>
-    <row r="103" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU102" s="3"/>
+      <c r="BV102" s="3"/>
+      <c r="BW102" s="3"/>
+      <c r="BX102" s="3"/>
+    </row>
+    <row r="103" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B103" s="2" t="s">
         <v>97</v>
       </c>
@@ -11563,34 +12306,34 @@
       <c r="M103" s="3"/>
       <c r="N103" s="3"/>
       <c r="O103" s="3"/>
-      <c r="P103" s="3">
-        <f t="shared" ref="P103:U103" si="63">P104-P102</f>
+      <c r="P103" s="3"/>
+      <c r="Q103" s="3"/>
+      <c r="R103" s="3"/>
+      <c r="S103" s="3"/>
+      <c r="T103" s="3">
+        <f t="shared" ref="T103:Y103" si="66">T104-T102</f>
         <v>697.96999999999969</v>
       </c>
-      <c r="Q103" s="3">
-        <f t="shared" si="63"/>
+      <c r="U103" s="3">
+        <f t="shared" si="66"/>
         <v>745.86199999999985</v>
       </c>
-      <c r="R103" s="3">
-        <f t="shared" si="63"/>
+      <c r="V103" s="3">
+        <f t="shared" si="66"/>
         <v>692.26100000000054</v>
       </c>
-      <c r="S103" s="3">
-        <f t="shared" si="63"/>
+      <c r="W103" s="3">
+        <f t="shared" si="66"/>
         <v>1124.1540000000005</v>
       </c>
-      <c r="T103" s="3">
-        <f t="shared" si="63"/>
+      <c r="X103" s="3">
+        <f t="shared" si="66"/>
         <v>834.36800000000017</v>
       </c>
-      <c r="U103" s="3">
-        <f t="shared" si="63"/>
+      <c r="Y103" s="3">
+        <f t="shared" si="66"/>
         <v>527.56900000000076</v>
       </c>
-      <c r="V103" s="3"/>
-      <c r="W103" s="3"/>
-      <c r="X103" s="3"/>
-      <c r="Y103" s="3"/>
       <c r="Z103" s="3"/>
       <c r="AA103" s="3"/>
       <c r="AB103" s="3"/>
@@ -11638,8 +12381,12 @@
       <c r="BR103" s="3"/>
       <c r="BS103" s="3"/>
       <c r="BT103" s="3"/>
-    </row>
-    <row r="104" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU103" s="3"/>
+      <c r="BV103" s="3"/>
+      <c r="BW103" s="3"/>
+      <c r="BX103" s="3"/>
+    </row>
+    <row r="104" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B104" s="2" t="s">
         <v>98</v>
       </c>
@@ -11656,33 +12403,33 @@
       <c r="M104" s="3"/>
       <c r="N104" s="3"/>
       <c r="O104" s="3"/>
-      <c r="P104" s="3">
-        <f>Q103</f>
-        <v>745.86199999999985</v>
-      </c>
-      <c r="Q104" s="3">
-        <f>R103</f>
-        <v>692.26100000000054</v>
-      </c>
-      <c r="R104" s="3">
-        <f>S103</f>
-        <v>1124.1540000000005</v>
-      </c>
-      <c r="S104" s="3">
-        <f>T103</f>
-        <v>834.36800000000017</v>
-      </c>
+      <c r="P104" s="3"/>
+      <c r="Q104" s="3"/>
+      <c r="R104" s="3"/>
+      <c r="S104" s="3"/>
       <c r="T104" s="3">
         <f>U103</f>
+        <v>745.86199999999985</v>
+      </c>
+      <c r="U104" s="3">
+        <f>V103</f>
+        <v>692.26100000000054</v>
+      </c>
+      <c r="V104" s="3">
+        <f>W103</f>
+        <v>1124.1540000000005</v>
+      </c>
+      <c r="W104" s="3">
+        <f>X103</f>
+        <v>834.36800000000017</v>
+      </c>
+      <c r="X104" s="3">
+        <f>Y103</f>
         <v>527.56900000000076</v>
       </c>
-      <c r="U104" s="3">
+      <c r="Y104" s="3">
         <v>909.68499999999995</v>
       </c>
-      <c r="V104" s="3"/>
-      <c r="W104" s="3"/>
-      <c r="X104" s="3"/>
-      <c r="Y104" s="3"/>
       <c r="Z104" s="3"/>
       <c r="AA104" s="3"/>
       <c r="AB104" s="3"/>
@@ -11730,8 +12477,12 @@
       <c r="BR104" s="3"/>
       <c r="BS104" s="3"/>
       <c r="BT104" s="3"/>
-    </row>
-    <row r="105" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU104" s="3"/>
+      <c r="BV104" s="3"/>
+      <c r="BW104" s="3"/>
+      <c r="BX104" s="3"/>
+    </row>
+    <row r="105" spans="2:76" x14ac:dyDescent="0.2">
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
@@ -11802,8 +12553,12 @@
       <c r="BR105" s="3"/>
       <c r="BS105" s="3"/>
       <c r="BT105" s="3"/>
-    </row>
-    <row r="106" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU105" s="3"/>
+      <c r="BV105" s="3"/>
+      <c r="BW105" s="3"/>
+      <c r="BX105" s="3"/>
+    </row>
+    <row r="106" spans="2:76" x14ac:dyDescent="0.2">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -11874,8 +12629,12 @@
       <c r="BR106" s="3"/>
       <c r="BS106" s="3"/>
       <c r="BT106" s="3"/>
-    </row>
-    <row r="107" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU106" s="3"/>
+      <c r="BV106" s="3"/>
+      <c r="BW106" s="3"/>
+      <c r="BX106" s="3"/>
+    </row>
+    <row r="107" spans="2:76" x14ac:dyDescent="0.2">
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
@@ -11946,8 +12705,12 @@
       <c r="BR107" s="3"/>
       <c r="BS107" s="3"/>
       <c r="BT107" s="3"/>
-    </row>
-    <row r="108" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU107" s="3"/>
+      <c r="BV107" s="3"/>
+      <c r="BW107" s="3"/>
+      <c r="BX107" s="3"/>
+    </row>
+    <row r="108" spans="2:76" x14ac:dyDescent="0.2">
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -12018,8 +12781,12 @@
       <c r="BR108" s="3"/>
       <c r="BS108" s="3"/>
       <c r="BT108" s="3"/>
-    </row>
-    <row r="109" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU108" s="3"/>
+      <c r="BV108" s="3"/>
+      <c r="BW108" s="3"/>
+      <c r="BX108" s="3"/>
+    </row>
+    <row r="109" spans="2:76" x14ac:dyDescent="0.2">
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
@@ -12090,8 +12857,12 @@
       <c r="BR109" s="3"/>
       <c r="BS109" s="3"/>
       <c r="BT109" s="3"/>
-    </row>
-    <row r="110" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU109" s="3"/>
+      <c r="BV109" s="3"/>
+      <c r="BW109" s="3"/>
+      <c r="BX109" s="3"/>
+    </row>
+    <row r="110" spans="2:76" x14ac:dyDescent="0.2">
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
@@ -12162,8 +12933,12 @@
       <c r="BR110" s="3"/>
       <c r="BS110" s="3"/>
       <c r="BT110" s="3"/>
-    </row>
-    <row r="111" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU110" s="3"/>
+      <c r="BV110" s="3"/>
+      <c r="BW110" s="3"/>
+      <c r="BX110" s="3"/>
+    </row>
+    <row r="111" spans="2:76" x14ac:dyDescent="0.2">
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -12234,8 +13009,12 @@
       <c r="BR111" s="3"/>
       <c r="BS111" s="3"/>
       <c r="BT111" s="3"/>
-    </row>
-    <row r="112" spans="2:72" x14ac:dyDescent="0.2">
+      <c r="BU111" s="3"/>
+      <c r="BV111" s="3"/>
+      <c r="BW111" s="3"/>
+      <c r="BX111" s="3"/>
+    </row>
+    <row r="112" spans="2:76" x14ac:dyDescent="0.2">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -12306,8 +13085,12 @@
       <c r="BR112" s="3"/>
       <c r="BS112" s="3"/>
       <c r="BT112" s="3"/>
-    </row>
-    <row r="113" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU112" s="3"/>
+      <c r="BV112" s="3"/>
+      <c r="BW112" s="3"/>
+      <c r="BX112" s="3"/>
+    </row>
+    <row r="113" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
@@ -12378,8 +13161,12 @@
       <c r="BR113" s="3"/>
       <c r="BS113" s="3"/>
       <c r="BT113" s="3"/>
-    </row>
-    <row r="114" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU113" s="3"/>
+      <c r="BV113" s="3"/>
+      <c r="BW113" s="3"/>
+      <c r="BX113" s="3"/>
+    </row>
+    <row r="114" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -12450,8 +13237,12 @@
       <c r="BR114" s="3"/>
       <c r="BS114" s="3"/>
       <c r="BT114" s="3"/>
-    </row>
-    <row r="115" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU114" s="3"/>
+      <c r="BV114" s="3"/>
+      <c r="BW114" s="3"/>
+      <c r="BX114" s="3"/>
+    </row>
+    <row r="115" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -12522,8 +13313,12 @@
       <c r="BR115" s="3"/>
       <c r="BS115" s="3"/>
       <c r="BT115" s="3"/>
-    </row>
-    <row r="116" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU115" s="3"/>
+      <c r="BV115" s="3"/>
+      <c r="BW115" s="3"/>
+      <c r="BX115" s="3"/>
+    </row>
+    <row r="116" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -12594,8 +13389,12 @@
       <c r="BR116" s="3"/>
       <c r="BS116" s="3"/>
       <c r="BT116" s="3"/>
-    </row>
-    <row r="117" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU116" s="3"/>
+      <c r="BV116" s="3"/>
+      <c r="BW116" s="3"/>
+      <c r="BX116" s="3"/>
+    </row>
+    <row r="117" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
@@ -12666,8 +13465,12 @@
       <c r="BR117" s="3"/>
       <c r="BS117" s="3"/>
       <c r="BT117" s="3"/>
-    </row>
-    <row r="118" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU117" s="3"/>
+      <c r="BV117" s="3"/>
+      <c r="BW117" s="3"/>
+      <c r="BX117" s="3"/>
+    </row>
+    <row r="118" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -12738,8 +13541,12 @@
       <c r="BR118" s="3"/>
       <c r="BS118" s="3"/>
       <c r="BT118" s="3"/>
-    </row>
-    <row r="119" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU118" s="3"/>
+      <c r="BV118" s="3"/>
+      <c r="BW118" s="3"/>
+      <c r="BX118" s="3"/>
+    </row>
+    <row r="119" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
@@ -12810,8 +13617,12 @@
       <c r="BR119" s="3"/>
       <c r="BS119" s="3"/>
       <c r="BT119" s="3"/>
-    </row>
-    <row r="120" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU119" s="3"/>
+      <c r="BV119" s="3"/>
+      <c r="BW119" s="3"/>
+      <c r="BX119" s="3"/>
+    </row>
+    <row r="120" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -12882,8 +13693,12 @@
       <c r="BR120" s="3"/>
       <c r="BS120" s="3"/>
       <c r="BT120" s="3"/>
-    </row>
-    <row r="121" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU120" s="3"/>
+      <c r="BV120" s="3"/>
+      <c r="BW120" s="3"/>
+      <c r="BX120" s="3"/>
+    </row>
+    <row r="121" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
@@ -12954,8 +13769,12 @@
       <c r="BR121" s="3"/>
       <c r="BS121" s="3"/>
       <c r="BT121" s="3"/>
-    </row>
-    <row r="122" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU121" s="3"/>
+      <c r="BV121" s="3"/>
+      <c r="BW121" s="3"/>
+      <c r="BX121" s="3"/>
+    </row>
+    <row r="122" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -13026,8 +13845,12 @@
       <c r="BR122" s="3"/>
       <c r="BS122" s="3"/>
       <c r="BT122" s="3"/>
-    </row>
-    <row r="123" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU122" s="3"/>
+      <c r="BV122" s="3"/>
+      <c r="BW122" s="3"/>
+      <c r="BX122" s="3"/>
+    </row>
+    <row r="123" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -13098,8 +13921,12 @@
       <c r="BR123" s="3"/>
       <c r="BS123" s="3"/>
       <c r="BT123" s="3"/>
-    </row>
-    <row r="124" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU123" s="3"/>
+      <c r="BV123" s="3"/>
+      <c r="BW123" s="3"/>
+      <c r="BX123" s="3"/>
+    </row>
+    <row r="124" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -13170,8 +13997,12 @@
       <c r="BR124" s="3"/>
       <c r="BS124" s="3"/>
       <c r="BT124" s="3"/>
-    </row>
-    <row r="125" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU124" s="3"/>
+      <c r="BV124" s="3"/>
+      <c r="BW124" s="3"/>
+      <c r="BX124" s="3"/>
+    </row>
+    <row r="125" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
@@ -13242,8 +14073,12 @@
       <c r="BR125" s="3"/>
       <c r="BS125" s="3"/>
       <c r="BT125" s="3"/>
-    </row>
-    <row r="126" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU125" s="3"/>
+      <c r="BV125" s="3"/>
+      <c r="BW125" s="3"/>
+      <c r="BX125" s="3"/>
+    </row>
+    <row r="126" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -13314,8 +14149,12 @@
       <c r="BR126" s="3"/>
       <c r="BS126" s="3"/>
       <c r="BT126" s="3"/>
-    </row>
-    <row r="127" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU126" s="3"/>
+      <c r="BV126" s="3"/>
+      <c r="BW126" s="3"/>
+      <c r="BX126" s="3"/>
+    </row>
+    <row r="127" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
@@ -13386,8 +14225,12 @@
       <c r="BR127" s="3"/>
       <c r="BS127" s="3"/>
       <c r="BT127" s="3"/>
-    </row>
-    <row r="128" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU127" s="3"/>
+      <c r="BV127" s="3"/>
+      <c r="BW127" s="3"/>
+      <c r="BX127" s="3"/>
+    </row>
+    <row r="128" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -13458,8 +14301,12 @@
       <c r="BR128" s="3"/>
       <c r="BS128" s="3"/>
       <c r="BT128" s="3"/>
-    </row>
-    <row r="129" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU128" s="3"/>
+      <c r="BV128" s="3"/>
+      <c r="BW128" s="3"/>
+      <c r="BX128" s="3"/>
+    </row>
+    <row r="129" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
@@ -13530,8 +14377,12 @@
       <c r="BR129" s="3"/>
       <c r="BS129" s="3"/>
       <c r="BT129" s="3"/>
-    </row>
-    <row r="130" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU129" s="3"/>
+      <c r="BV129" s="3"/>
+      <c r="BW129" s="3"/>
+      <c r="BX129" s="3"/>
+    </row>
+    <row r="130" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -13602,8 +14453,12 @@
       <c r="BR130" s="3"/>
       <c r="BS130" s="3"/>
       <c r="BT130" s="3"/>
-    </row>
-    <row r="131" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU130" s="3"/>
+      <c r="BV130" s="3"/>
+      <c r="BW130" s="3"/>
+      <c r="BX130" s="3"/>
+    </row>
+    <row r="131" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -13674,8 +14529,12 @@
       <c r="BR131" s="3"/>
       <c r="BS131" s="3"/>
       <c r="BT131" s="3"/>
-    </row>
-    <row r="132" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU131" s="3"/>
+      <c r="BV131" s="3"/>
+      <c r="BW131" s="3"/>
+      <c r="BX131" s="3"/>
+    </row>
+    <row r="132" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -13746,8 +14605,12 @@
       <c r="BR132" s="3"/>
       <c r="BS132" s="3"/>
       <c r="BT132" s="3"/>
-    </row>
-    <row r="133" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU132" s="3"/>
+      <c r="BV132" s="3"/>
+      <c r="BW132" s="3"/>
+      <c r="BX132" s="3"/>
+    </row>
+    <row r="133" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
@@ -13818,8 +14681,12 @@
       <c r="BR133" s="3"/>
       <c r="BS133" s="3"/>
       <c r="BT133" s="3"/>
-    </row>
-    <row r="134" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU133" s="3"/>
+      <c r="BV133" s="3"/>
+      <c r="BW133" s="3"/>
+      <c r="BX133" s="3"/>
+    </row>
+    <row r="134" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -13890,8 +14757,12 @@
       <c r="BR134" s="3"/>
       <c r="BS134" s="3"/>
       <c r="BT134" s="3"/>
-    </row>
-    <row r="135" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU134" s="3"/>
+      <c r="BV134" s="3"/>
+      <c r="BW134" s="3"/>
+      <c r="BX134" s="3"/>
+    </row>
+    <row r="135" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
@@ -13962,8 +14833,12 @@
       <c r="BR135" s="3"/>
       <c r="BS135" s="3"/>
       <c r="BT135" s="3"/>
-    </row>
-    <row r="136" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU135" s="3"/>
+      <c r="BV135" s="3"/>
+      <c r="BW135" s="3"/>
+      <c r="BX135" s="3"/>
+    </row>
+    <row r="136" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -14034,8 +14909,12 @@
       <c r="BR136" s="3"/>
       <c r="BS136" s="3"/>
       <c r="BT136" s="3"/>
-    </row>
-    <row r="137" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU136" s="3"/>
+      <c r="BV136" s="3"/>
+      <c r="BW136" s="3"/>
+      <c r="BX136" s="3"/>
+    </row>
+    <row r="137" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -14106,8 +14985,12 @@
       <c r="BR137" s="3"/>
       <c r="BS137" s="3"/>
       <c r="BT137" s="3"/>
-    </row>
-    <row r="138" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU137" s="3"/>
+      <c r="BV137" s="3"/>
+      <c r="BW137" s="3"/>
+      <c r="BX137" s="3"/>
+    </row>
+    <row r="138" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -14178,8 +15061,12 @@
       <c r="BR138" s="3"/>
       <c r="BS138" s="3"/>
       <c r="BT138" s="3"/>
-    </row>
-    <row r="139" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU138" s="3"/>
+      <c r="BV138" s="3"/>
+      <c r="BW138" s="3"/>
+      <c r="BX138" s="3"/>
+    </row>
+    <row r="139" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -14250,8 +15137,12 @@
       <c r="BR139" s="3"/>
       <c r="BS139" s="3"/>
       <c r="BT139" s="3"/>
-    </row>
-    <row r="140" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU139" s="3"/>
+      <c r="BV139" s="3"/>
+      <c r="BW139" s="3"/>
+      <c r="BX139" s="3"/>
+    </row>
+    <row r="140" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -14322,8 +15213,12 @@
       <c r="BR140" s="3"/>
       <c r="BS140" s="3"/>
       <c r="BT140" s="3"/>
-    </row>
-    <row r="141" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU140" s="3"/>
+      <c r="BV140" s="3"/>
+      <c r="BW140" s="3"/>
+      <c r="BX140" s="3"/>
+    </row>
+    <row r="141" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
@@ -14394,8 +15289,12 @@
       <c r="BR141" s="3"/>
       <c r="BS141" s="3"/>
       <c r="BT141" s="3"/>
-    </row>
-    <row r="142" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU141" s="3"/>
+      <c r="BV141" s="3"/>
+      <c r="BW141" s="3"/>
+      <c r="BX141" s="3"/>
+    </row>
+    <row r="142" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -14466,8 +15365,12 @@
       <c r="BR142" s="3"/>
       <c r="BS142" s="3"/>
       <c r="BT142" s="3"/>
-    </row>
-    <row r="143" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU142" s="3"/>
+      <c r="BV142" s="3"/>
+      <c r="BW142" s="3"/>
+      <c r="BX142" s="3"/>
+    </row>
+    <row r="143" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -14538,8 +15441,12 @@
       <c r="BR143" s="3"/>
       <c r="BS143" s="3"/>
       <c r="BT143" s="3"/>
-    </row>
-    <row r="144" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU143" s="3"/>
+      <c r="BV143" s="3"/>
+      <c r="BW143" s="3"/>
+      <c r="BX143" s="3"/>
+    </row>
+    <row r="144" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -14610,8 +15517,12 @@
       <c r="BR144" s="3"/>
       <c r="BS144" s="3"/>
       <c r="BT144" s="3"/>
-    </row>
-    <row r="145" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU144" s="3"/>
+      <c r="BV144" s="3"/>
+      <c r="BW144" s="3"/>
+      <c r="BX144" s="3"/>
+    </row>
+    <row r="145" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -14682,8 +15593,12 @@
       <c r="BR145" s="3"/>
       <c r="BS145" s="3"/>
       <c r="BT145" s="3"/>
-    </row>
-    <row r="146" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU145" s="3"/>
+      <c r="BV145" s="3"/>
+      <c r="BW145" s="3"/>
+      <c r="BX145" s="3"/>
+    </row>
+    <row r="146" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -14754,8 +15669,12 @@
       <c r="BR146" s="3"/>
       <c r="BS146" s="3"/>
       <c r="BT146" s="3"/>
-    </row>
-    <row r="147" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU146" s="3"/>
+      <c r="BV146" s="3"/>
+      <c r="BW146" s="3"/>
+      <c r="BX146" s="3"/>
+    </row>
+    <row r="147" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
@@ -14826,8 +15745,12 @@
       <c r="BR147" s="3"/>
       <c r="BS147" s="3"/>
       <c r="BT147" s="3"/>
-    </row>
-    <row r="148" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU147" s="3"/>
+      <c r="BV147" s="3"/>
+      <c r="BW147" s="3"/>
+      <c r="BX147" s="3"/>
+    </row>
+    <row r="148" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -14898,8 +15821,12 @@
       <c r="BR148" s="3"/>
       <c r="BS148" s="3"/>
       <c r="BT148" s="3"/>
-    </row>
-    <row r="149" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU148" s="3"/>
+      <c r="BV148" s="3"/>
+      <c r="BW148" s="3"/>
+      <c r="BX148" s="3"/>
+    </row>
+    <row r="149" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -14970,8 +15897,12 @@
       <c r="BR149" s="3"/>
       <c r="BS149" s="3"/>
       <c r="BT149" s="3"/>
-    </row>
-    <row r="150" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU149" s="3"/>
+      <c r="BV149" s="3"/>
+      <c r="BW149" s="3"/>
+      <c r="BX149" s="3"/>
+    </row>
+    <row r="150" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -15042,8 +15973,12 @@
       <c r="BR150" s="3"/>
       <c r="BS150" s="3"/>
       <c r="BT150" s="3"/>
-    </row>
-    <row r="151" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU150" s="3"/>
+      <c r="BV150" s="3"/>
+      <c r="BW150" s="3"/>
+      <c r="BX150" s="3"/>
+    </row>
+    <row r="151" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -15114,8 +16049,12 @@
       <c r="BR151" s="3"/>
       <c r="BS151" s="3"/>
       <c r="BT151" s="3"/>
-    </row>
-    <row r="152" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU151" s="3"/>
+      <c r="BV151" s="3"/>
+      <c r="BW151" s="3"/>
+      <c r="BX151" s="3"/>
+    </row>
+    <row r="152" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -15186,8 +16125,12 @@
       <c r="BR152" s="3"/>
       <c r="BS152" s="3"/>
       <c r="BT152" s="3"/>
-    </row>
-    <row r="153" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU152" s="3"/>
+      <c r="BV152" s="3"/>
+      <c r="BW152" s="3"/>
+      <c r="BX152" s="3"/>
+    </row>
+    <row r="153" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -15258,8 +16201,12 @@
       <c r="BR153" s="3"/>
       <c r="BS153" s="3"/>
       <c r="BT153" s="3"/>
-    </row>
-    <row r="154" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU153" s="3"/>
+      <c r="BV153" s="3"/>
+      <c r="BW153" s="3"/>
+      <c r="BX153" s="3"/>
+    </row>
+    <row r="154" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -15330,8 +16277,12 @@
       <c r="BR154" s="3"/>
       <c r="BS154" s="3"/>
       <c r="BT154" s="3"/>
-    </row>
-    <row r="155" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU154" s="3"/>
+      <c r="BV154" s="3"/>
+      <c r="BW154" s="3"/>
+      <c r="BX154" s="3"/>
+    </row>
+    <row r="155" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -15402,8 +16353,12 @@
       <c r="BR155" s="3"/>
       <c r="BS155" s="3"/>
       <c r="BT155" s="3"/>
-    </row>
-    <row r="156" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU155" s="3"/>
+      <c r="BV155" s="3"/>
+      <c r="BW155" s="3"/>
+      <c r="BX155" s="3"/>
+    </row>
+    <row r="156" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -15474,8 +16429,12 @@
       <c r="BR156" s="3"/>
       <c r="BS156" s="3"/>
       <c r="BT156" s="3"/>
-    </row>
-    <row r="157" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU156" s="3"/>
+      <c r="BV156" s="3"/>
+      <c r="BW156" s="3"/>
+      <c r="BX156" s="3"/>
+    </row>
+    <row r="157" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -15546,8 +16505,12 @@
       <c r="BR157" s="3"/>
       <c r="BS157" s="3"/>
       <c r="BT157" s="3"/>
-    </row>
-    <row r="158" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU157" s="3"/>
+      <c r="BV157" s="3"/>
+      <c r="BW157" s="3"/>
+      <c r="BX157" s="3"/>
+    </row>
+    <row r="158" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -15618,8 +16581,12 @@
       <c r="BR158" s="3"/>
       <c r="BS158" s="3"/>
       <c r="BT158" s="3"/>
-    </row>
-    <row r="159" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU158" s="3"/>
+      <c r="BV158" s="3"/>
+      <c r="BW158" s="3"/>
+      <c r="BX158" s="3"/>
+    </row>
+    <row r="159" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -15690,8 +16657,12 @@
       <c r="BR159" s="3"/>
       <c r="BS159" s="3"/>
       <c r="BT159" s="3"/>
-    </row>
-    <row r="160" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU159" s="3"/>
+      <c r="BV159" s="3"/>
+      <c r="BW159" s="3"/>
+      <c r="BX159" s="3"/>
+    </row>
+    <row r="160" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -15762,8 +16733,12 @@
       <c r="BR160" s="3"/>
       <c r="BS160" s="3"/>
       <c r="BT160" s="3"/>
-    </row>
-    <row r="161" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU160" s="3"/>
+      <c r="BV160" s="3"/>
+      <c r="BW160" s="3"/>
+      <c r="BX160" s="3"/>
+    </row>
+    <row r="161" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -15834,8 +16809,12 @@
       <c r="BR161" s="3"/>
       <c r="BS161" s="3"/>
       <c r="BT161" s="3"/>
-    </row>
-    <row r="162" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU161" s="3"/>
+      <c r="BV161" s="3"/>
+      <c r="BW161" s="3"/>
+      <c r="BX161" s="3"/>
+    </row>
+    <row r="162" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -15906,8 +16885,12 @@
       <c r="BR162" s="3"/>
       <c r="BS162" s="3"/>
       <c r="BT162" s="3"/>
-    </row>
-    <row r="163" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU162" s="3"/>
+      <c r="BV162" s="3"/>
+      <c r="BW162" s="3"/>
+      <c r="BX162" s="3"/>
+    </row>
+    <row r="163" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -15978,8 +16961,12 @@
       <c r="BR163" s="3"/>
       <c r="BS163" s="3"/>
       <c r="BT163" s="3"/>
-    </row>
-    <row r="164" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU163" s="3"/>
+      <c r="BV163" s="3"/>
+      <c r="BW163" s="3"/>
+      <c r="BX163" s="3"/>
+    </row>
+    <row r="164" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -16050,8 +17037,12 @@
       <c r="BR164" s="3"/>
       <c r="BS164" s="3"/>
       <c r="BT164" s="3"/>
-    </row>
-    <row r="165" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU164" s="3"/>
+      <c r="BV164" s="3"/>
+      <c r="BW164" s="3"/>
+      <c r="BX164" s="3"/>
+    </row>
+    <row r="165" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -16122,8 +17113,12 @@
       <c r="BR165" s="3"/>
       <c r="BS165" s="3"/>
       <c r="BT165" s="3"/>
-    </row>
-    <row r="166" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU165" s="3"/>
+      <c r="BV165" s="3"/>
+      <c r="BW165" s="3"/>
+      <c r="BX165" s="3"/>
+    </row>
+    <row r="166" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -16194,8 +17189,12 @@
       <c r="BR166" s="3"/>
       <c r="BS166" s="3"/>
       <c r="BT166" s="3"/>
-    </row>
-    <row r="167" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU166" s="3"/>
+      <c r="BV166" s="3"/>
+      <c r="BW166" s="3"/>
+      <c r="BX166" s="3"/>
+    </row>
+    <row r="167" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -16266,8 +17265,12 @@
       <c r="BR167" s="3"/>
       <c r="BS167" s="3"/>
       <c r="BT167" s="3"/>
-    </row>
-    <row r="168" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU167" s="3"/>
+      <c r="BV167" s="3"/>
+      <c r="BW167" s="3"/>
+      <c r="BX167" s="3"/>
+    </row>
+    <row r="168" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -16338,8 +17341,12 @@
       <c r="BR168" s="3"/>
       <c r="BS168" s="3"/>
       <c r="BT168" s="3"/>
-    </row>
-    <row r="169" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU168" s="3"/>
+      <c r="BV168" s="3"/>
+      <c r="BW168" s="3"/>
+      <c r="BX168" s="3"/>
+    </row>
+    <row r="169" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -16410,8 +17417,12 @@
       <c r="BR169" s="3"/>
       <c r="BS169" s="3"/>
       <c r="BT169" s="3"/>
-    </row>
-    <row r="170" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU169" s="3"/>
+      <c r="BV169" s="3"/>
+      <c r="BW169" s="3"/>
+      <c r="BX169" s="3"/>
+    </row>
+    <row r="170" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -16482,8 +17493,12 @@
       <c r="BR170" s="3"/>
       <c r="BS170" s="3"/>
       <c r="BT170" s="3"/>
-    </row>
-    <row r="171" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU170" s="3"/>
+      <c r="BV170" s="3"/>
+      <c r="BW170" s="3"/>
+      <c r="BX170" s="3"/>
+    </row>
+    <row r="171" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -16554,8 +17569,12 @@
       <c r="BR171" s="3"/>
       <c r="BS171" s="3"/>
       <c r="BT171" s="3"/>
-    </row>
-    <row r="172" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU171" s="3"/>
+      <c r="BV171" s="3"/>
+      <c r="BW171" s="3"/>
+      <c r="BX171" s="3"/>
+    </row>
+    <row r="172" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -16626,8 +17645,12 @@
       <c r="BR172" s="3"/>
       <c r="BS172" s="3"/>
       <c r="BT172" s="3"/>
-    </row>
-    <row r="173" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU172" s="3"/>
+      <c r="BV172" s="3"/>
+      <c r="BW172" s="3"/>
+      <c r="BX172" s="3"/>
+    </row>
+    <row r="173" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -16698,8 +17721,12 @@
       <c r="BR173" s="3"/>
       <c r="BS173" s="3"/>
       <c r="BT173" s="3"/>
-    </row>
-    <row r="174" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU173" s="3"/>
+      <c r="BV173" s="3"/>
+      <c r="BW173" s="3"/>
+      <c r="BX173" s="3"/>
+    </row>
+    <row r="174" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -16770,8 +17797,12 @@
       <c r="BR174" s="3"/>
       <c r="BS174" s="3"/>
       <c r="BT174" s="3"/>
-    </row>
-    <row r="175" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU174" s="3"/>
+      <c r="BV174" s="3"/>
+      <c r="BW174" s="3"/>
+      <c r="BX174" s="3"/>
+    </row>
+    <row r="175" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -16842,8 +17873,12 @@
       <c r="BR175" s="3"/>
       <c r="BS175" s="3"/>
       <c r="BT175" s="3"/>
-    </row>
-    <row r="176" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU175" s="3"/>
+      <c r="BV175" s="3"/>
+      <c r="BW175" s="3"/>
+      <c r="BX175" s="3"/>
+    </row>
+    <row r="176" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -16914,8 +17949,12 @@
       <c r="BR176" s="3"/>
       <c r="BS176" s="3"/>
       <c r="BT176" s="3"/>
-    </row>
-    <row r="177" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU176" s="3"/>
+      <c r="BV176" s="3"/>
+      <c r="BW176" s="3"/>
+      <c r="BX176" s="3"/>
+    </row>
+    <row r="177" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -16986,8 +18025,12 @@
       <c r="BR177" s="3"/>
       <c r="BS177" s="3"/>
       <c r="BT177" s="3"/>
-    </row>
-    <row r="178" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU177" s="3"/>
+      <c r="BV177" s="3"/>
+      <c r="BW177" s="3"/>
+      <c r="BX177" s="3"/>
+    </row>
+    <row r="178" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -17058,8 +18101,12 @@
       <c r="BR178" s="3"/>
       <c r="BS178" s="3"/>
       <c r="BT178" s="3"/>
-    </row>
-    <row r="179" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU178" s="3"/>
+      <c r="BV178" s="3"/>
+      <c r="BW178" s="3"/>
+      <c r="BX178" s="3"/>
+    </row>
+    <row r="179" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -17130,8 +18177,12 @@
       <c r="BR179" s="3"/>
       <c r="BS179" s="3"/>
       <c r="BT179" s="3"/>
-    </row>
-    <row r="180" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU179" s="3"/>
+      <c r="BV179" s="3"/>
+      <c r="BW179" s="3"/>
+      <c r="BX179" s="3"/>
+    </row>
+    <row r="180" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -17202,8 +18253,12 @@
       <c r="BR180" s="3"/>
       <c r="BS180" s="3"/>
       <c r="BT180" s="3"/>
-    </row>
-    <row r="181" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU180" s="3"/>
+      <c r="BV180" s="3"/>
+      <c r="BW180" s="3"/>
+      <c r="BX180" s="3"/>
+    </row>
+    <row r="181" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -17274,8 +18329,12 @@
       <c r="BR181" s="3"/>
       <c r="BS181" s="3"/>
       <c r="BT181" s="3"/>
-    </row>
-    <row r="182" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU181" s="3"/>
+      <c r="BV181" s="3"/>
+      <c r="BW181" s="3"/>
+      <c r="BX181" s="3"/>
+    </row>
+    <row r="182" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -17346,8 +18405,12 @@
       <c r="BR182" s="3"/>
       <c r="BS182" s="3"/>
       <c r="BT182" s="3"/>
-    </row>
-    <row r="183" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU182" s="3"/>
+      <c r="BV182" s="3"/>
+      <c r="BW182" s="3"/>
+      <c r="BX182" s="3"/>
+    </row>
+    <row r="183" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -17418,8 +18481,12 @@
       <c r="BR183" s="3"/>
       <c r="BS183" s="3"/>
       <c r="BT183" s="3"/>
-    </row>
-    <row r="184" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU183" s="3"/>
+      <c r="BV183" s="3"/>
+      <c r="BW183" s="3"/>
+      <c r="BX183" s="3"/>
+    </row>
+    <row r="184" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -17490,8 +18557,12 @@
       <c r="BR184" s="3"/>
       <c r="BS184" s="3"/>
       <c r="BT184" s="3"/>
-    </row>
-    <row r="185" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU184" s="3"/>
+      <c r="BV184" s="3"/>
+      <c r="BW184" s="3"/>
+      <c r="BX184" s="3"/>
+    </row>
+    <row r="185" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -17562,8 +18633,12 @@
       <c r="BR185" s="3"/>
       <c r="BS185" s="3"/>
       <c r="BT185" s="3"/>
-    </row>
-    <row r="186" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU185" s="3"/>
+      <c r="BV185" s="3"/>
+      <c r="BW185" s="3"/>
+      <c r="BX185" s="3"/>
+    </row>
+    <row r="186" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -17634,8 +18709,12 @@
       <c r="BR186" s="3"/>
       <c r="BS186" s="3"/>
       <c r="BT186" s="3"/>
-    </row>
-    <row r="187" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU186" s="3"/>
+      <c r="BV186" s="3"/>
+      <c r="BW186" s="3"/>
+      <c r="BX186" s="3"/>
+    </row>
+    <row r="187" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -17706,8 +18785,12 @@
       <c r="BR187" s="3"/>
       <c r="BS187" s="3"/>
       <c r="BT187" s="3"/>
-    </row>
-    <row r="188" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU187" s="3"/>
+      <c r="BV187" s="3"/>
+      <c r="BW187" s="3"/>
+      <c r="BX187" s="3"/>
+    </row>
+    <row r="188" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -17778,8 +18861,12 @@
       <c r="BR188" s="3"/>
       <c r="BS188" s="3"/>
       <c r="BT188" s="3"/>
-    </row>
-    <row r="189" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU188" s="3"/>
+      <c r="BV188" s="3"/>
+      <c r="BW188" s="3"/>
+      <c r="BX188" s="3"/>
+    </row>
+    <row r="189" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -17850,8 +18937,12 @@
       <c r="BR189" s="3"/>
       <c r="BS189" s="3"/>
       <c r="BT189" s="3"/>
-    </row>
-    <row r="190" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU189" s="3"/>
+      <c r="BV189" s="3"/>
+      <c r="BW189" s="3"/>
+      <c r="BX189" s="3"/>
+    </row>
+    <row r="190" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -17922,8 +19013,12 @@
       <c r="BR190" s="3"/>
       <c r="BS190" s="3"/>
       <c r="BT190" s="3"/>
-    </row>
-    <row r="191" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU190" s="3"/>
+      <c r="BV190" s="3"/>
+      <c r="BW190" s="3"/>
+      <c r="BX190" s="3"/>
+    </row>
+    <row r="191" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -17994,8 +19089,12 @@
       <c r="BR191" s="3"/>
       <c r="BS191" s="3"/>
       <c r="BT191" s="3"/>
-    </row>
-    <row r="192" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU191" s="3"/>
+      <c r="BV191" s="3"/>
+      <c r="BW191" s="3"/>
+      <c r="BX191" s="3"/>
+    </row>
+    <row r="192" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -18066,8 +19165,12 @@
       <c r="BR192" s="3"/>
       <c r="BS192" s="3"/>
       <c r="BT192" s="3"/>
-    </row>
-    <row r="193" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU192" s="3"/>
+      <c r="BV192" s="3"/>
+      <c r="BW192" s="3"/>
+      <c r="BX192" s="3"/>
+    </row>
+    <row r="193" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -18138,8 +19241,12 @@
       <c r="BR193" s="3"/>
       <c r="BS193" s="3"/>
       <c r="BT193" s="3"/>
-    </row>
-    <row r="194" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU193" s="3"/>
+      <c r="BV193" s="3"/>
+      <c r="BW193" s="3"/>
+      <c r="BX193" s="3"/>
+    </row>
+    <row r="194" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -18210,8 +19317,12 @@
       <c r="BR194" s="3"/>
       <c r="BS194" s="3"/>
       <c r="BT194" s="3"/>
-    </row>
-    <row r="195" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU194" s="3"/>
+      <c r="BV194" s="3"/>
+      <c r="BW194" s="3"/>
+      <c r="BX194" s="3"/>
+    </row>
+    <row r="195" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -18282,8 +19393,12 @@
       <c r="BR195" s="3"/>
       <c r="BS195" s="3"/>
       <c r="BT195" s="3"/>
-    </row>
-    <row r="196" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU195" s="3"/>
+      <c r="BV195" s="3"/>
+      <c r="BW195" s="3"/>
+      <c r="BX195" s="3"/>
+    </row>
+    <row r="196" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -18354,8 +19469,12 @@
       <c r="BR196" s="3"/>
       <c r="BS196" s="3"/>
       <c r="BT196" s="3"/>
-    </row>
-    <row r="197" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU196" s="3"/>
+      <c r="BV196" s="3"/>
+      <c r="BW196" s="3"/>
+      <c r="BX196" s="3"/>
+    </row>
+    <row r="197" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -18426,8 +19545,12 @@
       <c r="BR197" s="3"/>
       <c r="BS197" s="3"/>
       <c r="BT197" s="3"/>
-    </row>
-    <row r="198" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU197" s="3"/>
+      <c r="BV197" s="3"/>
+      <c r="BW197" s="3"/>
+      <c r="BX197" s="3"/>
+    </row>
+    <row r="198" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -18498,8 +19621,12 @@
       <c r="BR198" s="3"/>
       <c r="BS198" s="3"/>
       <c r="BT198" s="3"/>
-    </row>
-    <row r="199" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU198" s="3"/>
+      <c r="BV198" s="3"/>
+      <c r="BW198" s="3"/>
+      <c r="BX198" s="3"/>
+    </row>
+    <row r="199" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -18570,8 +19697,12 @@
       <c r="BR199" s="3"/>
       <c r="BS199" s="3"/>
       <c r="BT199" s="3"/>
-    </row>
-    <row r="200" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU199" s="3"/>
+      <c r="BV199" s="3"/>
+      <c r="BW199" s="3"/>
+      <c r="BX199" s="3"/>
+    </row>
+    <row r="200" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -18642,8 +19773,12 @@
       <c r="BR200" s="3"/>
       <c r="BS200" s="3"/>
       <c r="BT200" s="3"/>
-    </row>
-    <row r="201" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU200" s="3"/>
+      <c r="BV200" s="3"/>
+      <c r="BW200" s="3"/>
+      <c r="BX200" s="3"/>
+    </row>
+    <row r="201" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
@@ -18714,8 +19849,12 @@
       <c r="BR201" s="3"/>
       <c r="BS201" s="3"/>
       <c r="BT201" s="3"/>
-    </row>
-    <row r="202" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU201" s="3"/>
+      <c r="BV201" s="3"/>
+      <c r="BW201" s="3"/>
+      <c r="BX201" s="3"/>
+    </row>
+    <row r="202" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -18786,8 +19925,12 @@
       <c r="BR202" s="3"/>
       <c r="BS202" s="3"/>
       <c r="BT202" s="3"/>
-    </row>
-    <row r="203" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU202" s="3"/>
+      <c r="BV202" s="3"/>
+      <c r="BW202" s="3"/>
+      <c r="BX202" s="3"/>
+    </row>
+    <row r="203" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -18858,8 +20001,12 @@
       <c r="BR203" s="3"/>
       <c r="BS203" s="3"/>
       <c r="BT203" s="3"/>
-    </row>
-    <row r="204" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU203" s="3"/>
+      <c r="BV203" s="3"/>
+      <c r="BW203" s="3"/>
+      <c r="BX203" s="3"/>
+    </row>
+    <row r="204" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -18930,8 +20077,12 @@
       <c r="BR204" s="3"/>
       <c r="BS204" s="3"/>
       <c r="BT204" s="3"/>
-    </row>
-    <row r="205" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU204" s="3"/>
+      <c r="BV204" s="3"/>
+      <c r="BW204" s="3"/>
+      <c r="BX204" s="3"/>
+    </row>
+    <row r="205" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
@@ -19002,8 +20153,12 @@
       <c r="BR205" s="3"/>
       <c r="BS205" s="3"/>
       <c r="BT205" s="3"/>
-    </row>
-    <row r="206" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU205" s="3"/>
+      <c r="BV205" s="3"/>
+      <c r="BW205" s="3"/>
+      <c r="BX205" s="3"/>
+    </row>
+    <row r="206" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -19074,8 +20229,12 @@
       <c r="BR206" s="3"/>
       <c r="BS206" s="3"/>
       <c r="BT206" s="3"/>
-    </row>
-    <row r="207" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU206" s="3"/>
+      <c r="BV206" s="3"/>
+      <c r="BW206" s="3"/>
+      <c r="BX206" s="3"/>
+    </row>
+    <row r="207" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -19146,8 +20305,12 @@
       <c r="BR207" s="3"/>
       <c r="BS207" s="3"/>
       <c r="BT207" s="3"/>
-    </row>
-    <row r="208" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU207" s="3"/>
+      <c r="BV207" s="3"/>
+      <c r="BW207" s="3"/>
+      <c r="BX207" s="3"/>
+    </row>
+    <row r="208" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -19218,8 +20381,12 @@
       <c r="BR208" s="3"/>
       <c r="BS208" s="3"/>
       <c r="BT208" s="3"/>
-    </row>
-    <row r="209" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU208" s="3"/>
+      <c r="BV208" s="3"/>
+      <c r="BW208" s="3"/>
+      <c r="BX208" s="3"/>
+    </row>
+    <row r="209" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -19290,8 +20457,12 @@
       <c r="BR209" s="3"/>
       <c r="BS209" s="3"/>
       <c r="BT209" s="3"/>
-    </row>
-    <row r="210" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU209" s="3"/>
+      <c r="BV209" s="3"/>
+      <c r="BW209" s="3"/>
+      <c r="BX209" s="3"/>
+    </row>
+    <row r="210" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -19362,8 +20533,12 @@
       <c r="BR210" s="3"/>
       <c r="BS210" s="3"/>
       <c r="BT210" s="3"/>
-    </row>
-    <row r="211" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU210" s="3"/>
+      <c r="BV210" s="3"/>
+      <c r="BW210" s="3"/>
+      <c r="BX210" s="3"/>
+    </row>
+    <row r="211" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
@@ -19434,8 +20609,12 @@
       <c r="BR211" s="3"/>
       <c r="BS211" s="3"/>
       <c r="BT211" s="3"/>
-    </row>
-    <row r="212" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU211" s="3"/>
+      <c r="BV211" s="3"/>
+      <c r="BW211" s="3"/>
+      <c r="BX211" s="3"/>
+    </row>
+    <row r="212" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -19506,8 +20685,12 @@
       <c r="BR212" s="3"/>
       <c r="BS212" s="3"/>
       <c r="BT212" s="3"/>
-    </row>
-    <row r="213" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU212" s="3"/>
+      <c r="BV212" s="3"/>
+      <c r="BW212" s="3"/>
+      <c r="BX212" s="3"/>
+    </row>
+    <row r="213" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
@@ -19578,8 +20761,12 @@
       <c r="BR213" s="3"/>
       <c r="BS213" s="3"/>
       <c r="BT213" s="3"/>
-    </row>
-    <row r="214" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU213" s="3"/>
+      <c r="BV213" s="3"/>
+      <c r="BW213" s="3"/>
+      <c r="BX213" s="3"/>
+    </row>
+    <row r="214" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -19650,8 +20837,12 @@
       <c r="BR214" s="3"/>
       <c r="BS214" s="3"/>
       <c r="BT214" s="3"/>
-    </row>
-    <row r="215" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU214" s="3"/>
+      <c r="BV214" s="3"/>
+      <c r="BW214" s="3"/>
+      <c r="BX214" s="3"/>
+    </row>
+    <row r="215" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -19722,8 +20913,12 @@
       <c r="BR215" s="3"/>
       <c r="BS215" s="3"/>
       <c r="BT215" s="3"/>
-    </row>
-    <row r="216" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU215" s="3"/>
+      <c r="BV215" s="3"/>
+      <c r="BW215" s="3"/>
+      <c r="BX215" s="3"/>
+    </row>
+    <row r="216" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -19794,8 +20989,12 @@
       <c r="BR216" s="3"/>
       <c r="BS216" s="3"/>
       <c r="BT216" s="3"/>
-    </row>
-    <row r="217" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU216" s="3"/>
+      <c r="BV216" s="3"/>
+      <c r="BW216" s="3"/>
+      <c r="BX216" s="3"/>
+    </row>
+    <row r="217" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
@@ -19866,8 +21065,12 @@
       <c r="BR217" s="3"/>
       <c r="BS217" s="3"/>
       <c r="BT217" s="3"/>
-    </row>
-    <row r="218" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU217" s="3"/>
+      <c r="BV217" s="3"/>
+      <c r="BW217" s="3"/>
+      <c r="BX217" s="3"/>
+    </row>
+    <row r="218" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -19938,8 +21141,12 @@
       <c r="BR218" s="3"/>
       <c r="BS218" s="3"/>
       <c r="BT218" s="3"/>
-    </row>
-    <row r="219" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU218" s="3"/>
+      <c r="BV218" s="3"/>
+      <c r="BW218" s="3"/>
+      <c r="BX218" s="3"/>
+    </row>
+    <row r="219" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
@@ -20010,8 +21217,12 @@
       <c r="BR219" s="3"/>
       <c r="BS219" s="3"/>
       <c r="BT219" s="3"/>
-    </row>
-    <row r="220" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU219" s="3"/>
+      <c r="BV219" s="3"/>
+      <c r="BW219" s="3"/>
+      <c r="BX219" s="3"/>
+    </row>
+    <row r="220" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -20082,8 +21293,12 @@
       <c r="BR220" s="3"/>
       <c r="BS220" s="3"/>
       <c r="BT220" s="3"/>
-    </row>
-    <row r="221" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU220" s="3"/>
+      <c r="BV220" s="3"/>
+      <c r="BW220" s="3"/>
+      <c r="BX220" s="3"/>
+    </row>
+    <row r="221" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -20154,8 +21369,12 @@
       <c r="BR221" s="3"/>
       <c r="BS221" s="3"/>
       <c r="BT221" s="3"/>
-    </row>
-    <row r="222" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU221" s="3"/>
+      <c r="BV221" s="3"/>
+      <c r="BW221" s="3"/>
+      <c r="BX221" s="3"/>
+    </row>
+    <row r="222" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
@@ -20226,8 +21445,12 @@
       <c r="BR222" s="3"/>
       <c r="BS222" s="3"/>
       <c r="BT222" s="3"/>
-    </row>
-    <row r="223" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU222" s="3"/>
+      <c r="BV222" s="3"/>
+      <c r="BW222" s="3"/>
+      <c r="BX222" s="3"/>
+    </row>
+    <row r="223" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
@@ -20298,8 +21521,12 @@
       <c r="BR223" s="3"/>
       <c r="BS223" s="3"/>
       <c r="BT223" s="3"/>
-    </row>
-    <row r="224" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU223" s="3"/>
+      <c r="BV223" s="3"/>
+      <c r="BW223" s="3"/>
+      <c r="BX223" s="3"/>
+    </row>
+    <row r="224" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
@@ -20370,8 +21597,12 @@
       <c r="BR224" s="3"/>
       <c r="BS224" s="3"/>
       <c r="BT224" s="3"/>
-    </row>
-    <row r="225" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU224" s="3"/>
+      <c r="BV224" s="3"/>
+      <c r="BW224" s="3"/>
+      <c r="BX224" s="3"/>
+    </row>
+    <row r="225" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
@@ -20442,8 +21673,12 @@
       <c r="BR225" s="3"/>
       <c r="BS225" s="3"/>
       <c r="BT225" s="3"/>
-    </row>
-    <row r="226" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU225" s="3"/>
+      <c r="BV225" s="3"/>
+      <c r="BW225" s="3"/>
+      <c r="BX225" s="3"/>
+    </row>
+    <row r="226" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
@@ -20514,8 +21749,12 @@
       <c r="BR226" s="3"/>
       <c r="BS226" s="3"/>
       <c r="BT226" s="3"/>
-    </row>
-    <row r="227" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU226" s="3"/>
+      <c r="BV226" s="3"/>
+      <c r="BW226" s="3"/>
+      <c r="BX226" s="3"/>
+    </row>
+    <row r="227" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
       <c r="E227" s="3"/>
@@ -20586,8 +21825,12 @@
       <c r="BR227" s="3"/>
       <c r="BS227" s="3"/>
       <c r="BT227" s="3"/>
-    </row>
-    <row r="228" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU227" s="3"/>
+      <c r="BV227" s="3"/>
+      <c r="BW227" s="3"/>
+      <c r="BX227" s="3"/>
+    </row>
+    <row r="228" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
@@ -20658,8 +21901,12 @@
       <c r="BR228" s="3"/>
       <c r="BS228" s="3"/>
       <c r="BT228" s="3"/>
-    </row>
-    <row r="229" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU228" s="3"/>
+      <c r="BV228" s="3"/>
+      <c r="BW228" s="3"/>
+      <c r="BX228" s="3"/>
+    </row>
+    <row r="229" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
@@ -20730,8 +21977,12 @@
       <c r="BR229" s="3"/>
       <c r="BS229" s="3"/>
       <c r="BT229" s="3"/>
-    </row>
-    <row r="230" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU229" s="3"/>
+      <c r="BV229" s="3"/>
+      <c r="BW229" s="3"/>
+      <c r="BX229" s="3"/>
+    </row>
+    <row r="230" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
@@ -20802,8 +22053,12 @@
       <c r="BR230" s="3"/>
       <c r="BS230" s="3"/>
       <c r="BT230" s="3"/>
-    </row>
-    <row r="231" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU230" s="3"/>
+      <c r="BV230" s="3"/>
+      <c r="BW230" s="3"/>
+      <c r="BX230" s="3"/>
+    </row>
+    <row r="231" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
       <c r="E231" s="3"/>
@@ -20874,8 +22129,12 @@
       <c r="BR231" s="3"/>
       <c r="BS231" s="3"/>
       <c r="BT231" s="3"/>
-    </row>
-    <row r="232" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU231" s="3"/>
+      <c r="BV231" s="3"/>
+      <c r="BW231" s="3"/>
+      <c r="BX231" s="3"/>
+    </row>
+    <row r="232" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
@@ -20946,8 +22205,12 @@
       <c r="BR232" s="3"/>
       <c r="BS232" s="3"/>
       <c r="BT232" s="3"/>
-    </row>
-    <row r="233" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU232" s="3"/>
+      <c r="BV232" s="3"/>
+      <c r="BW232" s="3"/>
+      <c r="BX232" s="3"/>
+    </row>
+    <row r="233" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
       <c r="E233" s="3"/>
@@ -21018,8 +22281,12 @@
       <c r="BR233" s="3"/>
       <c r="BS233" s="3"/>
       <c r="BT233" s="3"/>
-    </row>
-    <row r="234" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU233" s="3"/>
+      <c r="BV233" s="3"/>
+      <c r="BW233" s="3"/>
+      <c r="BX233" s="3"/>
+    </row>
+    <row r="234" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
       <c r="E234" s="3"/>
@@ -21090,8 +22357,12 @@
       <c r="BR234" s="3"/>
       <c r="BS234" s="3"/>
       <c r="BT234" s="3"/>
-    </row>
-    <row r="235" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU234" s="3"/>
+      <c r="BV234" s="3"/>
+      <c r="BW234" s="3"/>
+      <c r="BX234" s="3"/>
+    </row>
+    <row r="235" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
@@ -21162,8 +22433,12 @@
       <c r="BR235" s="3"/>
       <c r="BS235" s="3"/>
       <c r="BT235" s="3"/>
-    </row>
-    <row r="236" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="BU235" s="3"/>
+      <c r="BV235" s="3"/>
+      <c r="BW235" s="3"/>
+      <c r="BX235" s="3"/>
+    </row>
+    <row r="236" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
@@ -21184,8 +22459,12 @@
       <c r="T236" s="3"/>
       <c r="U236" s="3"/>
       <c r="V236" s="3"/>
-    </row>
-    <row r="237" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="W236" s="3"/>
+      <c r="X236" s="3"/>
+      <c r="Y236" s="3"/>
+      <c r="Z236" s="3"/>
+    </row>
+    <row r="237" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="3"/>
@@ -21206,8 +22485,12 @@
       <c r="T237" s="3"/>
       <c r="U237" s="3"/>
       <c r="V237" s="3"/>
-    </row>
-    <row r="238" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="W237" s="3"/>
+      <c r="X237" s="3"/>
+      <c r="Y237" s="3"/>
+      <c r="Z237" s="3"/>
+    </row>
+    <row r="238" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
       <c r="E238" s="3"/>
@@ -21228,8 +22511,12 @@
       <c r="T238" s="3"/>
       <c r="U238" s="3"/>
       <c r="V238" s="3"/>
-    </row>
-    <row r="239" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="W238" s="3"/>
+      <c r="X238" s="3"/>
+      <c r="Y238" s="3"/>
+      <c r="Z238" s="3"/>
+    </row>
+    <row r="239" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
       <c r="E239" s="3"/>
@@ -21250,8 +22537,12 @@
       <c r="T239" s="3"/>
       <c r="U239" s="3"/>
       <c r="V239" s="3"/>
-    </row>
-    <row r="240" spans="3:72" x14ac:dyDescent="0.2">
+      <c r="W239" s="3"/>
+      <c r="X239" s="3"/>
+      <c r="Y239" s="3"/>
+      <c r="Z239" s="3"/>
+    </row>
+    <row r="240" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
       <c r="E240" s="3"/>
@@ -21272,8 +22563,12 @@
       <c r="T240" s="3"/>
       <c r="U240" s="3"/>
       <c r="V240" s="3"/>
-    </row>
-    <row r="241" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W240" s="3"/>
+      <c r="X240" s="3"/>
+      <c r="Y240" s="3"/>
+      <c r="Z240" s="3"/>
+    </row>
+    <row r="241" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
       <c r="E241" s="3"/>
@@ -21294,8 +22589,12 @@
       <c r="T241" s="3"/>
       <c r="U241" s="3"/>
       <c r="V241" s="3"/>
-    </row>
-    <row r="242" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W241" s="3"/>
+      <c r="X241" s="3"/>
+      <c r="Y241" s="3"/>
+      <c r="Z241" s="3"/>
+    </row>
+    <row r="242" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
@@ -21316,8 +22615,12 @@
       <c r="T242" s="3"/>
       <c r="U242" s="3"/>
       <c r="V242" s="3"/>
-    </row>
-    <row r="243" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W242" s="3"/>
+      <c r="X242" s="3"/>
+      <c r="Y242" s="3"/>
+      <c r="Z242" s="3"/>
+    </row>
+    <row r="243" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
       <c r="E243" s="3"/>
@@ -21338,8 +22641,12 @@
       <c r="T243" s="3"/>
       <c r="U243" s="3"/>
       <c r="V243" s="3"/>
-    </row>
-    <row r="244" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W243" s="3"/>
+      <c r="X243" s="3"/>
+      <c r="Y243" s="3"/>
+      <c r="Z243" s="3"/>
+    </row>
+    <row r="244" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
@@ -21360,8 +22667,12 @@
       <c r="T244" s="3"/>
       <c r="U244" s="3"/>
       <c r="V244" s="3"/>
-    </row>
-    <row r="245" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W244" s="3"/>
+      <c r="X244" s="3"/>
+      <c r="Y244" s="3"/>
+      <c r="Z244" s="3"/>
+    </row>
+    <row r="245" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
       <c r="E245" s="3"/>
@@ -21382,8 +22693,12 @@
       <c r="T245" s="3"/>
       <c r="U245" s="3"/>
       <c r="V245" s="3"/>
-    </row>
-    <row r="246" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W245" s="3"/>
+      <c r="X245" s="3"/>
+      <c r="Y245" s="3"/>
+      <c r="Z245" s="3"/>
+    </row>
+    <row r="246" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
       <c r="E246" s="3"/>
@@ -21404,8 +22719,12 @@
       <c r="T246" s="3"/>
       <c r="U246" s="3"/>
       <c r="V246" s="3"/>
-    </row>
-    <row r="247" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W246" s="3"/>
+      <c r="X246" s="3"/>
+      <c r="Y246" s="3"/>
+      <c r="Z246" s="3"/>
+    </row>
+    <row r="247" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
       <c r="E247" s="3"/>
@@ -21426,8 +22745,12 @@
       <c r="T247" s="3"/>
       <c r="U247" s="3"/>
       <c r="V247" s="3"/>
-    </row>
-    <row r="248" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W247" s="3"/>
+      <c r="X247" s="3"/>
+      <c r="Y247" s="3"/>
+      <c r="Z247" s="3"/>
+    </row>
+    <row r="248" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
       <c r="E248" s="3"/>
@@ -21448,6 +22771,10 @@
       <c r="T248" s="3"/>
       <c r="U248" s="3"/>
       <c r="V248" s="3"/>
+      <c r="W248" s="3"/>
+      <c r="X248" s="3"/>
+      <c r="Y248" s="3"/>
+      <c r="Z248" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -23864,19 +25191,19 @@
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B69" s="73"/>
-      <c r="C69" s="79" t="s">
+      <c r="C69" s="78" t="s">
         <v>154</v>
       </c>
-      <c r="D69" s="79"/>
-      <c r="E69" s="79"/>
-      <c r="F69" s="79"/>
-      <c r="G69" s="79"/>
-      <c r="H69" s="79"/>
-      <c r="I69" s="79"/>
-      <c r="J69" s="80"/>
+      <c r="D69" s="78"/>
+      <c r="E69" s="78"/>
+      <c r="F69" s="78"/>
+      <c r="G69" s="78"/>
+      <c r="H69" s="78"/>
+      <c r="I69" s="78"/>
+      <c r="J69" s="79"/>
     </row>
     <row r="70" spans="1:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="81" t="s">
+      <c r="B70" s="80" t="s">
         <v>153</v>
       </c>
       <c r="C70" s="74"/>
@@ -23889,7 +25216,7 @@
       <c r="J70" s="75"/>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B71" s="81"/>
+      <c r="B71" s="80"/>
       <c r="C71" s="76"/>
       <c r="D71" s="77"/>
       <c r="E71" s="77"/>
@@ -23900,7 +25227,7 @@
       <c r="J71" s="77"/>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B72" s="81"/>
+      <c r="B72" s="80"/>
       <c r="C72" s="76"/>
       <c r="D72" s="77"/>
       <c r="E72" s="77"/>
@@ -23911,7 +25238,7 @@
       <c r="J72" s="77"/>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B73" s="81"/>
+      <c r="B73" s="80"/>
       <c r="C73" s="76"/>
       <c r="D73" s="77"/>
       <c r="E73" s="77"/>
@@ -23922,7 +25249,7 @@
       <c r="J73" s="77"/>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B74" s="81"/>
+      <c r="B74" s="80"/>
       <c r="C74" s="76"/>
       <c r="D74" s="77"/>
       <c r="E74" s="77"/>
@@ -23933,7 +25260,7 @@
       <c r="J74" s="77"/>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B75" s="81"/>
+      <c r="B75" s="80"/>
       <c r="C75" s="76"/>
       <c r="D75" s="77"/>
       <c r="E75" s="77"/>
@@ -23944,7 +25271,7 @@
       <c r="J75" s="77"/>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B76" s="81"/>
+      <c r="B76" s="80"/>
       <c r="C76" s="76"/>
       <c r="D76" s="77"/>
       <c r="E76" s="77"/>
@@ -23955,7 +25282,7 @@
       <c r="J76" s="77"/>
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B77" s="82"/>
+      <c r="B77" s="81"/>
       <c r="C77" s="76"/>
       <c r="D77" s="77"/>
       <c r="E77" s="77"/>
